--- a/database/event/2261/event_2261_evp_summary.xlsx
+++ b/database/event/2261/event_2261_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7893</v>
+        <v>7.4539</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0522</v>
+        <v>3.351</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3214</v>
+        <v>2.5257</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7893</v>
+        <v>7.4539</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5753</v>
+        <v>3.2399</v>
       </c>
       <c r="G2" t="n">
         <v>4.214</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5753</v>
+        <v>3.2399</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5753</v>
+        <v>3.2399</v>
       </c>
       <c r="J2" t="n">
         <v>4.214</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>6.789300000000001</v>
+        <v>7.453900000000001</v>
       </c>
       <c r="N2" t="n">
         <v>333</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1334</v>
+        <v>6.4674</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7574</v>
+        <v>2.9075</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0564</v>
+        <v>2.1327</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1334</v>
+        <v>6.4674</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2748</v>
+        <v>4.6088</v>
       </c>
       <c r="G3" t="n">
         <v>1.8586</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6381</v>
+        <v>5.9818</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7593</v>
+        <v>4.8484</v>
       </c>
       <c r="J3" t="n">
         <v>1.8586</v>
@@ -575,7 +575,7 @@
         <v>85</v>
       </c>
       <c r="M3" t="n">
-        <v>5.617900000000001</v>
+        <v>6.707</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5065</v>
+        <v>6.2302</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4755</v>
+        <v>2.8009</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8031</v>
+        <v>2.0382</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5065</v>
+        <v>6.2302</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2162</v>
+        <v>2.4585</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2903</v>
+        <v>3.7717</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2162</v>
+        <v>2.4585</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2162</v>
+        <v>2.4585</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2903</v>
+        <v>3.7717</v>
       </c>
       <c r="K4" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5065</v>
+        <v>6.2302</v>
       </c>
       <c r="N4" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4803</v>
+        <v>5.7127</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4638</v>
+        <v>2.5682</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7926</v>
+        <v>1.832</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4803</v>
+        <v>5.7127</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7086</v>
+        <v>1.4224</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7717</v>
+        <v>4.2903</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7086</v>
+        <v>1.4224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7086</v>
+        <v>1.4224</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7717</v>
+        <v>4.2903</v>
       </c>
       <c r="K5" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="L5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4803</v>
+        <v>5.7127</v>
       </c>
       <c r="N5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6127</v>
+        <v>4.3547</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6242</v>
+        <v>1.9577</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0381</v>
+        <v>1.291</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6127</v>
+        <v>4.3547</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9901</v>
+        <v>3.7321</v>
       </c>
       <c r="G6" t="n">
         <v>0.6226</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9901</v>
+        <v>3.7321</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4235</v>
+        <v>3.025</v>
       </c>
       <c r="J6" t="n">
         <v>0.6226</v>
@@ -713,7 +713,7 @@
         <v>85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0461</v>
+        <v>3.6476</v>
       </c>
       <c r="N6" t="n">
         <v>211</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4931</v>
+        <v>3.831</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5704</v>
+        <v>1.7223</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9898</v>
+        <v>1.0824</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4931</v>
+        <v>3.831</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4229</v>
+        <v>4.1722</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9298</v>
+        <v>-0.3412</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2337</v>
+        <v>4.2252</v>
       </c>
       <c r="I7" t="n">
-        <v>4.242</v>
+        <v>3.4246</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9298</v>
+        <v>-0.3412</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3122</v>
+        <v>3.0834</v>
       </c>
       <c r="N7" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2289</v>
+        <v>3.7728</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4516</v>
+        <v>1.6961</v>
       </c>
       <c r="D8" t="n">
-        <v>0.883</v>
+        <v>1.0592</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2289</v>
+        <v>3.7728</v>
       </c>
       <c r="F8" t="n">
-        <v>0.198</v>
+        <v>4.7026</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0309</v>
+        <v>-0.9298</v>
       </c>
       <c r="H8" t="n">
-        <v>0.198</v>
+        <v>6.3594</v>
       </c>
       <c r="I8" t="n">
-        <v>0.198</v>
+        <v>5.1544</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0309</v>
+        <v>-0.9298</v>
       </c>
       <c r="K8" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L8" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2289</v>
+        <v>4.2246</v>
       </c>
       <c r="N8" t="n">
-        <v>333</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1575</v>
+        <v>3.7436</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4195</v>
+        <v>1.683</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8542</v>
+        <v>1.0475</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1575</v>
+        <v>3.7436</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6441</v>
+        <v>1.7353</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4866</v>
+        <v>2.0083</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6441</v>
+        <v>1.7353</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9536</v>
+        <v>1.7353</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4866</v>
+        <v>2.0083</v>
       </c>
       <c r="K9" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="M9" t="n">
-        <v>2.467</v>
+        <v>3.7436</v>
       </c>
       <c r="N9" t="n">
-        <v>211</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0983</v>
+        <v>3.6695</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3929</v>
+        <v>1.6497</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8303</v>
+        <v>1.018</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0983</v>
+        <v>3.6695</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4395</v>
+        <v>4.1561</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3412</v>
+        <v>-0.4866</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4395</v>
+        <v>4.1606</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7878</v>
+        <v>3.3723</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3412</v>
+        <v>-0.4866</v>
       </c>
       <c r="K10" t="n">
         <v>126</v>
@@ -897,7 +897,7 @@
         <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4466</v>
+        <v>2.8857</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -906,955 +906,955 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8985</v>
+        <v>3.4276</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3031</v>
+        <v>1.5409</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7496</v>
+        <v>0.9216</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8985</v>
+        <v>3.4276</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8902</v>
+        <v>0.3967</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0083</v>
+        <v>3.0309</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8902</v>
+        <v>0.3967</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8902</v>
+        <v>0.3967</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0083</v>
+        <v>3.0309</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8985</v>
+        <v>3.4276</v>
       </c>
       <c r="N11" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.566</v>
+        <v>3.2723</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1536</v>
+        <v>1.4711</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6152</v>
+        <v>0.8598</v>
       </c>
       <c r="E12" t="n">
-        <v>2.566</v>
+        <v>3.2723</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4309</v>
+        <v>3.2723</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9969</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4309</v>
+        <v>3.2723</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4309</v>
+        <v>3.2723</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9969</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.566</v>
+        <v>3.2723</v>
       </c>
       <c r="N12" t="n">
-        <v>334</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.303</v>
+        <v>3.1195</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0354</v>
+        <v>1.4024</v>
       </c>
       <c r="D13" t="n">
-        <v>0.509</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.303</v>
+        <v>3.1195</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2742</v>
+        <v>2.778</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0288</v>
+        <v>0.3415</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2742</v>
+        <v>2.778</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2742</v>
+        <v>2.8013</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0288</v>
+        <v>0.3415</v>
       </c>
       <c r="K13" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="L13" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
-        <v>2.303</v>
+        <v>3.1428</v>
       </c>
       <c r="N13" t="n">
-        <v>333</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1276</v>
+        <v>3.0357</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9565</v>
+        <v>1.3648</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4381</v>
+        <v>0.7655</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1276</v>
+        <v>3.0357</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0609</v>
+        <v>4.0357</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0667</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0609</v>
+        <v>4.0357</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6704</v>
+        <v>4.0697</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0667</v>
+        <v>-1</v>
       </c>
       <c r="K14" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L14" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7371</v>
+        <v>3.0697</v>
       </c>
       <c r="N14" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1156</v>
+        <v>2.695</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9510999999999999</v>
+        <v>1.2116</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4333</v>
+        <v>0.6298</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1156</v>
+        <v>2.695</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8161</v>
+        <v>2.6283</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7005</v>
+        <v>0.0667</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8161</v>
+        <v>2.6283</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2825</v>
+        <v>2.1303</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7005</v>
+        <v>0.0667</v>
       </c>
       <c r="K15" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.582</v>
+        <v>2.197</v>
       </c>
       <c r="N15" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0741</v>
+        <v>2.5701</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9324</v>
+        <v>1.1554</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4165</v>
+        <v>0.58</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0741</v>
+        <v>2.5701</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0741</v>
+        <v>-0.4268</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.9969</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0741</v>
+        <v>-0.4268</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0741</v>
+        <v>-0.4268</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.9969</v>
       </c>
       <c r="K16" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0741</v>
+        <v>2.5701</v>
       </c>
       <c r="N16" t="n">
-        <v>127</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7749</v>
+        <v>2.5168</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.1315</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2957</v>
+        <v>0.5588</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7749</v>
+        <v>2.5168</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4334</v>
+        <v>2.5168</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3415</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4334</v>
+        <v>2.5168</v>
       </c>
       <c r="I17" t="n">
-        <v>1.44</v>
+        <v>2.5168</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3415</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7815</v>
+        <v>2.5168</v>
       </c>
       <c r="N17" t="n">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7502</v>
+        <v>2.5091</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7868000000000001</v>
+        <v>1.128</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2857</v>
+        <v>0.5557</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7502</v>
+        <v>2.5091</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3817</v>
+        <v>3.2096</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1319</v>
+        <v>-0.7005</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3817</v>
+        <v>3.2096</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3817</v>
+        <v>2.6015</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1319</v>
+        <v>-0.7005</v>
       </c>
       <c r="K18" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L18" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7502</v>
+        <v>1.901</v>
       </c>
       <c r="N18" t="n">
-        <v>333</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7147</v>
+        <v>2.3586</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7709</v>
+        <v>1.0603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2713</v>
+        <v>0.4958</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7147</v>
+        <v>2.3586</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7147</v>
+        <v>0.3298</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.0288</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7147</v>
+        <v>0.3298</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7147</v>
+        <v>0.3298</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.0288</v>
       </c>
       <c r="K19" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7147</v>
+        <v>2.3586</v>
       </c>
       <c r="N19" t="n">
-        <v>146</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.705</v>
+        <v>2.1689</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7665</v>
+        <v>0.9751</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2674</v>
+        <v>0.4202</v>
       </c>
       <c r="E20" t="n">
-        <v>1.705</v>
+        <v>2.1689</v>
       </c>
       <c r="F20" t="n">
-        <v>2.705</v>
+        <v>2.1689</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.705</v>
+        <v>2.1689</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7176</v>
+        <v>2.1689</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7176</v>
+        <v>2.1689</v>
       </c>
       <c r="N20" t="n">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3498</v>
+        <v>2.0407</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6068</v>
+        <v>0.9174</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1239</v>
+        <v>0.3691</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3498</v>
+        <v>2.0407</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1786</v>
+        <v>1.9659</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1712</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1786</v>
+        <v>1.9659</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9553</v>
+        <v>1.9659</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1712</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>129</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1265</v>
+        <v>2.0407</v>
       </c>
       <c r="N21" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3208</v>
+        <v>2.0322</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5938</v>
+        <v>0.9136</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1122</v>
+        <v>0.3657</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3208</v>
+        <v>2.0322</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3208</v>
+        <v>-0.0997</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.1319</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3208</v>
+        <v>-0.0997</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3208</v>
+        <v>-0.0997</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.1319</v>
       </c>
       <c r="K22" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3208</v>
+        <v>2.0322</v>
       </c>
       <c r="N22" t="n">
-        <v>146</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3171</v>
+        <v>1.9863</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5921</v>
+        <v>0.893</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1107</v>
+        <v>0.3474</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3171</v>
+        <v>1.9863</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2359</v>
+        <v>2.3244</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0812</v>
+        <v>-0.3381</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2359</v>
+        <v>2.3244</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2359</v>
+        <v>2.344</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0812</v>
+        <v>-0.3381</v>
       </c>
       <c r="K23" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="L23" t="n">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3171</v>
+        <v>2.0059</v>
       </c>
       <c r="N23" t="n">
-        <v>334</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.302</v>
+        <v>1.9034</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5853</v>
+        <v>0.8557</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1046</v>
+        <v>0.3144</v>
       </c>
       <c r="E24" t="n">
-        <v>1.302</v>
+        <v>1.9034</v>
       </c>
       <c r="F24" t="n">
-        <v>1.302</v>
+        <v>1.7322</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1712</v>
       </c>
       <c r="H24" t="n">
-        <v>1.302</v>
+        <v>1.7322</v>
       </c>
       <c r="I24" t="n">
-        <v>1.302</v>
+        <v>1.404</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1712</v>
       </c>
       <c r="K24" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M24" t="n">
-        <v>1.302</v>
+        <v>1.5752</v>
       </c>
       <c r="N24" t="n">
-        <v>127</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5834</v>
+        <v>0.8329</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1028</v>
+        <v>0.2942</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2976</v>
+        <v>1.8527</v>
       </c>
       <c r="N25" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2768</v>
+        <v>1.7258</v>
       </c>
       <c r="C26" t="n">
-        <v>0.574</v>
+        <v>0.7759</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0944</v>
+        <v>0.2436</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2768</v>
+        <v>1.7258</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6149</v>
+        <v>1.7258</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3381</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6149</v>
+        <v>1.7258</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6225</v>
+        <v>1.7258</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3381</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2844</v>
+        <v>1.7258</v>
       </c>
       <c r="N26" t="n">
-        <v>199</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0295</v>
+        <v>1.3496</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4628</v>
+        <v>0.6067</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0055</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0295</v>
+        <v>1.3496</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9547</v>
+        <v>1.3496</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07480000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9547</v>
+        <v>1.3496</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9547</v>
+        <v>1.3496</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07480000000000001</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L27" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0295</v>
+        <v>1.3496</v>
       </c>
       <c r="N27" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9291</v>
+        <v>1.3257</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4177</v>
+        <v>0.596</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.046</v>
+        <v>0.0842</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9291</v>
+        <v>1.3257</v>
       </c>
       <c r="F28" t="n">
-        <v>1.194</v>
+        <v>0.2445</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2649</v>
+        <v>1.0812</v>
       </c>
       <c r="H28" t="n">
-        <v>1.194</v>
+        <v>0.2445</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9678</v>
+        <v>0.2445</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2649</v>
+        <v>1.0812</v>
       </c>
       <c r="K28" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7029</v>
+        <v>1.3257</v>
       </c>
       <c r="N28" t="n">
-        <v>187</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3845</v>
+        <v>0.5938</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07580000000000001</v>
+        <v>0.0823</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3209</v>
       </c>
       <c r="N29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7522</v>
+        <v>1.2761</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3382</v>
+        <v>0.5737</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1175</v>
+        <v>0.0645</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7522</v>
+        <v>1.2761</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7522</v>
+        <v>1.6879</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4118</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7522</v>
+        <v>1.6879</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7522</v>
+        <v>1.3681</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4118</v>
       </c>
       <c r="K30" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7522</v>
+        <v>0.9563000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>126</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.711</v>
+        <v>1.0646</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3196</v>
+        <v>0.4786</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1341</v>
+        <v>-0.0198</v>
       </c>
       <c r="E31" t="n">
-        <v>0.711</v>
+        <v>1.0646</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1228</v>
+        <v>1.3295</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4118</v>
+        <v>-0.2649</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1228</v>
+        <v>1.3295</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9101</v>
+        <v>1.0776</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4118</v>
+        <v>-0.2649</v>
       </c>
       <c r="K31" t="n">
         <v>129</v>
@@ -1863,7 +1863,7 @@
         <v>58</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4983</v>
+        <v>0.8126999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>187</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2675</v>
+        <v>0.4218</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.181</v>
+        <v>-0.0701</v>
       </c>
       <c r="E32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="F32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="I32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.595</v>
+        <v>0.9383</v>
       </c>
       <c r="N32" t="n">
         <v>127</v>
@@ -1918,415 +1918,415 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5694</v>
+        <v>0.9018</v>
       </c>
       <c r="C33" t="n">
-        <v>0.256</v>
+        <v>0.4054</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1913</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5694</v>
+        <v>0.9018</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5694</v>
+        <v>0.7242</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1776</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5694</v>
+        <v>0.7242</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5694</v>
+        <v>0.7242</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.1776</v>
       </c>
       <c r="K33" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5694</v>
+        <v>0.9017999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>137</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="C34" t="n">
-        <v>0.202</v>
+        <v>0.3393</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2398</v>
+        <v>-0.1432</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4494</v>
+        <v>0.7547</v>
       </c>
       <c r="N34" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1817</v>
+        <v>0.256</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2581</v>
+        <v>-0.2171</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4042</v>
+        <v>0.5694</v>
       </c>
       <c r="N35" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3152</v>
+        <v>0.5218</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1417</v>
+        <v>0.2346</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.294</v>
+        <v>-0.236</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3152</v>
+        <v>0.5218</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1376</v>
+        <v>0.5218</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1776</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1376</v>
+        <v>0.5218</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1376</v>
+        <v>0.5218</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1776</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="L36" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3152</v>
+        <v>0.5218</v>
       </c>
       <c r="N36" t="n">
-        <v>334</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1243</v>
+        <v>0.1817</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3097</v>
+        <v>-0.2829</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2764</v>
+        <v>0.4042</v>
       </c>
       <c r="N37" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0687</v>
+        <v>0.1772</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3596</v>
+        <v>-0.2869</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1528</v>
+        <v>0.3941</v>
       </c>
       <c r="N38" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0496</v>
+        <v>0.1511</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3768</v>
+        <v>-0.31</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1104</v>
+        <v>0.3362</v>
       </c>
       <c r="N39" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1092</v>
+        <v>0.3276</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0491</v>
+        <v>0.1473</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3772</v>
+        <v>-0.3134</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1092</v>
+        <v>0.3276</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1092</v>
+        <v>1.1745</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.8469</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1092</v>
+        <v>1.1745</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1092</v>
+        <v>1.1745</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.8469</v>
       </c>
       <c r="K40" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1092</v>
+        <v>0.3276000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0141</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4087</v>
+        <v>-0.3827</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0313</v>
+        <v>0.1536</v>
       </c>
       <c r="N41" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0677</v>
+        <v>0.0184</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4822</v>
+        <v>-0.4276</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1505</v>
+        <v>0.041</v>
       </c>
       <c r="N42" t="n">
         <v>137</v>
@@ -2378,369 +2378,369 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0843</v>
+        <v>0.0141</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4971</v>
+        <v>-0.4314</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1876</v>
+        <v>0.0313</v>
       </c>
       <c r="N43" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1863</v>
+        <v>-0.0843</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5888</v>
+        <v>-0.5187</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.4144</v>
+        <v>-0.1876</v>
       </c>
       <c r="N44" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.483</v>
+        <v>-0.4144</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2171</v>
+        <v>-0.1863</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6165</v>
+        <v>-0.609</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.483</v>
+        <v>-0.4144</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3639</v>
+        <v>-0.4144</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.8469</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3639</v>
+        <v>-0.4144</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3639</v>
+        <v>-0.4144</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8469</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L45" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.483</v>
+        <v>-0.4144</v>
       </c>
       <c r="N45" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.6313</v>
+        <v>-0.4243</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2838</v>
+        <v>-0.1908</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6764</v>
+        <v>-0.613</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.6313</v>
+        <v>-0.4243</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6313</v>
+        <v>0.5757</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6313</v>
+        <v>0.5757</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6313</v>
+        <v>0.5757</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.6313</v>
+        <v>-0.4243</v>
       </c>
       <c r="N46" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.643</v>
+        <v>-0.6313</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2891</v>
+        <v>-0.2838</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6811</v>
+        <v>-0.6954</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.643</v>
+        <v>-0.6313</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0243</v>
+        <v>-0.6313</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0243</v>
+        <v>-0.6313</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0244</v>
+        <v>-0.6313</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="L47" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6429</v>
+        <v>-0.6313</v>
       </c>
       <c r="N47" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.8759</v>
+        <v>-0.6431</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3938</v>
+        <v>-0.2891</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7752</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.8759</v>
+        <v>-0.6431</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1241</v>
+        <v>0.0242</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>-0.6673</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1241</v>
+        <v>0.0242</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1241</v>
+        <v>0.0244</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>-0.6673</v>
       </c>
       <c r="K48" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.8759</v>
+        <v>-0.6429</v>
       </c>
       <c r="N48" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.0044</v>
+        <v>-0.8164</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4515</v>
+        <v>-0.367</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.7692</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0044</v>
+        <v>-0.8164</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4628</v>
+        <v>0.1836</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5416</v>
+        <v>-1</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4628</v>
+        <v>0.1836</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4628</v>
+        <v>0.1851</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5416</v>
+        <v>-1</v>
       </c>
       <c r="K49" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L49" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.0044</v>
+        <v>-0.8149</v>
       </c>
       <c r="N49" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.0085</v>
+        <v>-0.9568</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4534</v>
+        <v>-0.4301</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8288</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0085</v>
+        <v>-0.9568</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.4152</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>-0.5416</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.4152</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0086</v>
+        <v>-0.4152</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>-0.5416</v>
       </c>
       <c r="K50" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.0086</v>
+        <v>-0.9568</v>
       </c>
       <c r="N50" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51">
@@ -2756,7 +2756,7 @@
         <v>-0.4809</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8535</v>
+        <v>-0.8701</v>
       </c>
       <c r="E51" t="n">
         <v>-1.0697</v>
@@ -2802,7 +2802,7 @@
         <v>-0.4909</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8625</v>
+        <v>-0.8789</v>
       </c>
       <c r="E52" t="n">
         <v>-1.0919</v>
@@ -2848,7 +2848,7 @@
         <v>-0.5646</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9287</v>
+        <v>-0.9443</v>
       </c>
       <c r="E53" t="n">
         <v>-1.2559</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.4375</v>
+        <v>-1.4287</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6463</v>
+        <v>-0.6423</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0021</v>
+        <v>-1.0131</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.4375</v>
+        <v>-1.4287</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.7326</v>
+        <v>-0.7238</v>
       </c>
       <c r="G54" t="n">
         <v>-0.7049</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7326</v>
+        <v>-0.7238</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.7326</v>
+        <v>-0.7238</v>
       </c>
       <c r="J54" t="n">
         <v>-0.7049</v>
@@ -2921,7 +2921,7 @@
         <v>62</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.4375</v>
+        <v>-1.4287</v>
       </c>
       <c r="N54" t="n">
         <v>191</v>
@@ -2940,7 +2940,7 @@
         <v>-0.6681</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.0217</v>
+        <v>-1.036</v>
       </c>
       <c r="E55" t="n">
         <v>-1.4861</v>
@@ -2986,7 +2986,7 @@
         <v>-0.6971000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.0477</v>
+        <v>-1.0616</v>
       </c>
       <c r="E56" t="n">
         <v>-1.5505</v>
@@ -3032,7 +3032,7 @@
         <v>-0.86</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1942</v>
+        <v>-1.206</v>
       </c>
       <c r="E57" t="n">
         <v>-1.913</v>
@@ -3078,7 +3078,7 @@
         <v>-0.8637</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1974</v>
+        <v>-1.2093</v>
       </c>
       <c r="E58" t="n">
         <v>-1.9211</v>
@@ -3124,7 +3124,7 @@
         <v>-0.9275</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2548</v>
+        <v>-1.2659</v>
       </c>
       <c r="E59" t="n">
         <v>-2.0632</v>
@@ -3170,7 +3170,7 @@
         <v>-1.0924</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.403</v>
+        <v>-1.412</v>
       </c>
       <c r="E60" t="n">
         <v>-2.43</v>
@@ -3216,7 +3216,7 @@
         <v>-1.2326</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.529</v>
+        <v>-1.5362</v>
       </c>
       <c r="E61" t="n">
         <v>-2.7418</v>

--- a/database/event/2261/event_2261_evp_summary.xlsx
+++ b/database/event/2261/event_2261_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4539</v>
+        <v>6.9526</v>
       </c>
       <c r="C2" t="n">
-        <v>3.351</v>
+        <v>3.1257</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5257</v>
+        <v>2.5007</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4539</v>
+        <v>6.9526</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2399</v>
+        <v>2.9727</v>
       </c>
       <c r="G2" t="n">
-        <v>4.214</v>
+        <v>3.9799</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2399</v>
+        <v>3.1677</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2399</v>
+        <v>3.1677</v>
       </c>
       <c r="J2" t="n">
-        <v>4.214</v>
+        <v>3.9799</v>
       </c>
       <c r="K2" t="n">
         <v>133</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.453900000000001</v>
+        <v>7.147600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>333</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4674</v>
+        <v>5.9321</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9075</v>
+        <v>2.6669</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1327</v>
+        <v>2.04</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4674</v>
+        <v>5.9321</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6088</v>
+        <v>2.6605</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8586</v>
+        <v>3.2716</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9818</v>
+        <v>2.6605</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8484</v>
+        <v>2.6605</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8586</v>
+        <v>3.2716</v>
       </c>
       <c r="K3" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L3" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>6.707</v>
+        <v>5.9321</v>
       </c>
       <c r="N3" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2302</v>
+        <v>5.6615</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8009</v>
+        <v>2.5452</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0382</v>
+        <v>1.9179</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2302</v>
+        <v>5.6615</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4585</v>
+        <v>4.0812</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7717</v>
+        <v>1.5803</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4585</v>
+        <v>8.8931</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4585</v>
+        <v>4.624</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7717</v>
+        <v>1.5803</v>
       </c>
       <c r="K4" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L4" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2302</v>
+        <v>6.2043</v>
       </c>
       <c r="N4" t="n">
-        <v>333</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7127</v>
+        <v>5.1348</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5682</v>
+        <v>2.3084</v>
       </c>
       <c r="D5" t="n">
-        <v>1.832</v>
+        <v>1.6801</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7127</v>
+        <v>5.1348</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4224</v>
+        <v>1.5204</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2903</v>
+        <v>3.6144</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4224</v>
+        <v>1.5204</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4224</v>
+        <v>1.5204</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2903</v>
+        <v>3.6144</v>
       </c>
       <c r="K5" t="n">
         <v>124</v>
@@ -667,7 +667,7 @@
         <v>210</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7127</v>
+        <v>5.1348</v>
       </c>
       <c r="N5" t="n">
         <v>334</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3547</v>
+        <v>3.8512</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9577</v>
+        <v>1.7314</v>
       </c>
       <c r="D6" t="n">
-        <v>1.291</v>
+        <v>1.1006</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3547</v>
+        <v>3.8512</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7321</v>
+        <v>3.2003</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6226</v>
+        <v>0.6509</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7321</v>
+        <v>5.7895</v>
       </c>
       <c r="I6" t="n">
-        <v>3.025</v>
+        <v>3.0103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6226</v>
+        <v>0.6509</v>
       </c>
       <c r="K6" t="n">
         <v>126</v>
@@ -713,7 +713,7 @@
         <v>85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6476</v>
+        <v>3.6612</v>
       </c>
       <c r="N6" t="n">
         <v>211</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.831</v>
+        <v>3.688</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7223</v>
+        <v>1.658</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0824</v>
+        <v>1.0269</v>
       </c>
       <c r="E7" t="n">
-        <v>3.831</v>
+        <v>3.688</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1722</v>
+        <v>1.8938</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3412</v>
+        <v>1.7942</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2252</v>
+        <v>1.8938</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4246</v>
+        <v>1.8938</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3412</v>
+        <v>1.7942</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0834</v>
+        <v>3.688</v>
       </c>
       <c r="N7" t="n">
-        <v>211</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7728</v>
+        <v>3.5302</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6961</v>
+        <v>1.5871</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0592</v>
+        <v>0.9557</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7728</v>
+        <v>3.5302</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7026</v>
+        <v>4.1312</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9298</v>
+        <v>-0.601</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3594</v>
+        <v>9.0694</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1544</v>
+        <v>4.7157</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9298</v>
+        <v>-0.601</v>
       </c>
       <c r="K8" t="n">
         <v>129</v>
@@ -805,7 +805,7 @@
         <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2246</v>
+        <v>4.1147</v>
       </c>
       <c r="N8" t="n">
         <v>187</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7436</v>
+        <v>3.2595</v>
       </c>
       <c r="C9" t="n">
-        <v>1.683</v>
+        <v>1.4654</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0475</v>
+        <v>0.8335</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7436</v>
+        <v>3.2595</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7353</v>
+        <v>3.4119</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0083</v>
+        <v>-0.1524</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7353</v>
+        <v>6.5352</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7353</v>
+        <v>3.398</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0083</v>
+        <v>-0.1524</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7436</v>
+        <v>3.2456</v>
       </c>
       <c r="N9" t="n">
-        <v>334</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6695</v>
+        <v>3.2174</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6497</v>
+        <v>1.4464</v>
       </c>
       <c r="D10" t="n">
-        <v>1.018</v>
+        <v>0.8145</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6695</v>
+        <v>3.2174</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1561</v>
+        <v>0.6938</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4866</v>
+        <v>2.5236</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1606</v>
+        <v>0.6938</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3723</v>
+        <v>0.6938</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4866</v>
+        <v>2.5236</v>
       </c>
       <c r="K10" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L10" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8857</v>
+        <v>3.2174</v>
       </c>
       <c r="N10" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4276</v>
+        <v>3.2058</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5409</v>
+        <v>1.4412</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9216</v>
+        <v>0.8092</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4276</v>
+        <v>3.2058</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3967</v>
+        <v>3.399</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0309</v>
+        <v>-0.1932</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3967</v>
+        <v>6.4895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3967</v>
+        <v>3.3743</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0309</v>
+        <v>-0.1932</v>
       </c>
       <c r="K11" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L11" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4276</v>
+        <v>3.1811</v>
       </c>
       <c r="N11" t="n">
-        <v>333</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2723</v>
+        <v>3.0145</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4711</v>
+        <v>1.3552</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8598</v>
+        <v>0.7229</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2723</v>
+        <v>3.0145</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2723</v>
+        <v>3.0145</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2723</v>
+        <v>3.2595</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2723</v>
+        <v>3.2595</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2723</v>
+        <v>3.2595</v>
       </c>
       <c r="N12" t="n">
         <v>127</v>
@@ -998,277 +998,277 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1195</v>
+        <v>2.8241</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4024</v>
+        <v>1.2696</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.6369</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1195</v>
+        <v>2.8241</v>
       </c>
       <c r="F13" t="n">
-        <v>2.778</v>
+        <v>2.8065</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3415</v>
+        <v>0.0176</v>
       </c>
       <c r="H13" t="n">
-        <v>2.778</v>
+        <v>4.4022</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8013</v>
+        <v>2.2889</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3415</v>
+        <v>0.0176</v>
       </c>
       <c r="K13" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1428</v>
+        <v>2.3065</v>
       </c>
       <c r="N13" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0357</v>
+        <v>2.8179</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3648</v>
+        <v>1.2668</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7655</v>
+        <v>0.6341</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0357</v>
+        <v>2.8179</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0357</v>
+        <v>2.8179</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0357</v>
+        <v>2.8279</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0697</v>
+        <v>2.8279</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0697</v>
+        <v>2.8279</v>
       </c>
       <c r="N14" t="n">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.695</v>
+        <v>2.813</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2116</v>
+        <v>1.2646</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6298</v>
+        <v>0.6319</v>
       </c>
       <c r="E15" t="n">
-        <v>2.695</v>
+        <v>2.813</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6283</v>
+        <v>2.4928</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0667</v>
+        <v>0.3202</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6283</v>
+        <v>2.4928</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1303</v>
+        <v>2.5954</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0667</v>
+        <v>0.3202</v>
       </c>
       <c r="K15" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L15" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.197</v>
+        <v>2.9156</v>
       </c>
       <c r="N15" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5701</v>
+        <v>2.7294</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1554</v>
+        <v>1.227</v>
       </c>
       <c r="D16" t="n">
-        <v>0.58</v>
+        <v>0.5942</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5701</v>
+        <v>2.7294</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4268</v>
+        <v>3.1163</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9969</v>
+        <v>-0.3869</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4268</v>
+        <v>5.4938</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4268</v>
+        <v>2.8565</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9969</v>
+        <v>-0.3869</v>
       </c>
       <c r="K16" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L16" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5701</v>
+        <v>2.4696</v>
       </c>
       <c r="N16" t="n">
-        <v>334</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5168</v>
+        <v>2.6953</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1315</v>
+        <v>1.2117</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5588</v>
+        <v>0.5788</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5168</v>
+        <v>2.6953</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5168</v>
+        <v>0.1661</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.5292</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5168</v>
+        <v>0.1661</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5168</v>
+        <v>0.1661</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.5292</v>
       </c>
       <c r="K17" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5168</v>
+        <v>2.6953</v>
       </c>
       <c r="N17" t="n">
-        <v>127</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5091</v>
+        <v>2.6254</v>
       </c>
       <c r="C18" t="n">
-        <v>1.128</v>
+        <v>1.1803</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5557</v>
+        <v>0.5472</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5091</v>
+        <v>2.6254</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2096</v>
+        <v>2.3943</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7005</v>
+        <v>0.2311</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2096</v>
+        <v>2.9495</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6015</v>
+        <v>1.5336</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7005</v>
+        <v>0.2311</v>
       </c>
       <c r="K18" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.901</v>
+        <v>1.7647</v>
       </c>
       <c r="N18" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3586</v>
+        <v>2.6144</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0603</v>
+        <v>1.1753</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4958</v>
+        <v>0.5423</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3586</v>
+        <v>2.6144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3298</v>
+        <v>0.7178</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0288</v>
+        <v>1.8966</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3298</v>
+        <v>0.7178</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3298</v>
+        <v>0.7178</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0288</v>
+        <v>1.8966</v>
       </c>
       <c r="K19" t="n">
         <v>133</v>
@@ -1311,7 +1311,7 @@
         <v>200</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3586</v>
+        <v>2.6144</v>
       </c>
       <c r="N19" t="n">
         <v>333</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1689</v>
+        <v>2.5338</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9751</v>
+        <v>1.1391</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4202</v>
+        <v>0.5059</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1689</v>
+        <v>2.5338</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1689</v>
+        <v>3.2672</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1689</v>
+        <v>3.8145</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1689</v>
+        <v>3.9714</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1689</v>
+        <v>3.238</v>
       </c>
       <c r="N20" t="n">
-        <v>127</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0407</v>
+        <v>2.2486</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9174</v>
+        <v>1.0109</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3691</v>
+        <v>0.3771</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0407</v>
+        <v>2.2486</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9659</v>
+        <v>2.3513</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.1027</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9659</v>
+        <v>2.7983</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9659</v>
+        <v>1.455</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.1027</v>
       </c>
       <c r="K21" t="n">
         <v>129</v>
       </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0407</v>
+        <v>1.3523</v>
       </c>
       <c r="N21" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0322</v>
+        <v>2.1965</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9136</v>
+        <v>0.9875</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3657</v>
+        <v>0.3536</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0322</v>
+        <v>2.1965</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0997</v>
+        <v>0.3384</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1319</v>
+        <v>1.8581</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0997</v>
+        <v>0.3384</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0997</v>
+        <v>0.3384</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1319</v>
+        <v>1.8581</v>
       </c>
       <c r="K22" t="n">
         <v>133</v>
@@ -1449,7 +1449,7 @@
         <v>200</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0322</v>
+        <v>2.1965</v>
       </c>
       <c r="N22" t="n">
         <v>333</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9863</v>
+        <v>2.1631</v>
       </c>
       <c r="C23" t="n">
-        <v>0.893</v>
+        <v>0.9725</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3474</v>
+        <v>0.3385</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9863</v>
+        <v>2.1631</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3244</v>
+        <v>2.2731</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3381</v>
+        <v>-0.11</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3244</v>
+        <v>2.2731</v>
       </c>
       <c r="I23" t="n">
-        <v>2.344</v>
+        <v>2.3666</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3381</v>
+        <v>-0.11</v>
       </c>
       <c r="K23" t="n">
         <v>154</v>
@@ -1495,7 +1495,7 @@
         <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0059</v>
+        <v>2.2566</v>
       </c>
       <c r="N23" t="n">
         <v>199</v>
@@ -1504,369 +1504,369 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9034</v>
+        <v>2.1104</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8557</v>
+        <v>0.9488</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3144</v>
+        <v>0.3147</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9034</v>
+        <v>2.1104</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7322</v>
+        <v>2.1104</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1712</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7322</v>
+        <v>2.1104</v>
       </c>
       <c r="I24" t="n">
-        <v>1.404</v>
+        <v>2.1104</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1712</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="L24" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5752</v>
+        <v>2.1104</v>
       </c>
       <c r="N24" t="n">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8329</v>
+        <v>0.9312</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2942</v>
+        <v>0.2971</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8527</v>
+        <v>2.0713</v>
       </c>
       <c r="N25" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7258</v>
+        <v>2.027</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7759</v>
+        <v>0.9113</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2436</v>
+        <v>0.2771</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7258</v>
+        <v>2.027</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7258</v>
+        <v>2.3137</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.2867</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7258</v>
+        <v>2.6657</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7258</v>
+        <v>1.386</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.2867</v>
       </c>
       <c r="K26" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7258</v>
+        <v>1.0993</v>
       </c>
       <c r="N26" t="n">
-        <v>146</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3496</v>
+        <v>2.0235</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6067</v>
+        <v>0.9097</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.2755</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3496</v>
+        <v>2.0235</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3496</v>
+        <v>0.6453</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.3782</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3496</v>
+        <v>0.6453</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3496</v>
+        <v>0.6453</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.3782</v>
       </c>
       <c r="K27" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3496</v>
+        <v>2.0235</v>
       </c>
       <c r="N27" t="n">
-        <v>127</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3257</v>
+        <v>1.9594</v>
       </c>
       <c r="C28" t="n">
-        <v>0.596</v>
+        <v>0.8809</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0842</v>
+        <v>0.2466</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3257</v>
+        <v>1.9594</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2445</v>
+        <v>1.9393</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0812</v>
+        <v>0.0201</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2445</v>
+        <v>1.9393</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2445</v>
+        <v>1.9393</v>
       </c>
       <c r="J28" t="n">
-        <v>1.0812</v>
+        <v>0.0201</v>
       </c>
       <c r="K28" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L28" t="n">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3257</v>
+        <v>1.9594</v>
       </c>
       <c r="N28" t="n">
-        <v>334</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5938</v>
+        <v>0.8672</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0823</v>
+        <v>0.2328</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3209</v>
+        <v>1.929</v>
       </c>
       <c r="N29" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2761</v>
+        <v>1.5432</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5737</v>
+        <v>0.6938</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0645</v>
+        <v>0.0587</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2761</v>
+        <v>1.5432</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6879</v>
+        <v>1.5432</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4118</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6879</v>
+        <v>1.5432</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3681</v>
+        <v>1.5432</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4118</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L30" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9563000000000001</v>
+        <v>1.5432</v>
       </c>
       <c r="N30" t="n">
-        <v>187</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0646</v>
+        <v>1.3972</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4786</v>
+        <v>0.6281</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0198</v>
+        <v>-0.0072</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0646</v>
+        <v>1.3972</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3295</v>
+        <v>1.3972</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2649</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3295</v>
+        <v>1.3972</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0776</v>
+        <v>1.3972</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2649</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="L31" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8126999999999999</v>
+        <v>1.3972</v>
       </c>
       <c r="N31" t="n">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4218</v>
+        <v>0.6278</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0701</v>
+        <v>-0.0076</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9383</v>
+        <v>1.3965</v>
       </c>
       <c r="N32" t="n">
         <v>127</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9018</v>
+        <v>1.2061</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4054</v>
+        <v>0.5422</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.0935</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9018</v>
+        <v>1.2061</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7242</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1776</v>
+        <v>0.4102</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7242</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7242</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1776</v>
+        <v>0.4102</v>
       </c>
       <c r="K33" t="n">
         <v>124</v>
@@ -1955,7 +1955,7 @@
         <v>210</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9017999999999999</v>
+        <v>1.2061</v>
       </c>
       <c r="N33" t="n">
         <v>334</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3393</v>
+        <v>0.5129</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1432</v>
+        <v>-0.123</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7547</v>
+        <v>1.1409</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2010,277 +2010,277 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="C35" t="n">
-        <v>0.256</v>
+        <v>0.3883</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2171</v>
+        <v>-0.2481</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5694</v>
+        <v>0.8637</v>
       </c>
       <c r="N35" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2346</v>
+        <v>0.357</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.236</v>
+        <v>-0.2795</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5218</v>
+        <v>0.7941</v>
       </c>
       <c r="N36" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1817</v>
+        <v>0.3423</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2829</v>
+        <v>-0.2942</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4042</v>
+        <v>0.7615</v>
       </c>
       <c r="N37" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3941</v>
+        <v>0.755</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1772</v>
+        <v>0.3394</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2869</v>
+        <v>-0.2972</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3941</v>
+        <v>0.755</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3941</v>
+        <v>1.3111</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5561</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3941</v>
+        <v>1.3111</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3941</v>
+        <v>1.3111</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5561</v>
       </c>
       <c r="K38" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3941</v>
+        <v>0.7549999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>146</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1511</v>
+        <v>0.306</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.31</v>
+        <v>-0.3308</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3362</v>
+        <v>0.6806</v>
       </c>
       <c r="N39" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3276</v>
+        <v>0.6669</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1473</v>
+        <v>0.2998</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3134</v>
+        <v>-0.3369</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3276</v>
+        <v>0.6669</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1745</v>
+        <v>0.6669</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8469</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1745</v>
+        <v>0.6669</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1745</v>
+        <v>0.6669</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8469</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L40" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3276000000000001</v>
+        <v>0.6669</v>
       </c>
       <c r="N40" t="n">
-        <v>191</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="C41" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.2369</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3827</v>
+        <v>-0.4001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1536</v>
+        <v>0.5269</v>
       </c>
       <c r="N41" t="n">
         <v>126</v>
@@ -2332,93 +2332,93 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0184</v>
+        <v>0.1925</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4276</v>
+        <v>-0.4447</v>
       </c>
       <c r="E42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="F42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="I42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.041</v>
+        <v>0.4281</v>
       </c>
       <c r="N42" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0141</v>
+        <v>0.1923</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4314</v>
+        <v>-0.4449</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0313</v>
+        <v>0.4278</v>
       </c>
       <c r="N43" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0843</v>
+        <v>0.1412</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5187</v>
+        <v>-0.4963</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.1876</v>
+        <v>0.314</v>
       </c>
       <c r="N44" t="n">
         <v>132</v>
@@ -2470,369 +2470,369 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4144</v>
+        <v>0.162</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1863</v>
+        <v>0.0728</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.609</v>
+        <v>-0.5649</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4144</v>
+        <v>0.162</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4144</v>
+        <v>1.0229</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.8609</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4144</v>
+        <v>1.0229</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4144</v>
+        <v>1.0229</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.8609</v>
       </c>
       <c r="K45" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4144</v>
+        <v>0.1619999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4243</v>
+        <v>-0.0209</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1908</v>
+        <v>-0.0094</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.613</v>
+        <v>-0.6474</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4243</v>
+        <v>-0.0209</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5757</v>
+        <v>-0.0209</v>
       </c>
       <c r="G46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5757</v>
+        <v>-0.0209</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5757</v>
+        <v>-0.0209</v>
       </c>
       <c r="J46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L46" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4243</v>
+        <v>-0.0209</v>
       </c>
       <c r="N46" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6313</v>
+        <v>-0.2581</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2838</v>
+        <v>-0.116</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6954</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6313</v>
+        <v>-0.2581</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6313</v>
+        <v>0.2276</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.4857</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6313</v>
+        <v>0.2276</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6313</v>
+        <v>0.237</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.4857</v>
       </c>
       <c r="K47" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6313</v>
+        <v>-0.2487</v>
       </c>
       <c r="N47" t="n">
-        <v>132</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6431</v>
+        <v>-0.4563</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2891</v>
+        <v>-0.2051</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.844</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6431</v>
+        <v>-0.4563</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0242</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.6673</v>
+        <v>-0.3601</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0242</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0244</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.6673</v>
+        <v>-0.3601</v>
       </c>
       <c r="K48" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L48" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6429</v>
+        <v>-0.4563</v>
       </c>
       <c r="N48" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8164</v>
+        <v>-0.462</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.367</v>
+        <v>-0.2077</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7692</v>
+        <v>-0.8466</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.8164</v>
+        <v>-0.462</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1836</v>
+        <v>-0.462</v>
       </c>
       <c r="G49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1836</v>
+        <v>-0.462</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1851</v>
+        <v>-0.462</v>
       </c>
       <c r="J49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="L49" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8149</v>
+        <v>-0.462</v>
       </c>
       <c r="N49" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.9568</v>
+        <v>-0.4915</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4301</v>
+        <v>-0.221</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.8599</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.9568</v>
+        <v>-0.4915</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4152</v>
+        <v>0.4229</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5416</v>
+        <v>-0.9144</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4152</v>
+        <v>0.4229</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4152</v>
+        <v>0.4403</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5416</v>
+        <v>-0.9144</v>
       </c>
       <c r="K50" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L50" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.9568</v>
+        <v>-0.4741</v>
       </c>
       <c r="N50" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4809</v>
+        <v>-0.2437</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8701</v>
+        <v>-0.8827</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-1.0697</v>
+        <v>-0.542</v>
       </c>
       <c r="N51" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0919</v>
+        <v>-0.6706</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4909</v>
+        <v>-0.3015</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8789</v>
+        <v>-0.9408</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.0919</v>
+        <v>-0.6706</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.0919</v>
+        <v>-0.2204</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.4502</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.0919</v>
+        <v>-0.2204</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0919</v>
+        <v>-0.2204</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.4502</v>
       </c>
       <c r="K52" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.0919</v>
+        <v>-0.6706</v>
       </c>
       <c r="N52" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.5646</v>
+        <v>-0.3875</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9443</v>
+        <v>-1.0272</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.2559</v>
+        <v>-0.862</v>
       </c>
       <c r="N53" t="n">
         <v>132</v>
@@ -2884,47 +2884,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.4287</v>
+        <v>-0.9215</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6423</v>
+        <v>-0.4143</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0131</v>
+        <v>-1.054</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.4287</v>
+        <v>-0.9215</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.7238</v>
+        <v>-0.9215</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.7049</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7238</v>
+        <v>-0.9215</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.7238</v>
+        <v>-0.9215</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.7049</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.4287</v>
+        <v>-0.9215</v>
       </c>
       <c r="N54" t="n">
-        <v>191</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.6681</v>
+        <v>-0.4301</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.036</v>
+        <v>-1.0699</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.4861</v>
+        <v>-0.9566</v>
       </c>
       <c r="N55" t="n">
         <v>127</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.4638</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.0616</v>
+        <v>-1.1037</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.5505</v>
+        <v>-1.0316</v>
       </c>
       <c r="N56" t="n">
         <v>132</v>
@@ -3022,231 +3022,231 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.86</v>
+        <v>-0.5696</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.206</v>
+        <v>-1.21</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.913</v>
+        <v>-1.267</v>
       </c>
       <c r="N57" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.8637</v>
+        <v>-0.6269</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2093</v>
+        <v>-1.2676</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.9211</v>
+        <v>-1.3945</v>
       </c>
       <c r="N58" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.9275</v>
+        <v>-0.6605</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2659</v>
+        <v>-1.3012</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.0632</v>
+        <v>-1.4691</v>
       </c>
       <c r="N59" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.0924</v>
+        <v>-0.8223</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.412</v>
+        <v>-1.4637</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.43</v>
+        <v>-1.829</v>
       </c>
       <c r="N60" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.2326</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.5362</v>
+        <v>-1.4726</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.7418</v>
+        <v>-1.8487</v>
       </c>
       <c r="N61" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3349,10 +3349,10 @@
         <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6693</v>
+        <v>0.6121</v>
       </c>
       <c r="J2" t="n">
-        <v>13.386</v>
+        <v>12.242</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6574</v>
+        <v>0.6018</v>
       </c>
       <c r="J3" t="n">
-        <v>13.148</v>
+        <v>12.036</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4802</v>
+        <v>0.4677</v>
       </c>
       <c r="J4" t="n">
-        <v>9.603999999999999</v>
+        <v>9.353999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4127</v>
+        <v>0.4136</v>
       </c>
       <c r="J5" t="n">
-        <v>8.254</v>
+        <v>8.272</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3334</v>
+        <v>0.3455</v>
       </c>
       <c r="J6" t="n">
-        <v>6.668</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4203</v>
+        <v>0.3662</v>
       </c>
       <c r="J7" t="n">
-        <v>8.406000000000001</v>
+        <v>7.324</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3027</v>
+        <v>-0.2299</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.054</v>
+        <v>-4.598</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.74</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3842</v>
+        <v>-0.2667</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.684</v>
+        <v>-5.334</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.62</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5674</v>
+        <v>-0.3791</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.348</v>
+        <v>-7.582</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7625</v>
+        <v>-0.5188</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.25</v>
+        <v>-10.376</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4839</v>
+        <v>0.5716</v>
       </c>
       <c r="J12" t="n">
-        <v>14.517</v>
+        <v>17.148</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3288</v>
+        <v>0.3744</v>
       </c>
       <c r="J13" t="n">
-        <v>9.864000000000001</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1415</v>
+        <v>0.156</v>
       </c>
       <c r="J14" t="n">
-        <v>4.245</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3318</v>
+        <v>-0.2018</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.954000000000001</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3903</v>
+        <v>-0.2425</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.709</v>
+        <v>-7.275</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2045</v>
+        <v>1.1249</v>
       </c>
       <c r="J17" t="n">
-        <v>36.135</v>
+        <v>33.747</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8622</v>
+        <v>0.8446</v>
       </c>
       <c r="J18" t="n">
-        <v>25.866</v>
+        <v>25.338</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.159</v>
+        <v>0.2044</v>
       </c>
       <c r="J19" t="n">
-        <v>4.77</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0282</v>
+        <v>0.0277</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.846</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8703</v>
+        <v>-0.8312</v>
       </c>
       <c r="J21" t="n">
-        <v>-26.109</v>
+        <v>-24.936</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="J22" t="n">
-        <v>16.044</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0954</v>
+        <v>0.1108</v>
       </c>
       <c r="J23" t="n">
-        <v>2.862</v>
+        <v>3.324</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0834</v>
+        <v>-0.0391</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.502</v>
+        <v>-1.173</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1064</v>
+        <v>-0.0533</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.192</v>
+        <v>-1.599</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3023</v>
+        <v>-0.1813</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.069000000000001</v>
+        <v>-5.439</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7785</v>
       </c>
       <c r="J27" t="n">
-        <v>24.027</v>
+        <v>23.355</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.526</v>
+        <v>0.5065</v>
       </c>
       <c r="J28" t="n">
-        <v>15.78</v>
+        <v>15.195</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3063</v>
+        <v>0.3229</v>
       </c>
       <c r="J29" t="n">
-        <v>9.189</v>
+        <v>9.686999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2022</v>
+        <v>0.2378</v>
       </c>
       <c r="J30" t="n">
-        <v>6.066</v>
+        <v>7.134</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4712</v>
+        <v>-0.4066</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.136</v>
+        <v>-12.198</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5748</v>
+        <v>0.5429</v>
       </c>
       <c r="J32" t="n">
-        <v>19.5432</v>
+        <v>18.4586</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3691</v>
+        <v>0.3797</v>
       </c>
       <c r="J33" t="n">
-        <v>12.5494</v>
+        <v>12.9098</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3616</v>
+        <v>-0.2291</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.2944</v>
+        <v>-7.7894</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4486</v>
+        <v>-0.2881</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.2524</v>
+        <v>-9.795400000000001</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6819</v>
+        <v>-0.4569</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.1846</v>
+        <v>-15.5346</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>1.17</v>
+        <v>0.8365</v>
       </c>
       <c r="J37" t="n">
-        <v>39.78</v>
+        <v>28.441</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6249</v>
+        <v>0.5199</v>
       </c>
       <c r="J38" t="n">
-        <v>21.2466</v>
+        <v>17.6766</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4454</v>
+        <v>0.4365</v>
       </c>
       <c r="J39" t="n">
-        <v>15.1436</v>
+        <v>14.841</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4182</v>
+        <v>0.4218</v>
       </c>
       <c r="J40" t="n">
-        <v>14.2188</v>
+        <v>14.3412</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0737</v>
+        <v>0.1464</v>
       </c>
       <c r="J41" t="n">
-        <v>2.5058</v>
+        <v>4.9776</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.6</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7837</v>
+        <v>0.5544</v>
       </c>
       <c r="J42" t="n">
-        <v>17.2414</v>
+        <v>12.1968</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.37</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5099</v>
+        <v>0.4104</v>
       </c>
       <c r="J43" t="n">
-        <v>11.2178</v>
+        <v>9.0288</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4023</v>
+        <v>0.3658</v>
       </c>
       <c r="J44" t="n">
-        <v>8.8506</v>
+        <v>8.047599999999999</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3012</v>
+        <v>0.3071</v>
       </c>
       <c r="J45" t="n">
-        <v>6.6264</v>
+        <v>6.7562</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0597</v>
+        <v>0.0944</v>
       </c>
       <c r="J46" t="n">
-        <v>1.3134</v>
+        <v>2.0768</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>14.8478</v>
+        <v>11.3872</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3747</v>
+        <v>-0.2588</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.243399999999999</v>
+        <v>-5.6936</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.62</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5712</v>
+        <v>-0.381</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.5664</v>
+        <v>-8.382</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6251</v>
+        <v>-0.4184</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.7522</v>
+        <v>-9.204800000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6899</v>
+        <v>-0.4649</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.1778</v>
+        <v>-10.2278</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.27</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5001</v>
+        <v>0.483</v>
       </c>
       <c r="J52" t="n">
-        <v>14.5029</v>
+        <v>14.007</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1488</v>
+        <v>-0.0946</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.3152</v>
+        <v>-2.7434</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1692</v>
+        <v>-0.1059</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.9068</v>
+        <v>-3.0711</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3392</v>
+        <v>-0.2122</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.8368</v>
+        <v>-6.1538</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.78</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3986</v>
+        <v>-0.2522</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.5594</v>
+        <v>-7.3138</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9079</v>
+        <v>0.6672</v>
       </c>
       <c r="J57" t="n">
-        <v>26.3291</v>
+        <v>19.3488</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6223</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>18.0467</v>
+        <v>14.5145</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6223</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>18.0467</v>
+        <v>14.5145</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1682</v>
+        <v>0.2255</v>
       </c>
       <c r="J60" t="n">
-        <v>4.8778</v>
+        <v>6.5395</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3756</v>
+        <v>-0.3026</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.8924</v>
+        <v>-8.775399999999999</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3581</v>
+        <v>0.373</v>
       </c>
       <c r="J62" t="n">
-        <v>10.743</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1952</v>
+        <v>0.1968</v>
       </c>
       <c r="J63" t="n">
-        <v>5.856</v>
+        <v>5.904</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0038</v>
+        <v>-0.0164</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.114</v>
+        <v>-0.492</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3996</v>
+        <v>-0.2527</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.988</v>
+        <v>-7.581</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4697</v>
+        <v>-0.3015</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.091</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4479</v>
+        <v>1.0126</v>
       </c>
       <c r="J67" t="n">
-        <v>43.437</v>
+        <v>30.378</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6309</v>
+        <v>0.4951</v>
       </c>
       <c r="J68" t="n">
-        <v>18.927</v>
+        <v>14.853</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2022</v>
+        <v>0.2378</v>
       </c>
       <c r="J69" t="n">
-        <v>6.066</v>
+        <v>7.134</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3851</v>
+        <v>-0.3187</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.553</v>
+        <v>-9.561</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8892</v>
+        <v>-0.8524</v>
       </c>
       <c r="J71" t="n">
-        <v>-26.676</v>
+        <v>-25.572</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="J72" t="n">
-        <v>1.974</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0122</v>
+        <v>-0.034</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.3416</v>
+        <v>-0.952</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1869</v>
+        <v>-0.1419</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.2332</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4601</v>
+        <v>-0.2995</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.8828</v>
+        <v>-8.385999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4601</v>
+        <v>-0.2995</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.8828</v>
+        <v>-8.385999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7702</v>
+        <v>0.5849</v>
       </c>
       <c r="J77" t="n">
-        <v>21.5656</v>
+        <v>16.3772</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.673</v>
+        <v>0.5289</v>
       </c>
       <c r="J78" t="n">
-        <v>18.844</v>
+        <v>14.8092</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4132</v>
+        <v>0.3995</v>
       </c>
       <c r="J79" t="n">
-        <v>11.5696</v>
+        <v>11.186</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2604</v>
+        <v>0.3121</v>
       </c>
       <c r="J80" t="n">
-        <v>7.2912</v>
+        <v>8.738799999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0469</v>
+        <v>0.0175</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.3132</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.325</v>
+        <v>0.3452</v>
       </c>
       <c r="J82" t="n">
-        <v>8.125</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3094</v>
+        <v>0.3306</v>
       </c>
       <c r="J83" t="n">
-        <v>7.735</v>
+        <v>8.265000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2645</v>
+        <v>-0.1676</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.6125</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4476</v>
+        <v>-0.2876</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.19</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5026</v>
+        <v>-0.326</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.565</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.5132</v>
+        <v>1.0569</v>
       </c>
       <c r="J87" t="n">
-        <v>37.83</v>
+        <v>26.4225</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3526</v>
+        <v>0.3572</v>
       </c>
       <c r="J88" t="n">
-        <v>8.815</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2308</v>
+        <v>-0.1618</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.77</v>
+        <v>-4.045</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2998</v>
+        <v>-0.2301</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.495</v>
+        <v>-5.7525</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.332</v>
+        <v>-0.2624</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0321</v>
+        <v>-0.0104</v>
       </c>
       <c r="J92" t="n">
-        <v>0.642</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4028</v>
+        <v>-0.3181</v>
       </c>
       <c r="J93" t="n">
-        <v>-8.055999999999999</v>
+        <v>-6.362</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.52</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.6484</v>
+        <v>-0.4458</v>
       </c>
       <c r="J94" t="n">
-        <v>-12.968</v>
+        <v>-8.916</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.51</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6631</v>
+        <v>-0.4552</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.262</v>
+        <v>-9.103999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8527</v>
+        <v>-0.5884</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.054</v>
+        <v>-11.768</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7154</v>
+        <v>1.2162</v>
       </c>
       <c r="J97" t="n">
-        <v>34.308</v>
+        <v>24.324</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.6</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2629</v>
+        <v>0.9325</v>
       </c>
       <c r="J98" t="n">
-        <v>25.258</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I99" t="n">
-        <v>0.901</v>
+        <v>0.7466</v>
       </c>
       <c r="J99" t="n">
-        <v>18.02</v>
+        <v>14.932</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.4</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8163</v>
+        <v>0.697</v>
       </c>
       <c r="J100" t="n">
-        <v>16.326</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7315</v>
+        <v>0.6462</v>
       </c>
       <c r="J101" t="n">
-        <v>14.63</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5724</v>
+        <v>0.4418</v>
       </c>
       <c r="J102" t="n">
-        <v>12.5928</v>
+        <v>9.7196</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5077</v>
+        <v>0.4101</v>
       </c>
       <c r="J103" t="n">
-        <v>11.1694</v>
+        <v>9.0222</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.34</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4658</v>
+        <v>0.3909</v>
       </c>
       <c r="J104" t="n">
-        <v>10.2476</v>
+        <v>8.5998</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4507</v>
+        <v>0.3846</v>
       </c>
       <c r="J105" t="n">
-        <v>9.9154</v>
+        <v>8.4612</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1696</v>
+        <v>0.1932</v>
       </c>
       <c r="J106" t="n">
-        <v>3.7312</v>
+        <v>4.2504</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0914</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.0746</v>
+        <v>-2.0108</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0914</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.0746</v>
+        <v>-2.0108</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2378</v>
+        <v>-0.1788</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.2316</v>
+        <v>-3.9336</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3711</v>
+        <v>-0.2462</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.164199999999999</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5462</v>
+        <v>-0.3607</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.0164</v>
+        <v>-7.9354</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>0.86</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0944</v>
+        <v>-0.1044</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.9824</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2839</v>
+        <v>-0.2395</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.9619</v>
+        <v>-5.0295</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5768</v>
+        <v>-0.4014</v>
       </c>
       <c r="J114" t="n">
-        <v>-12.1128</v>
+        <v>-8.429399999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5927</v>
+        <v>-0.4106</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.4467</v>
+        <v>-8.6226</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.31</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.93</v>
+        <v>-0.6476</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.53</v>
+        <v>-13.5996</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.87</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7397</v>
+        <v>1.2382</v>
       </c>
       <c r="J117" t="n">
-        <v>36.5337</v>
+        <v>26.0022</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2618</v>
+        <v>0.9323</v>
       </c>
       <c r="J118" t="n">
-        <v>26.4978</v>
+        <v>19.5783</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>1.131</v>
+        <v>0.8638</v>
       </c>
       <c r="J119" t="n">
-        <v>23.751</v>
+        <v>18.1398</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>1.35</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7095</v>
+        <v>0.6331</v>
       </c>
       <c r="J120" t="n">
-        <v>14.8995</v>
+        <v>13.2951</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6019</v>
+        <v>0.5672</v>
       </c>
       <c r="J121" t="n">
-        <v>12.6399</v>
+        <v>11.9112</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3385</v>
+        <v>-0.2856</v>
       </c>
       <c r="J122" t="n">
-        <v>-6.4315</v>
+        <v>-5.4264</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4306</v>
+        <v>-0.3496</v>
       </c>
       <c r="J123" t="n">
-        <v>-8.1814</v>
+        <v>-6.6424</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>0.46</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.6846</v>
+        <v>-0.4814</v>
       </c>
       <c r="J124" t="n">
-        <v>-13.0074</v>
+        <v>-9.146599999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.43</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7326</v>
+        <v>-0.5098</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.9194</v>
+        <v>-9.686199999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8629</v>
+        <v>-0.5979</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.3951</v>
+        <v>-11.3601</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.96</v>
       </c>
       <c r="I127" t="n">
-        <v>1.814</v>
+        <v>1.3258</v>
       </c>
       <c r="J127" t="n">
-        <v>34.466</v>
+        <v>25.1902</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.7215</v>
+        <v>1.227</v>
       </c>
       <c r="J128" t="n">
-        <v>32.7085</v>
+        <v>23.313</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I129" t="n">
-        <v>1.5025</v>
+        <v>1.0829</v>
       </c>
       <c r="J129" t="n">
-        <v>28.5475</v>
+        <v>20.5751</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.38</v>
       </c>
       <c r="I130" t="n">
-        <v>0.7513</v>
+        <v>0.6643</v>
       </c>
       <c r="J130" t="n">
-        <v>14.2747</v>
+        <v>12.6217</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0549</v>
+        <v>0.0343</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.0431</v>
+        <v>0.6516999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8066</v>
+        <v>1.0009</v>
       </c>
       <c r="J132" t="n">
-        <v>22.5848</v>
+        <v>28.0252</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3516</v>
+        <v>0.3992</v>
       </c>
       <c r="J133" t="n">
-        <v>9.844799999999999</v>
+        <v>11.1776</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.99</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0453</v>
+        <v>-0.0211</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.2684</v>
+        <v>-0.5908</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5346</v>
+        <v>-0.3466</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.9688</v>
+        <v>-9.704800000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5979</v>
+        <v>-0.3933</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.7412</v>
+        <v>-11.0124</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8516</v>
+        <v>0.8295</v>
       </c>
       <c r="J137" t="n">
-        <v>23.8448</v>
+        <v>23.226</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6858</v>
+        <v>0.6597</v>
       </c>
       <c r="J138" t="n">
-        <v>19.2024</v>
+        <v>18.4716</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3217</v>
+        <v>0.3238</v>
       </c>
       <c r="J139" t="n">
-        <v>9.0076</v>
+        <v>9.0664</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3202</v>
+        <v>-0.2548</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.9656</v>
+        <v>-7.1344</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4401</v>
+        <v>-0.3756</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.3228</v>
+        <v>-10.5168</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1433</v>
+        <v>1.1095</v>
       </c>
       <c r="J142" t="n">
-        <v>28.5825</v>
+        <v>27.7375</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9721</v>
+        <v>1.0043</v>
       </c>
       <c r="J143" t="n">
-        <v>24.3025</v>
+        <v>25.1075</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9495</v>
+        <v>0.988</v>
       </c>
       <c r="J144" t="n">
-        <v>23.7375</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6685</v>
+        <v>0.7632</v>
       </c>
       <c r="J145" t="n">
-        <v>16.7125</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.18</v>
       </c>
       <c r="I146" t="n">
-        <v>0.3811</v>
+        <v>0.4783</v>
       </c>
       <c r="J146" t="n">
-        <v>9.5275</v>
+        <v>11.9575</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0053</v>
+        <v>-0.0376</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.1325</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0053</v>
+        <v>-0.0376</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.1325</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3164</v>
+        <v>-0.2387</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.91</v>
+        <v>-5.9675</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6465</v>
+        <v>-0.4343</v>
       </c>
       <c r="J150" t="n">
-        <v>-16.1625</v>
+        <v>-10.8575</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.51</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7111</v>
+        <v>-0.4809</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.7775</v>
+        <v>-12.0225</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3221</v>
+        <v>0.3449</v>
       </c>
       <c r="J152" t="n">
-        <v>7.4083</v>
+        <v>7.9327</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2726</v>
+        <v>0.2804</v>
       </c>
       <c r="J153" t="n">
-        <v>6.2698</v>
+        <v>6.4492</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4103</v>
+        <v>-0.2682</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.4369</v>
+        <v>-6.1686</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5381</v>
+        <v>-0.3541</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.3763</v>
+        <v>-8.144299999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6428</v>
+        <v>-0.4289</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.7844</v>
+        <v>-9.864699999999999</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.6</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3536</v>
+        <v>1.2359</v>
       </c>
       <c r="J157" t="n">
-        <v>31.1328</v>
+        <v>28.4257</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.44</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0306</v>
+        <v>1.0378</v>
       </c>
       <c r="J158" t="n">
-        <v>23.7038</v>
+        <v>23.8694</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8484</v>
+        <v>0.8963</v>
       </c>
       <c r="J159" t="n">
-        <v>19.5132</v>
+        <v>20.6149</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6539</v>
       </c>
       <c r="J160" t="n">
-        <v>12.926</v>
+        <v>15.0397</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0304</v>
+        <v>0.0521</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.6992</v>
+        <v>1.1983</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5917</v>
+        <v>1.3842</v>
       </c>
       <c r="J162" t="n">
-        <v>42.9759</v>
+        <v>37.3734</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6424</v>
       </c>
       <c r="J163" t="n">
-        <v>17.5959</v>
+        <v>17.3448</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4234</v>
+        <v>0.4458</v>
       </c>
       <c r="J164" t="n">
-        <v>11.4318</v>
+        <v>12.0366</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5936</v>
+        <v>-0.5306</v>
       </c>
       <c r="J165" t="n">
-        <v>-16.0272</v>
+        <v>-14.3262</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.84</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.619</v>
+        <v>-0.5575</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.713</v>
+        <v>-15.0525</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6217</v>
+        <v>0.7538</v>
       </c>
       <c r="J167" t="n">
-        <v>16.7859</v>
+        <v>20.3526</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0409</v>
+        <v>0.0133</v>
       </c>
       <c r="J168" t="n">
-        <v>1.1043</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4087</v>
+        <v>-0.2601</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.0349</v>
+        <v>-7.0227</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.77</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4087</v>
+        <v>-0.2601</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.0349</v>
+        <v>-7.0227</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4512</v>
+        <v>-0.2893</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.1824</v>
+        <v>-7.8111</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2363</v>
+        <v>1.1513</v>
       </c>
       <c r="J172" t="n">
-        <v>32.1438</v>
+        <v>29.9338</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6349</v>
+        <v>0.6516</v>
       </c>
       <c r="J173" t="n">
-        <v>16.5074</v>
+        <v>16.9416</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4817</v>
+        <v>0.5347</v>
       </c>
       <c r="J174" t="n">
-        <v>12.5242</v>
+        <v>13.9022</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1105</v>
+        <v>0.1812</v>
       </c>
       <c r="J175" t="n">
-        <v>2.873</v>
+        <v>4.7112</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1105</v>
+        <v>0.1812</v>
       </c>
       <c r="J176" t="n">
-        <v>2.873</v>
+        <v>4.7112</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3294</v>
+        <v>0.3628</v>
       </c>
       <c r="J177" t="n">
-        <v>8.564399999999999</v>
+        <v>9.4328</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2822</v>
+        <v>0.3032</v>
       </c>
       <c r="J178" t="n">
-        <v>7.3372</v>
+        <v>7.8832</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1968</v>
+        <v>0.198</v>
       </c>
       <c r="J179" t="n">
-        <v>5.1168</v>
+        <v>5.148</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2923</v>
+        <v>-0.1814</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.5998</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.53</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7218</v>
+        <v>-0.487</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.7668</v>
+        <v>-12.662</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2694</v>
+        <v>0.2768</v>
       </c>
       <c r="J182" t="n">
-        <v>6.4656</v>
+        <v>6.6432</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1997</v>
+        <v>-0.1513</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.7928</v>
+        <v>-3.6312</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2646</v>
+        <v>-0.1811</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.3504</v>
+        <v>-4.3464</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2837</v>
+        <v>-0.1909</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.8088</v>
+        <v>-4.5816</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6061</v>
+        <v>-0.4021</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.5464</v>
+        <v>-9.650399999999999</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4297</v>
+        <v>1.2813</v>
       </c>
       <c r="J187" t="n">
-        <v>34.3128</v>
+        <v>30.7512</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.4</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.983</v>
       </c>
       <c r="J188" t="n">
-        <v>23.1888</v>
+        <v>23.592</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4337</v>
+        <v>0.5182</v>
       </c>
       <c r="J189" t="n">
-        <v>10.4088</v>
+        <v>12.4368</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4084</v>
+        <v>0.4932</v>
       </c>
       <c r="J190" t="n">
-        <v>9.801600000000001</v>
+        <v>11.8368</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1105</v>
+        <v>0.1924</v>
       </c>
       <c r="J191" t="n">
-        <v>2.652</v>
+        <v>4.6176</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4566</v>
+        <v>0.5292</v>
       </c>
       <c r="J192" t="n">
-        <v>11.8716</v>
+        <v>13.7592</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2116</v>
+        <v>0.2174</v>
       </c>
       <c r="J193" t="n">
-        <v>5.5016</v>
+        <v>5.6524</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1323</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.4398</v>
+        <v>-2.1736</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3715</v>
+        <v>-0.2333</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.659000000000001</v>
+        <v>-6.0658</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5109</v>
+        <v>-0.3307</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.2834</v>
+        <v>-8.5982</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1266</v>
+        <v>1.0741</v>
       </c>
       <c r="J197" t="n">
-        <v>29.2916</v>
+        <v>27.9266</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.26</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7503</v>
+        <v>0.7281</v>
       </c>
       <c r="J198" t="n">
-        <v>19.5078</v>
+        <v>18.9306</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4942</v>
+        <v>0.4793</v>
       </c>
       <c r="J199" t="n">
-        <v>12.8492</v>
+        <v>12.4618</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5009</v>
+        <v>-0.4365</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.0234</v>
+        <v>-11.349</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6807</v>
+        <v>-0.6259</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.6982</v>
+        <v>-16.2734</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.45</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1388</v>
+        <v>1.0856</v>
       </c>
       <c r="J202" t="n">
-        <v>30.7476</v>
+        <v>29.3112</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9697</v>
+        <v>0.961</v>
       </c>
       <c r="J203" t="n">
-        <v>26.1819</v>
+        <v>25.947</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5636</v>
+        <v>0.5662</v>
       </c>
       <c r="J204" t="n">
-        <v>15.2172</v>
+        <v>15.2874</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.465</v>
+        <v>-0.3943</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.555</v>
+        <v>-10.6461</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.465</v>
+        <v>-0.3943</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.555</v>
+        <v>-10.6461</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6591</v>
+        <v>0.8076</v>
       </c>
       <c r="J207" t="n">
-        <v>17.7957</v>
+        <v>21.8052</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.4516</v>
+        <v>-2.1195</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1508</v>
+        <v>-0.1132</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.0716</v>
+        <v>-3.0564</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.64</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5773</v>
+        <v>-0.38</v>
       </c>
       <c r="J210" t="n">
-        <v>-15.5871</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6283</v>
+        <v>-0.4173</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.9641</v>
+        <v>-11.2671</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.77</v>
       </c>
       <c r="I212" t="n">
-        <v>1.5972</v>
+        <v>1.4046</v>
       </c>
       <c r="J212" t="n">
-        <v>33.5412</v>
+        <v>29.4966</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1741</v>
+        <v>1.1515</v>
       </c>
       <c r="J213" t="n">
-        <v>24.6561</v>
+        <v>24.1815</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.0333</v>
       </c>
       <c r="J214" t="n">
-        <v>19.656</v>
+        <v>21.6993</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.43</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8923</v>
+        <v>1.0041</v>
       </c>
       <c r="J215" t="n">
-        <v>18.7383</v>
+        <v>21.0861</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I216" t="n">
-        <v>0.6332</v>
+        <v>0.7584</v>
       </c>
       <c r="J216" t="n">
-        <v>13.2972</v>
+        <v>15.9264</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.3178</v>
+        <v>-0.2546</v>
       </c>
       <c r="J217" t="n">
-        <v>-6.6738</v>
+        <v>-5.3466</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.35</v>
+        <v>-0.2743</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.35</v>
+        <v>-5.7603</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4391</v>
+        <v>-0.3207</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.2211</v>
+        <v>-6.7347</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.62</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5319</v>
+        <v>-0.3654</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.1699</v>
+        <v>-7.6734</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5774</v>
+        <v>-0.3932</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.1254</v>
+        <v>-8.257199999999999</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5645</v>
+        <v>0.6805</v>
       </c>
       <c r="J222" t="n">
-        <v>16.935</v>
+        <v>20.415</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.07</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1453</v>
+        <v>0.1729</v>
       </c>
       <c r="J223" t="n">
-        <v>4.359</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1213</v>
+        <v>0.1521</v>
       </c>
       <c r="J224" t="n">
-        <v>3.639</v>
+        <v>4.563</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2281</v>
+        <v>-0.1296</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.843</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2281</v>
+        <v>-0.1296</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.843</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6798</v>
+        <v>0.6563</v>
       </c>
       <c r="J227" t="n">
-        <v>20.394</v>
+        <v>19.689</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.22</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6549</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>19.647</v>
+        <v>18.948</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2678</v>
+        <v>0.2952</v>
       </c>
       <c r="J229" t="n">
-        <v>8.034000000000001</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0214</v>
+        <v>0.0716</v>
       </c>
       <c r="J230" t="n">
-        <v>0.642</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2584</v>
+        <v>-0.1919</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.752</v>
+        <v>-5.757</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1167</v>
+        <v>0.1034</v>
       </c>
       <c r="J232" t="n">
-        <v>3.0342</v>
+        <v>2.6884</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0533</v>
+        <v>-0.046</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.3858</v>
+        <v>-1.196</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.328</v>
+        <v>-2.1632</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1895</v>
+        <v>-0.1173</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.927</v>
+        <v>-3.0498</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2433</v>
+        <v>-0.15</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.3258</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1442</v>
+        <v>1.0914</v>
       </c>
       <c r="J237" t="n">
-        <v>29.7492</v>
+        <v>28.3764</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.43</v>
       </c>
       <c r="I238" t="n">
-        <v>1.082</v>
+        <v>1.0519</v>
       </c>
       <c r="J238" t="n">
-        <v>28.132</v>
+        <v>27.3494</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.41</v>
       </c>
       <c r="I239" t="n">
-        <v>1.0399</v>
+        <v>1.0229</v>
       </c>
       <c r="J239" t="n">
-        <v>27.0374</v>
+        <v>26.5954</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.08</v>
       </c>
       <c r="I240" t="n">
-        <v>0.18</v>
+        <v>0.2463</v>
       </c>
       <c r="J240" t="n">
-        <v>4.68</v>
+        <v>6.4038</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.59</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.1832</v>
+        <v>-1.1834</v>
       </c>
       <c r="J241" t="n">
-        <v>-30.7632</v>
+        <v>-30.7684</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0441</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.8379</v>
+        <v>-1.1932</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.5</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.6355</v>
+        <v>-0.45</v>
       </c>
       <c r="J243" t="n">
-        <v>-12.0745</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.47</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.6852</v>
+        <v>-0.4777</v>
       </c>
       <c r="J244" t="n">
-        <v>-13.0188</v>
+        <v>-9.0763</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.46</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.7008</v>
+        <v>-0.4871</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.3152</v>
+        <v>-9.254899999999999</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.33</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8847</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.8093</v>
+        <v>-11.6546</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.92</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8288</v>
+        <v>1.5592</v>
       </c>
       <c r="J247" t="n">
-        <v>34.7472</v>
+        <v>29.6248</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3189</v>
+        <v>1.2468</v>
       </c>
       <c r="J248" t="n">
-        <v>25.0591</v>
+        <v>23.6892</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.2985</v>
+        <v>1.2355</v>
       </c>
       <c r="J249" t="n">
-        <v>24.6715</v>
+        <v>23.4745</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.55</v>
       </c>
       <c r="I250" t="n">
-        <v>1.1119</v>
+        <v>1.146</v>
       </c>
       <c r="J250" t="n">
-        <v>21.1261</v>
+        <v>21.774</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.2483</v>
+        <v>0.3568</v>
       </c>
       <c r="J251" t="n">
-        <v>4.7177</v>
+        <v>6.7792</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.36</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6474</v>
+        <v>0.7929</v>
       </c>
       <c r="J252" t="n">
-        <v>15.5376</v>
+        <v>19.0296</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.361</v>
+        <v>0.3972</v>
       </c>
       <c r="J253" t="n">
-        <v>8.664</v>
+        <v>9.5328</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.5026</v>
+        <v>-0.3284</v>
       </c>
       <c r="J254" t="n">
-        <v>-12.0624</v>
+        <v>-7.8816</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.4499</v>
       </c>
       <c r="J255" t="n">
-        <v>-16.1256</v>
+        <v>-10.7976</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6966</v>
+        <v>-0.4683</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.7184</v>
+        <v>-11.2392</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.66</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4978</v>
+        <v>1.3242</v>
       </c>
       <c r="J257" t="n">
-        <v>35.9472</v>
+        <v>31.7808</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.4</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9801</v>
+        <v>0.9886</v>
       </c>
       <c r="J258" t="n">
-        <v>23.5224</v>
+        <v>23.7264</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.27</v>
       </c>
       <c r="I259" t="n">
-        <v>0.6662</v>
+        <v>0.7111</v>
       </c>
       <c r="J259" t="n">
-        <v>15.9888</v>
+        <v>17.0664</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.04</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0248</v>
+        <v>0.1027</v>
       </c>
       <c r="J260" t="n">
-        <v>0.5952</v>
+        <v>2.4648</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2825</v>
+        <v>-0.1987</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.78</v>
+        <v>-4.7688</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6405</v>
+        <v>1.4175</v>
       </c>
       <c r="J262" t="n">
-        <v>47.5745</v>
+        <v>41.1075</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7187</v>
+        <v>0.7108</v>
       </c>
       <c r="J263" t="n">
-        <v>20.8423</v>
+        <v>20.6132</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6182</v>
+        <v>0.6151</v>
       </c>
       <c r="J264" t="n">
-        <v>17.9278</v>
+        <v>17.8379</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5455</v>
+        <v>-0.4788</v>
       </c>
       <c r="J265" t="n">
-        <v>-15.8195</v>
+        <v>-13.8852</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8365</v>
+        <v>-0.7929</v>
       </c>
       <c r="J266" t="n">
-        <v>-24.2585</v>
+        <v>-22.9941</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4173</v>
+        <v>0.4742</v>
       </c>
       <c r="J267" t="n">
-        <v>12.1017</v>
+        <v>13.7518</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1542</v>
+        <v>0.1398</v>
       </c>
       <c r="J268" t="n">
-        <v>4.4718</v>
+        <v>4.0542</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2063</v>
+        <v>-0.1352</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.9827</v>
+        <v>-3.9208</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.72</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4734</v>
+        <v>-0.3058</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.7286</v>
+        <v>-8.8682</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5275</v>
+        <v>-0.3439</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.2975</v>
+        <v>-9.973100000000001</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4912</v>
+        <v>0.5829</v>
       </c>
       <c r="J272" t="n">
-        <v>17.6832</v>
+        <v>20.9844</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.27</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4646</v>
+        <v>0.5483</v>
       </c>
       <c r="J273" t="n">
-        <v>16.7256</v>
+        <v>19.7388</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0074</v>
+        <v>0.0315</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2664</v>
+        <v>1.134</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2076</v>
+        <v>-0.1169</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.4736</v>
+        <v>-4.2084</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.75</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4628</v>
+        <v>-0.2937</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.6608</v>
+        <v>-10.5732</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5135</v>
       </c>
       <c r="J277" t="n">
-        <v>19.5048</v>
+        <v>18.486</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5148</v>
+        <v>0.4876</v>
       </c>
       <c r="J278" t="n">
-        <v>18.5328</v>
+        <v>17.5536</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3383</v>
+        <v>0.3267</v>
       </c>
       <c r="J279" t="n">
-        <v>12.1788</v>
+        <v>11.7612</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0677</v>
+        <v>-0.0173</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.4372</v>
+        <v>-0.6228</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2462</v>
+        <v>-0.1849</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.863200000000001</v>
+        <v>-6.6564</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8295</v>
+        <v>1.0242</v>
       </c>
       <c r="J282" t="n">
-        <v>29.862</v>
+        <v>36.8712</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2944</v>
+        <v>0.3344</v>
       </c>
       <c r="J283" t="n">
-        <v>10.5984</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.05</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1147</v>
+        <v>0.1326</v>
       </c>
       <c r="J284" t="n">
-        <v>4.1292</v>
+        <v>4.7736</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4204</v>
+        <v>-0.2635</v>
       </c>
       <c r="J285" t="n">
-        <v>-15.1344</v>
+        <v>-9.486000000000001</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5903</v>
+        <v>-0.3874</v>
       </c>
       <c r="J286" t="n">
-        <v>-21.2508</v>
+        <v>-13.9464</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.4</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0897</v>
+        <v>1.047</v>
       </c>
       <c r="J287" t="n">
-        <v>39.2292</v>
+        <v>37.692</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9159</v>
+        <v>0.8921</v>
       </c>
       <c r="J288" t="n">
-        <v>32.9724</v>
+        <v>32.1156</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0567</v>
+        <v>-0.0127</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.0412</v>
+        <v>-0.4572</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3361</v>
+        <v>-0.2766</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.0996</v>
+        <v>-9.957599999999999</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.65</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.0321</v>
+        <v>-1.0118</v>
       </c>
       <c r="J291" t="n">
-        <v>-37.1556</v>
+        <v>-36.4248</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2966</v>
+        <v>0.3359</v>
       </c>
       <c r="J292" t="n">
-        <v>10.0844</v>
+        <v>11.4206</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1593</v>
+        <v>0.1768</v>
       </c>
       <c r="J293" t="n">
-        <v>5.4162</v>
+        <v>6.0112</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.022</v>
+        <v>-0.0025</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.748</v>
+        <v>-0.08500000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0576</v>
+        <v>-0.0234</v>
       </c>
       <c r="J295" t="n">
-        <v>-1.9584</v>
+        <v>-0.7956</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1277</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.3418</v>
+        <v>-2.2644</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.41</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1197</v>
+        <v>1.0665</v>
       </c>
       <c r="J297" t="n">
-        <v>38.0698</v>
+        <v>36.261</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.1</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3657</v>
+        <v>0.335</v>
       </c>
       <c r="J298" t="n">
-        <v>12.4338</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.07</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2687</v>
+        <v>0.248</v>
       </c>
       <c r="J299" t="n">
-        <v>9.1358</v>
+        <v>8.432</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1072</v>
+        <v>-0.0633</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.6448</v>
+        <v>-2.1522</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0281</v>
+        <v>-1.0077</v>
       </c>
       <c r="J301" t="n">
-        <v>-34.9554</v>
+        <v>-34.2618</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.81</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7964</v>
+        <v>1.5244</v>
       </c>
       <c r="J302" t="n">
-        <v>44.91</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7147</v>
+        <v>0.7222</v>
       </c>
       <c r="J303" t="n">
-        <v>17.8675</v>
+        <v>18.055</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6642</v>
+        <v>0.6757</v>
       </c>
       <c r="J304" t="n">
-        <v>16.605</v>
+        <v>16.8925</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5058</v>
+        <v>-0.4342</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.645</v>
+        <v>-10.855</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.625</v>
       </c>
       <c r="J306" t="n">
-        <v>-17.1</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1101</v>
+        <v>0.0781</v>
       </c>
       <c r="J307" t="n">
-        <v>2.7525</v>
+        <v>1.9525</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.007</v>
+        <v>-0.0318</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.175</v>
+        <v>-0.795</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2824</v>
+        <v>-0.1907</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.06</v>
+        <v>-4.7675</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4564</v>
+        <v>-0.2979</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.41</v>
+        <v>-7.4475</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4848</v>
+        <v>-0.317</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.12</v>
+        <v>-7.925</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3</v>
+        <v>0.3309</v>
       </c>
       <c r="J312" t="n">
-        <v>10.2</v>
+        <v>11.2506</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2516</v>
+        <v>0.2714</v>
       </c>
       <c r="J313" t="n">
-        <v>8.554399999999999</v>
+        <v>9.227600000000001</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1817</v>
+        <v>0.1878</v>
       </c>
       <c r="J314" t="n">
-        <v>6.1778</v>
+        <v>6.3852</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.99</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.023</v>
+        <v>-0.0195</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.782</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6432</v>
+        <v>-0.4273</v>
       </c>
       <c r="J316" t="n">
-        <v>-21.8688</v>
+        <v>-14.5282</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6848</v>
+        <v>0.6495</v>
       </c>
       <c r="J317" t="n">
-        <v>23.2832</v>
+        <v>22.083</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.21</v>
       </c>
       <c r="I318" t="n">
-        <v>0.66</v>
+        <v>0.6243</v>
       </c>
       <c r="J318" t="n">
-        <v>22.44</v>
+        <v>21.2262</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1351</v>
+        <v>0.154</v>
       </c>
       <c r="J319" t="n">
-        <v>4.5934</v>
+        <v>5.236</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0528</v>
+        <v>-0.0112</v>
       </c>
       <c r="J320" t="n">
-        <v>-1.7952</v>
+        <v>-0.3808</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6876</v>
+        <v>-0.637</v>
       </c>
       <c r="J321" t="n">
-        <v>-23.3784</v>
+        <v>-21.658</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0362</v>
+        <v>-0.0612</v>
       </c>
       <c r="J322" t="n">
-        <v>-0.7964</v>
+        <v>-1.3464</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2843</v>
+        <v>-0.2298</v>
       </c>
       <c r="J323" t="n">
-        <v>-6.2546</v>
+        <v>-5.0556</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>0.68</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.4483</v>
+        <v>-0.3144</v>
       </c>
       <c r="J324" t="n">
-        <v>-9.8626</v>
+        <v>-6.9168</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.64</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.5143</v>
+        <v>-0.351</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.3146</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.46</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7618</v>
+        <v>-0.5192</v>
       </c>
       <c r="J326" t="n">
-        <v>-16.7596</v>
+        <v>-11.4224</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.87</v>
       </c>
       <c r="I327" t="n">
-        <v>1.8061</v>
+        <v>1.535</v>
       </c>
       <c r="J327" t="n">
-        <v>39.7342</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.7</v>
       </c>
       <c r="I328" t="n">
-        <v>1.5043</v>
+        <v>1.3386</v>
       </c>
       <c r="J328" t="n">
-        <v>33.0946</v>
+        <v>29.4492</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0265</v>
+        <v>1.0531</v>
       </c>
       <c r="J329" t="n">
-        <v>22.583</v>
+        <v>23.1682</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.3127</v>
+        <v>0.4146</v>
       </c>
       <c r="J330" t="n">
-        <v>6.8794</v>
+        <v>9.1212</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.91</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5014</v>
+        <v>-0.4232</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.0308</v>
+        <v>-9.3104</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.61</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4266</v>
+        <v>1.2752</v>
       </c>
       <c r="J332" t="n">
-        <v>37.0916</v>
+        <v>33.1552</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.38</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9619</v>
+        <v>0.9638</v>
       </c>
       <c r="J333" t="n">
-        <v>25.0094</v>
+        <v>25.0588</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.448</v>
+        <v>0.5088</v>
       </c>
       <c r="J334" t="n">
-        <v>11.648</v>
+        <v>13.2288</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.97</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2677</v>
+        <v>-0.187</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.9602</v>
+        <v>-4.862</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3022</v>
+        <v>-0.222</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.8572</v>
+        <v>-5.772</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3041</v>
+        <v>0.3245</v>
       </c>
       <c r="J337" t="n">
-        <v>7.9066</v>
+        <v>8.436999999999999</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1622</v>
+        <v>0.1464</v>
       </c>
       <c r="J338" t="n">
-        <v>4.2172</v>
+        <v>3.8064</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3508</v>
+        <v>-0.2251</v>
       </c>
       <c r="J339" t="n">
-        <v>-9.120799999999999</v>
+        <v>-5.8526</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.74</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4399</v>
+        <v>-0.2839</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.4374</v>
+        <v>-7.3814</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4541</v>
+        <v>-0.2936</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.8066</v>
+        <v>-7.6336</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.66</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5829</v>
+        <v>1.3786</v>
       </c>
       <c r="J342" t="n">
-        <v>47.487</v>
+        <v>41.358</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.12</v>
       </c>
       <c r="I343" t="n">
-        <v>0.386</v>
+        <v>0.3773</v>
       </c>
       <c r="J343" t="n">
-        <v>11.58</v>
+        <v>11.319</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0177</v>
+        <v>0.0328</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.531</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1805</v>
+        <v>-0.1177</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.415</v>
+        <v>-3.531</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.91</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="J346" t="n">
-        <v>-27.3</v>
+        <v>-26.265</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.13</v>
       </c>
       <c r="I347" t="n">
-        <v>0.2908</v>
+        <v>0.3168</v>
       </c>
       <c r="J347" t="n">
-        <v>8.724</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.09</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2246</v>
+        <v>0.2353</v>
       </c>
       <c r="J348" t="n">
-        <v>6.738</v>
+        <v>7.059</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0391</v>
+        <v>-0.0336</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.173</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.83</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3298</v>
+        <v>-0.2044</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.894</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3893</v>
+        <v>-0.2447</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.679</v>
+        <v>-7.341</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1751</v>
+        <v>0.1518</v>
       </c>
       <c r="J352" t="n">
-        <v>4.3775</v>
+        <v>3.795</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>0.96</v>
       </c>
       <c r="I353" t="n">
-        <v>0.0129</v>
+        <v>-0.025</v>
       </c>
       <c r="J353" t="n">
-        <v>0.3225</v>
+        <v>-0.625</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.66</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.5099</v>
+        <v>-0.3413</v>
       </c>
       <c r="J354" t="n">
-        <v>-12.7475</v>
+        <v>-8.532500000000001</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.62</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.5667</v>
+        <v>-0.3788</v>
       </c>
       <c r="J355" t="n">
-        <v>-14.1675</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.5</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.7247</v>
+        <v>-0.4907</v>
       </c>
       <c r="J356" t="n">
-        <v>-18.1175</v>
+        <v>-12.2675</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.78</v>
       </c>
       <c r="I357" t="n">
-        <v>1.6891</v>
+        <v>1.4533</v>
       </c>
       <c r="J357" t="n">
-        <v>42.2275</v>
+        <v>36.3325</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.77</v>
       </c>
       <c r="I358" t="n">
-        <v>1.6714</v>
+        <v>1.4415</v>
       </c>
       <c r="J358" t="n">
-        <v>41.785</v>
+        <v>36.0375</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.11</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2132</v>
+        <v>0.3012</v>
       </c>
       <c r="J359" t="n">
-        <v>5.33</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1631</v>
+        <v>-0.0788</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.0775</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2984</v>
+        <v>-0.2121</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.46</v>
+        <v>-5.3025</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>0.88</v>
       </c>
       <c r="I362" t="n">
-        <v>-0.1134</v>
+        <v>-0.1144</v>
       </c>
       <c r="J362" t="n">
-        <v>-2.1546</v>
+        <v>-2.1736</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.87</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.1302</v>
+        <v>-0.1259</v>
       </c>
       <c r="J363" t="n">
-        <v>-2.4738</v>
+        <v>-2.3921</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.77</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2933</v>
+        <v>-0.2328</v>
       </c>
       <c r="J364" t="n">
-        <v>-5.5727</v>
+        <v>-4.4232</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.54</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6622</v>
+        <v>-0.447</v>
       </c>
       <c r="J365" t="n">
-        <v>-12.5818</v>
+        <v>-8.493</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.49</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7275</v>
+        <v>-0.4937</v>
       </c>
       <c r="J366" t="n">
-        <v>-13.8225</v>
+        <v>-9.3803</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.86</v>
       </c>
       <c r="I367" t="n">
-        <v>1.7598</v>
+        <v>1.5083</v>
       </c>
       <c r="J367" t="n">
-        <v>33.4362</v>
+        <v>28.6577</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.64</v>
       </c>
       <c r="I368" t="n">
-        <v>1.3602</v>
+        <v>1.257</v>
       </c>
       <c r="J368" t="n">
-        <v>25.8438</v>
+        <v>23.883</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.36</v>
       </c>
       <c r="I369" t="n">
-        <v>0.7454</v>
+        <v>0.8712</v>
       </c>
       <c r="J369" t="n">
-        <v>14.1626</v>
+        <v>16.5528</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.33</v>
       </c>
       <c r="I370" t="n">
-        <v>0.6803</v>
+        <v>0.8052</v>
       </c>
       <c r="J370" t="n">
-        <v>12.9257</v>
+        <v>15.2988</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>1.27</v>
       </c>
       <c r="I371" t="n">
-        <v>0.5482</v>
+        <v>0.6687</v>
       </c>
       <c r="J371" t="n">
-        <v>10.4158</v>
+        <v>12.7053</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>2.03</v>
       </c>
       <c r="I372" t="n">
-        <v>1.9689</v>
+        <v>1.6753</v>
       </c>
       <c r="J372" t="n">
-        <v>33.4713</v>
+        <v>28.4801</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.99</v>
       </c>
       <c r="I373" t="n">
-        <v>1.9241</v>
+        <v>1.6319</v>
       </c>
       <c r="J373" t="n">
-        <v>32.7097</v>
+        <v>27.7423</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.44</v>
       </c>
       <c r="I374" t="n">
-        <v>0.8739</v>
+        <v>1.0067</v>
       </c>
       <c r="J374" t="n">
-        <v>14.8563</v>
+        <v>17.1139</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.27</v>
       </c>
       <c r="I375" t="n">
-        <v>0.5181</v>
+        <v>0.6476</v>
       </c>
       <c r="J375" t="n">
-        <v>8.807700000000001</v>
+        <v>11.0092</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.27</v>
       </c>
       <c r="I376" t="n">
-        <v>0.5181</v>
+        <v>0.6476</v>
       </c>
       <c r="J376" t="n">
-        <v>8.807700000000001</v>
+        <v>11.0092</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I377" t="n">
-        <v>0.0939</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J377" t="n">
-        <v>1.5963</v>
+        <v>1.3804</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.55</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.5347</v>
+        <v>-0.4071</v>
       </c>
       <c r="J378" t="n">
-        <v>-9.0899</v>
+        <v>-6.9207</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.53</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.575</v>
+        <v>-0.4247</v>
       </c>
       <c r="J379" t="n">
-        <v>-9.775</v>
+        <v>-7.2199</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.45</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.4974</v>
       </c>
       <c r="J380" t="n">
-        <v>-12.2094</v>
+        <v>-8.4558</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.17</v>
       </c>
       <c r="I381" t="n">
-        <v>-1.0875</v>
+        <v>-0.7741</v>
       </c>
       <c r="J381" t="n">
-        <v>-18.4875</v>
+        <v>-13.1597</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.76</v>
       </c>
       <c r="I382" t="n">
-        <v>1.5677</v>
+        <v>1.3887</v>
       </c>
       <c r="J382" t="n">
-        <v>31.354</v>
+        <v>27.774</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.71</v>
       </c>
       <c r="I383" t="n">
-        <v>1.4759</v>
+        <v>1.332</v>
       </c>
       <c r="J383" t="n">
-        <v>29.518</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.47</v>
       </c>
       <c r="I384" t="n">
-        <v>0.965</v>
+        <v>1.0563</v>
       </c>
       <c r="J384" t="n">
-        <v>19.3</v>
+        <v>21.126</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.47</v>
       </c>
       <c r="I385" t="n">
-        <v>0.965</v>
+        <v>1.0563</v>
       </c>
       <c r="J385" t="n">
-        <v>19.3</v>
+        <v>21.126</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.24</v>
       </c>
       <c r="I386" t="n">
-        <v>0.4699</v>
+        <v>0.5904</v>
       </c>
       <c r="J386" t="n">
-        <v>9.398</v>
+        <v>11.808</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>0.7</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.2909</v>
+        <v>-0.2502</v>
       </c>
       <c r="J387" t="n">
-        <v>-5.818</v>
+        <v>-5.004</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.59</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.4603</v>
+        <v>-0.3662</v>
       </c>
       <c r="J388" t="n">
-        <v>-9.206</v>
+        <v>-7.324</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.55</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.5261</v>
+        <v>-0.405</v>
       </c>
       <c r="J389" t="n">
-        <v>-10.522</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.42</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.7577</v>
+        <v>-0.5239</v>
       </c>
       <c r="J390" t="n">
-        <v>-15.154</v>
+        <v>-10.478</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.33</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.883</v>
+        <v>-0.6121</v>
       </c>
       <c r="J391" t="n">
-        <v>-17.66</v>
+        <v>-12.242</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.47</v>
       </c>
       <c r="I392" t="n">
-        <v>1.2389</v>
+        <v>1.1455</v>
       </c>
       <c r="J392" t="n">
-        <v>37.167</v>
+        <v>34.365</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>0.5847</v>
+        <v>0.5481</v>
       </c>
       <c r="J393" t="n">
-        <v>17.541</v>
+        <v>16.443</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.06</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2244</v>
+        <v>0.2164</v>
       </c>
       <c r="J394" t="n">
-        <v>6.732</v>
+        <v>6.492</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.84</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.586</v>
+        <v>-0.5308</v>
       </c>
       <c r="J395" t="n">
-        <v>-17.58</v>
+        <v>-15.924</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.71</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.8982</v>
+        <v>-0.8638</v>
       </c>
       <c r="J396" t="n">
-        <v>-26.946</v>
+        <v>-25.914</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J397" t="n">
-        <v>18.615</v>
+        <v>22.635</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.05</v>
       </c>
       <c r="I398" t="n">
-        <v>0.1147</v>
+        <v>0.1326</v>
       </c>
       <c r="J398" t="n">
-        <v>3.441</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.1498</v>
+        <v>-0.08</v>
       </c>
       <c r="J399" t="n">
-        <v>-4.494</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.91</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2227</v>
+        <v>-0.1274</v>
       </c>
       <c r="J400" t="n">
-        <v>-6.681</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.2396</v>
+        <v>-0.1387</v>
       </c>
       <c r="J401" t="n">
-        <v>-7.188</v>
+        <v>-4.161</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.34</v>
       </c>
       <c r="I402" t="n">
-        <v>0.5804</v>
+        <v>0.6972</v>
       </c>
       <c r="J402" t="n">
-        <v>16.2512</v>
+        <v>19.5216</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3029</v>
+        <v>0.3334</v>
       </c>
       <c r="J403" t="n">
-        <v>8.481199999999999</v>
+        <v>9.3352</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.96</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.1013</v>
+        <v>-0.0609</v>
       </c>
       <c r="J404" t="n">
-        <v>-2.8364</v>
+        <v>-1.7052</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.82</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3477</v>
+        <v>-0.2158</v>
       </c>
       <c r="J405" t="n">
-        <v>-9.7356</v>
+        <v>-6.0424</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.61</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6297</v>
+        <v>-0.4173</v>
       </c>
       <c r="J406" t="n">
-        <v>-17.6316</v>
+        <v>-11.6844</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.5</v>
       </c>
       <c r="I407" t="n">
-        <v>1.2818</v>
+        <v>1.1747</v>
       </c>
       <c r="J407" t="n">
-        <v>35.8904</v>
+        <v>32.8916</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.2</v>
       </c>
       <c r="I408" t="n">
-        <v>0.6165</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J408" t="n">
-        <v>17.262</v>
+        <v>16.4696</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.93</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.3472</v>
+        <v>-0.2833</v>
       </c>
       <c r="J409" t="n">
-        <v>-9.7216</v>
+        <v>-7.9324</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.9</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.4361</v>
+        <v>-0.3728</v>
       </c>
       <c r="J410" t="n">
-        <v>-12.2108</v>
+        <v>-10.4384</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.89</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4643</v>
+        <v>-0.4016</v>
       </c>
       <c r="J411" t="n">
-        <v>-13.0004</v>
+        <v>-11.2448</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.79</v>
       </c>
       <c r="I412" t="n">
-        <v>1.7469</v>
+        <v>1.4904</v>
       </c>
       <c r="J412" t="n">
-        <v>62.8884</v>
+        <v>53.6544</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.26</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J413" t="n">
-        <v>24.0408</v>
+        <v>24.948</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.247</v>
+        <v>0.3216</v>
       </c>
       <c r="J414" t="n">
-        <v>8.891999999999999</v>
+        <v>11.5776</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2188</v>
+        <v>0.2936</v>
       </c>
       <c r="J415" t="n">
-        <v>7.8768</v>
+        <v>10.5696</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.93</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4017</v>
+        <v>-0.3233</v>
       </c>
       <c r="J416" t="n">
-        <v>-14.4612</v>
+        <v>-11.6388</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3495</v>
+        <v>0.3838</v>
       </c>
       <c r="J417" t="n">
-        <v>12.582</v>
+        <v>13.8168</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.01</v>
       </c>
       <c r="I418" t="n">
-        <v>0.0919</v>
+        <v>0.0631</v>
       </c>
       <c r="J418" t="n">
-        <v>3.3084</v>
+        <v>2.2716</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.9</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1686</v>
+        <v>-0.1237</v>
       </c>
       <c r="J419" t="n">
-        <v>-6.0696</v>
+        <v>-4.4532</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.8</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J420" t="n">
-        <v>-12.6828</v>
+        <v>-8.121600000000001</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.59</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.6401</v>
+        <v>-0.426</v>
       </c>
       <c r="J421" t="n">
-        <v>-23.0436</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>0.82</v>
       </c>
       <c r="I422" t="n">
-        <v>-0.2133</v>
+        <v>-0.1816</v>
       </c>
       <c r="J422" t="n">
-        <v>-4.6926</v>
+        <v>-3.9952</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>0.78</v>
       </c>
       <c r="I423" t="n">
-        <v>-0.2781</v>
+        <v>-0.2231</v>
       </c>
       <c r="J423" t="n">
-        <v>-6.1182</v>
+        <v>-4.9082</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.4054</v>
+        <v>-0.2897</v>
       </c>
       <c r="J424" t="n">
-        <v>-8.918799999999999</v>
+        <v>-6.3734</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.65</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.5077</v>
+        <v>-0.3445</v>
       </c>
       <c r="J425" t="n">
-        <v>-11.1694</v>
+        <v>-7.579</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.6</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.5808</v>
+        <v>-0.3912</v>
       </c>
       <c r="J426" t="n">
-        <v>-12.7776</v>
+        <v>-8.606400000000001</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.76</v>
       </c>
       <c r="I427" t="n">
-        <v>1.6082</v>
+        <v>1.406</v>
       </c>
       <c r="J427" t="n">
-        <v>35.3804</v>
+        <v>30.932</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.59</v>
       </c>
       <c r="I428" t="n">
-        <v>1.2905</v>
+        <v>1.2072</v>
       </c>
       <c r="J428" t="n">
-        <v>28.391</v>
+        <v>26.5584</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>1.47</v>
       </c>
       <c r="I429" t="n">
-        <v>1.0414</v>
+        <v>1.0642</v>
       </c>
       <c r="J429" t="n">
-        <v>22.9108</v>
+        <v>23.4124</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>1.29</v>
       </c>
       <c r="I430" t="n">
-        <v>0.6139</v>
+        <v>0.7269</v>
       </c>
       <c r="J430" t="n">
-        <v>13.5058</v>
+        <v>15.9918</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>1.05</v>
       </c>
       <c r="I431" t="n">
-        <v>0.0107</v>
+        <v>0.0992</v>
       </c>
       <c r="J431" t="n">
-        <v>0.2354</v>
+        <v>2.1824</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2261/event_2261_evp_summary.xlsx
+++ b/database/event/2261/event_2261_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9526</v>
+        <v>6.8397</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1257</v>
+        <v>3.0749</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5007</v>
+        <v>2.4894</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9526</v>
+        <v>6.8397</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9727</v>
+        <v>2.6443</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9799</v>
+        <v>4.1954</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1677</v>
+        <v>3.0626</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1677</v>
+        <v>3.0626</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9799</v>
+        <v>4.1954</v>
       </c>
       <c r="K2" t="n">
         <v>133</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.147600000000001</v>
+        <v>7.258000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>333</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9321</v>
+        <v>5.953</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6669</v>
+        <v>2.6763</v>
       </c>
       <c r="D3" t="n">
-        <v>2.04</v>
+        <v>2.0857</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9321</v>
+        <v>5.953</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6605</v>
+        <v>2.3762</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2716</v>
+        <v>3.5768</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6605</v>
+        <v>2.4759</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6605</v>
+        <v>2.4759</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2716</v>
+        <v>3.5768</v>
       </c>
       <c r="K3" t="n">
         <v>133</v>
@@ -575,7 +575,7 @@
         <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9321</v>
+        <v>6.0527</v>
       </c>
       <c r="N3" t="n">
         <v>333</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6615</v>
+        <v>5.7852</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5452</v>
+        <v>2.6008</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9179</v>
+        <v>2.0093</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6615</v>
+        <v>5.7852</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0812</v>
+        <v>4.0158</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5803</v>
+        <v>1.7694</v>
       </c>
       <c r="H4" t="n">
-        <v>8.8931</v>
+        <v>8.355499999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.624</v>
+        <v>4.5119</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5803</v>
+        <v>1.7694</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>85</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2043</v>
+        <v>6.2813</v>
       </c>
       <c r="N4" t="n">
         <v>211</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1348</v>
+        <v>5.2452</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3084</v>
+        <v>2.3581</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6801</v>
+        <v>1.7635</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1348</v>
+        <v>5.2452</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5204</v>
+        <v>1.4186</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6144</v>
+        <v>3.8266</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5204</v>
+        <v>1.4186</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5204</v>
+        <v>1.4186</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6144</v>
+        <v>3.8266</v>
       </c>
       <c r="K5" t="n">
         <v>124</v>
@@ -667,7 +667,7 @@
         <v>210</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1348</v>
+        <v>5.245200000000001</v>
       </c>
       <c r="N5" t="n">
         <v>334</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8512</v>
+        <v>3.8565</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7314</v>
+        <v>1.7338</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1006</v>
+        <v>1.1314</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8512</v>
+        <v>3.8565</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2003</v>
+        <v>1.7872</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6509</v>
+        <v>2.0693</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7895</v>
+        <v>1.7872</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0103</v>
+        <v>1.7872</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6509</v>
+        <v>2.0693</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L6" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6612</v>
+        <v>3.8565</v>
       </c>
       <c r="N6" t="n">
-        <v>211</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.688</v>
+        <v>3.8549</v>
       </c>
       <c r="C7" t="n">
-        <v>1.658</v>
+        <v>1.733</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0269</v>
+        <v>1.1306</v>
       </c>
       <c r="E7" t="n">
-        <v>3.688</v>
+        <v>3.8549</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8938</v>
+        <v>3.155</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7942</v>
+        <v>0.6999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8938</v>
+        <v>5.5155</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8938</v>
+        <v>2.9783</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7942</v>
+        <v>0.6999</v>
       </c>
       <c r="K7" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.688</v>
+        <v>3.6782</v>
       </c>
       <c r="N7" t="n">
-        <v>334</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5302</v>
+        <v>3.4983</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5871</v>
+        <v>1.5727</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9557</v>
+        <v>0.9683</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5302</v>
+        <v>3.4983</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1312</v>
+        <v>4.1286</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.601</v>
+        <v>-0.6303</v>
       </c>
       <c r="H8" t="n">
-        <v>9.0694</v>
+        <v>8.7277</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7157</v>
+        <v>4.7129</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.601</v>
+        <v>-0.6303</v>
       </c>
       <c r="K8" t="n">
         <v>129</v>
@@ -805,7 +805,7 @@
         <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1147</v>
+        <v>4.0826</v>
       </c>
       <c r="N8" t="n">
         <v>187</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2595</v>
+        <v>3.4959</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4654</v>
+        <v>1.5716</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8335</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2595</v>
+        <v>3.4959</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4119</v>
+        <v>0.6641</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1524</v>
+        <v>2.8318</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5352</v>
+        <v>0.6641</v>
       </c>
       <c r="I9" t="n">
-        <v>3.398</v>
+        <v>0.6641</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1524</v>
+        <v>2.8318</v>
       </c>
       <c r="K9" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2456</v>
+        <v>3.4959</v>
       </c>
       <c r="N9" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2174</v>
+        <v>3.2442</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4464</v>
+        <v>1.4585</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8145</v>
+        <v>0.8526</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2174</v>
+        <v>3.2442</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6938</v>
+        <v>3.361</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5236</v>
+        <v>-0.1168</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6938</v>
+        <v>6.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6938</v>
+        <v>3.3452</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5236</v>
+        <v>-0.1168</v>
       </c>
       <c r="K10" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L10" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2174</v>
+        <v>3.2284</v>
       </c>
       <c r="N10" t="n">
-        <v>333</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2058</v>
+        <v>3.1575</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4412</v>
+        <v>1.4195</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8092</v>
+        <v>0.8132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2058</v>
+        <v>3.1575</v>
       </c>
       <c r="F11" t="n">
-        <v>3.399</v>
+        <v>3.3608</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1932</v>
+        <v>-0.2033</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4895</v>
+        <v>6.1944</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3743</v>
+        <v>3.3449</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1932</v>
+        <v>-0.2033</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1811</v>
+        <v>3.1416</v>
       </c>
       <c r="N11" t="n">
         <v>211</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0145</v>
+        <v>2.8255</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3552</v>
+        <v>1.2703</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7229</v>
+        <v>0.662</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0145</v>
+        <v>2.8255</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0145</v>
+        <v>0.7114</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.1141</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2595</v>
+        <v>0.7114</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2595</v>
+        <v>0.7114</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.1141</v>
       </c>
       <c r="K12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2595</v>
+        <v>2.8255</v>
       </c>
       <c r="N12" t="n">
-        <v>127</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8241</v>
+        <v>2.8196</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2696</v>
+        <v>1.2676</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6369</v>
+        <v>0.6593</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8241</v>
+        <v>2.8196</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8065</v>
+        <v>0.1087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0176</v>
+        <v>2.7109</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4022</v>
+        <v>0.1087</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2889</v>
+        <v>0.1087</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0176</v>
+        <v>2.7109</v>
       </c>
       <c r="K13" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3065</v>
+        <v>2.8196</v>
       </c>
       <c r="N13" t="n">
-        <v>187</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8179</v>
+        <v>2.7559</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2668</v>
+        <v>1.239</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6341</v>
+        <v>0.6303</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8179</v>
+        <v>2.7559</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8179</v>
+        <v>2.7534</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8279</v>
+        <v>4.1902</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8279</v>
+        <v>2.2627</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="K14" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8279</v>
+        <v>2.2652</v>
       </c>
       <c r="N14" t="n">
-        <v>127</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.813</v>
+        <v>2.6814</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2646</v>
+        <v>1.2055</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6319</v>
+        <v>0.5964</v>
       </c>
       <c r="E15" t="n">
-        <v>2.813</v>
+        <v>2.6814</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4928</v>
+        <v>2.3928</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3202</v>
+        <v>0.2886</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4928</v>
+        <v>2.5121</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5954</v>
+        <v>2.5768</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3202</v>
+        <v>0.2886</v>
       </c>
       <c r="K15" t="n">
         <v>154</v>
@@ -1127,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9156</v>
+        <v>2.8654</v>
       </c>
       <c r="N15" t="n">
         <v>199</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7294</v>
+        <v>2.6577</v>
       </c>
       <c r="C16" t="n">
-        <v>1.227</v>
+        <v>1.1948</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5942</v>
+        <v>0.5856</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7294</v>
+        <v>2.6577</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1163</v>
+        <v>3.0541</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3869</v>
+        <v>-0.3964</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4938</v>
+        <v>5.1825</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8565</v>
+        <v>2.7985</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3869</v>
+        <v>-0.3964</v>
       </c>
       <c r="K16" t="n">
         <v>126</v>
@@ -1173,7 +1173,7 @@
         <v>85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4696</v>
+        <v>2.4021</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6953</v>
+        <v>2.6559</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2117</v>
+        <v>1.194</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5788</v>
+        <v>0.5848</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6953</v>
+        <v>2.6559</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1661</v>
+        <v>2.6559</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5292</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1661</v>
+        <v>3.0881</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1661</v>
+        <v>3.0881</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5292</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6953</v>
+        <v>3.0881</v>
       </c>
       <c r="N17" t="n">
-        <v>334</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6254</v>
+        <v>2.6001</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1803</v>
+        <v>1.1689</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5472</v>
+        <v>0.5594</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6254</v>
+        <v>2.6001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3943</v>
+        <v>2.3642</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2311</v>
+        <v>0.2359</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9495</v>
+        <v>2.9062</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5336</v>
+        <v>1.5693</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2311</v>
+        <v>0.2359</v>
       </c>
       <c r="K18" t="n">
         <v>129</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7647</v>
+        <v>1.8052</v>
       </c>
       <c r="N18" t="n">
         <v>187</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6144</v>
+        <v>2.4855</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1753</v>
+        <v>1.1174</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5423</v>
+        <v>0.5072</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6144</v>
+        <v>2.4855</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7178</v>
+        <v>2.4855</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8966</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7178</v>
+        <v>2.7151</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7178</v>
+        <v>2.7151</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8966</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="L19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6144</v>
+        <v>2.7151</v>
       </c>
       <c r="N19" t="n">
-        <v>333</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5338</v>
+        <v>2.4021</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1391</v>
+        <v>1.0799</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5059</v>
+        <v>0.4693</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5338</v>
+        <v>2.4021</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2672</v>
+        <v>0.2996</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7334000000000001</v>
+        <v>2.1025</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8145</v>
+        <v>0.2996</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9714</v>
+        <v>0.2996</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7334000000000001</v>
+        <v>2.1025</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="M20" t="n">
-        <v>3.238</v>
+        <v>2.4021</v>
       </c>
       <c r="N20" t="n">
-        <v>199</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2486</v>
+        <v>2.2098</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0109</v>
+        <v>0.9935</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3771</v>
+        <v>0.3817</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2486</v>
+        <v>2.2098</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3513</v>
+        <v>2.9743</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1027</v>
+        <v>-0.7645</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7983</v>
+        <v>3.7848</v>
       </c>
       <c r="I21" t="n">
-        <v>1.455</v>
+        <v>3.8823</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1027</v>
+        <v>-0.7645</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3523</v>
+        <v>3.1178</v>
       </c>
       <c r="N21" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1965</v>
+        <v>2.1517</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9875</v>
+        <v>0.9673</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3536</v>
+        <v>0.3553</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1965</v>
+        <v>2.1517</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3384</v>
+        <v>2.2658</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8581</v>
+        <v>-0.1141</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3384</v>
+        <v>2.5815</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3384</v>
+        <v>1.394</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8581</v>
+        <v>-0.1141</v>
       </c>
       <c r="K22" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L22" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1965</v>
+        <v>1.2799</v>
       </c>
       <c r="N22" t="n">
-        <v>333</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1631</v>
+        <v>2.1368</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9725</v>
+        <v>0.9606</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3385</v>
+        <v>0.3485</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1631</v>
+        <v>2.1368</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2731</v>
+        <v>2.259</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.11</v>
+        <v>-0.1222</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2731</v>
+        <v>2.259</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3666</v>
+        <v>2.3172</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.11</v>
+        <v>-0.1222</v>
       </c>
       <c r="K23" t="n">
         <v>154</v>
@@ -1495,7 +1495,7 @@
         <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2566</v>
+        <v>2.195</v>
       </c>
       <c r="N23" t="n">
         <v>199</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1104</v>
+        <v>2.1362</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9488</v>
+        <v>0.9604</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3147</v>
+        <v>0.3482</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1104</v>
+        <v>2.1362</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1104</v>
+        <v>0.5947</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.5415</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1104</v>
+        <v>0.5947</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1104</v>
+        <v>0.5947</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.5415</v>
       </c>
       <c r="K24" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M24" t="n">
-        <v>2.1104</v>
+        <v>2.1362</v>
       </c>
       <c r="N24" t="n">
-        <v>146</v>
+        <v>334</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9312</v>
+        <v>0.9237</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2971</v>
+        <v>0.3111</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0713</v>
+        <v>2.0547</v>
       </c>
       <c r="N25" t="n">
         <v>127</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.027</v>
+        <v>2.0186</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9113</v>
+        <v>0.9075</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2771</v>
+        <v>0.2947</v>
       </c>
       <c r="E26" t="n">
-        <v>2.027</v>
+        <v>2.0186</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3137</v>
+        <v>2.0186</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2867</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6657</v>
+        <v>2.0186</v>
       </c>
       <c r="I26" t="n">
-        <v>1.386</v>
+        <v>2.0186</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2867</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0993</v>
+        <v>2.0186</v>
       </c>
       <c r="N26" t="n">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.0235</v>
+        <v>1.9944</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9097</v>
+        <v>0.8966</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2755</v>
+        <v>0.2837</v>
       </c>
       <c r="E27" t="n">
-        <v>2.0235</v>
+        <v>1.9944</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6453</v>
+        <v>2.3075</v>
       </c>
       <c r="G27" t="n">
-        <v>1.3782</v>
+        <v>-0.3131</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6453</v>
+        <v>2.7191</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6453</v>
+        <v>1.4683</v>
       </c>
       <c r="J27" t="n">
-        <v>1.3782</v>
+        <v>-0.3131</v>
       </c>
       <c r="K27" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L27" t="n">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
-        <v>2.0235</v>
+        <v>1.1552</v>
       </c>
       <c r="N27" t="n">
-        <v>334</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9594</v>
+        <v>1.8871</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8809</v>
+        <v>0.8484</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2466</v>
+        <v>0.2348</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9594</v>
+        <v>1.8871</v>
       </c>
       <c r="F28" t="n">
-        <v>1.9393</v>
+        <v>1.8696</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0201</v>
+        <v>0.0175</v>
       </c>
       <c r="H28" t="n">
-        <v>1.9393</v>
+        <v>1.8696</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9393</v>
+        <v>1.8696</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0201</v>
+        <v>0.0175</v>
       </c>
       <c r="K28" t="n">
         <v>129</v>
@@ -1725,7 +1725,7 @@
         <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9594</v>
+        <v>1.8871</v>
       </c>
       <c r="N28" t="n">
         <v>191</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8672</v>
+        <v>0.8232</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2328</v>
+        <v>0.2094</v>
       </c>
       <c r="E29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="F29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="I29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.929</v>
+        <v>1.8311</v>
       </c>
       <c r="N29" t="n">
         <v>137</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6938</v>
+        <v>0.6792</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0587</v>
+        <v>0.0635</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5432</v>
+        <v>1.5107</v>
       </c>
       <c r="N30" t="n">
         <v>127</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6281</v>
+        <v>0.628</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0072</v>
+        <v>0.0117</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3972</v>
+        <v>1.397</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6278</v>
+        <v>0.5916</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0076</v>
+        <v>-0.0252</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3965</v>
+        <v>1.3159</v>
       </c>
       <c r="N32" t="n">
         <v>127</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2061</v>
+        <v>1.3109</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5422</v>
+        <v>0.5893</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0935</v>
+        <v>-0.0275</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2061</v>
+        <v>1.3109</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7618</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4102</v>
+        <v>0.5491</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7618</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7618</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4102</v>
+        <v>0.5491</v>
       </c>
       <c r="K33" t="n">
         <v>124</v>
@@ -1955,7 +1955,7 @@
         <v>210</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2061</v>
+        <v>1.3109</v>
       </c>
       <c r="N33" t="n">
         <v>334</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5129</v>
+        <v>0.4743</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.123</v>
+        <v>-0.1439</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1409</v>
+        <v>1.0551</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3883</v>
+        <v>0.3635</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2481</v>
+        <v>-0.2561</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8637</v>
+        <v>0.8086</v>
       </c>
       <c r="N35" t="n">
         <v>146</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="C36" t="n">
-        <v>0.357</v>
+        <v>0.3269</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2795</v>
+        <v>-0.2932</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7941</v>
+        <v>0.7272</v>
       </c>
       <c r="N36" t="n">
         <v>137</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3423</v>
+        <v>0.288</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2942</v>
+        <v>-0.3326</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7615</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.755</v>
+        <v>0.6357</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3394</v>
+        <v>0.2858</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2972</v>
+        <v>-0.3348</v>
       </c>
       <c r="E38" t="n">
-        <v>0.755</v>
+        <v>0.6357</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3111</v>
+        <v>0.6357</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5561</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3111</v>
+        <v>0.6357</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3111</v>
+        <v>0.6357</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5561</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L38" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7549999999999999</v>
+        <v>0.6357</v>
       </c>
       <c r="N38" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6806</v>
+        <v>0.6351</v>
       </c>
       <c r="C39" t="n">
-        <v>0.306</v>
+        <v>0.2855</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3308</v>
+        <v>-0.3351</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6806</v>
+        <v>0.6351</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6806</v>
+        <v>1.2105</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.5754</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6806</v>
+        <v>1.2105</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6806</v>
+        <v>1.2105</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.5754</v>
       </c>
       <c r="K39" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6806</v>
+        <v>0.6350999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>146</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2998</v>
+        <v>0.2751</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3369</v>
+        <v>-0.3457</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6669</v>
+        <v>0.6119</v>
       </c>
       <c r="N40" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2369</v>
+        <v>0.1971</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4001</v>
+        <v>-0.4246</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5269</v>
+        <v>0.4385</v>
       </c>
       <c r="N41" t="n">
         <v>126</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1925</v>
+        <v>0.195</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4447</v>
+        <v>-0.4267</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4281</v>
+        <v>0.4338</v>
       </c>
       <c r="N42" t="n">
         <v>146</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1923</v>
+        <v>0.1494</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4449</v>
+        <v>-0.4729</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4278</v>
+        <v>0.3323</v>
       </c>
       <c r="N43" t="n">
         <v>137</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1412</v>
+        <v>0.1012</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4963</v>
+        <v>-0.5218</v>
       </c>
       <c r="E44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="F44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="I44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.314</v>
+        <v>0.225</v>
       </c>
       <c r="N44" t="n">
         <v>132</v>
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.162</v>
+        <v>0.1208</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0728</v>
+        <v>0.0543</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5649</v>
+        <v>-0.5692</v>
       </c>
       <c r="E45" t="n">
-        <v>0.162</v>
+        <v>0.1208</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0229</v>
+        <v>0.9419</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.8609</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0229</v>
+        <v>0.9419</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0229</v>
+        <v>0.9419</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8609</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="K45" t="n">
         <v>129</v>
@@ -2507,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1619999999999999</v>
+        <v>0.1207999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>191</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0094</v>
+        <v>-0.0271</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6474</v>
+        <v>-0.6516</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0209</v>
+        <v>-0.0602</v>
       </c>
       <c r="N46" t="n">
         <v>127</v>
@@ -2566,31 +2566,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.2581</v>
+        <v>-0.2216</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.116</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7251</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.2581</v>
+        <v>-0.2216</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2276</v>
+        <v>0.3024</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.4857</v>
+        <v>-0.524</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2276</v>
+        <v>0.3024</v>
       </c>
       <c r="I47" t="n">
-        <v>0.237</v>
+        <v>0.3102</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.4857</v>
+        <v>-0.524</v>
       </c>
       <c r="K47" t="n">
         <v>154</v>
@@ -2599,7 +2599,7 @@
         <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.2487</v>
+        <v>-0.2138</v>
       </c>
       <c r="N47" t="n">
         <v>199</v>
@@ -2608,139 +2608,139 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4563</v>
+        <v>-0.4424</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2051</v>
+        <v>-0.1989</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.844</v>
+        <v>-0.8256</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.4563</v>
+        <v>-0.4424</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.3601</v>
+        <v>-0.9341</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.5044</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.3601</v>
+        <v>-0.9341</v>
       </c>
       <c r="K48" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.4563</v>
+        <v>-0.4297000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.462</v>
+        <v>-0.472</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2077</v>
+        <v>-0.2122</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8466</v>
+        <v>-0.8391</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.462</v>
+        <v>-0.472</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.462</v>
+        <v>-0.119</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.353</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.462</v>
+        <v>-0.119</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.462</v>
+        <v>-0.119</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.353</v>
       </c>
       <c r="K49" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.462</v>
+        <v>-0.472</v>
       </c>
       <c r="N49" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4915</v>
+        <v>-0.5412</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.221</v>
+        <v>-0.2433</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8599</v>
+        <v>-0.8706</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4915</v>
+        <v>-0.5412</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4229</v>
+        <v>-0.5412</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.9144</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4229</v>
+        <v>-0.5412</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4403</v>
+        <v>-0.5412</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9144</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.4741</v>
+        <v>-0.5412</v>
       </c>
       <c r="N50" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2437</v>
+        <v>-0.2546</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8827</v>
+        <v>-0.882</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.542</v>
+        <v>-0.5664</v>
       </c>
       <c r="N51" t="n">
         <v>127</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6706</v>
+        <v>-0.6666</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3015</v>
+        <v>-0.2997</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9408</v>
+        <v>-0.9277</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.6706</v>
+        <v>-0.6666</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2204</v>
+        <v>-0.2443</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4502</v>
+        <v>-0.4223</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2204</v>
+        <v>-0.2443</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2204</v>
+        <v>-0.2443</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4502</v>
+        <v>-0.4223</v>
       </c>
       <c r="K52" t="n">
         <v>129</v>
@@ -2829,7 +2829,7 @@
         <v>62</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.6706</v>
+        <v>-0.6666</v>
       </c>
       <c r="N52" t="n">
         <v>191</v>
@@ -2838,93 +2838,93 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3875</v>
+        <v>-0.3956</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0272</v>
+        <v>-1.0248</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.862</v>
+        <v>-0.88</v>
       </c>
       <c r="N53" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4143</v>
+        <v>-0.4181</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.054</v>
+        <v>-1.0475</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.9215</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55">
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4301</v>
+        <v>-0.4198</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.0699</v>
+        <v>-1.0492</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.9566</v>
+        <v>-0.9337</v>
       </c>
       <c r="N55" t="n">
         <v>127</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4638</v>
+        <v>-0.4874</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1037</v>
+        <v>-1.1177</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.0316</v>
+        <v>-1.0841</v>
       </c>
       <c r="N56" t="n">
         <v>132</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5696</v>
+        <v>-0.5999</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.21</v>
+        <v>-1.2316</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.267</v>
+        <v>-1.3344</v>
       </c>
       <c r="N57" t="n">
         <v>126</v>
@@ -3068,185 +3068,185 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6269</v>
+        <v>-0.6561</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2676</v>
+        <v>-1.2886</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.3945</v>
+        <v>-1.4595</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6605</v>
+        <v>-0.6566</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.3012</v>
+        <v>-1.2891</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.4691</v>
+        <v>-1.4606</v>
       </c>
       <c r="N59" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.8223</v>
+        <v>-0.8293</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4637</v>
+        <v>-1.4639</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.829</v>
+        <v>-1.8447</v>
       </c>
       <c r="N60" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4726</v>
+        <v>-1.4801</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.8487</v>
+        <v>-1.8802</v>
       </c>
       <c r="N61" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3349,10 +3349,10 @@
         <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6121</v>
+        <v>0.6201</v>
       </c>
       <c r="J2" t="n">
-        <v>12.242</v>
+        <v>12.402</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6018</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>12.036</v>
+        <v>12.208</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4677</v>
+        <v>0.483</v>
       </c>
       <c r="J4" t="n">
-        <v>9.353999999999999</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4136</v>
+        <v>0.4312</v>
       </c>
       <c r="J5" t="n">
-        <v>8.272</v>
+        <v>8.624000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3455</v>
+        <v>0.3656</v>
       </c>
       <c r="J6" t="n">
-        <v>6.91</v>
+        <v>7.312</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3662</v>
+        <v>0.3514</v>
       </c>
       <c r="J7" t="n">
-        <v>7.324</v>
+        <v>7.028</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2299</v>
+        <v>-0.2496</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.598</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.74</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2667</v>
+        <v>-0.2861</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.334</v>
+        <v>-5.722</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.62</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3791</v>
+        <v>-0.3947</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.582</v>
+        <v>-7.894</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5188</v>
+        <v>-0.5266</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.376</v>
+        <v>-10.532</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5716</v>
+        <v>0.5578</v>
       </c>
       <c r="J12" t="n">
-        <v>17.148</v>
+        <v>16.734</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3744</v>
+        <v>0.3756</v>
       </c>
       <c r="J13" t="n">
-        <v>11.232</v>
+        <v>11.268</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="J14" t="n">
-        <v>4.68</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2018</v>
+        <v>-0.2146</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.054</v>
+        <v>-6.438</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2425</v>
+        <v>-0.2551</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.275</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1249</v>
+        <v>1.1098</v>
       </c>
       <c r="J17" t="n">
-        <v>33.747</v>
+        <v>33.294</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8446</v>
+        <v>0.7927</v>
       </c>
       <c r="J18" t="n">
-        <v>25.338</v>
+        <v>23.781</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2044</v>
+        <v>0.2137</v>
       </c>
       <c r="J19" t="n">
-        <v>6.132</v>
+        <v>6.411</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0277</v>
+        <v>0.0412</v>
       </c>
       <c r="J20" t="n">
-        <v>0.831</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8312</v>
+        <v>-0.7667</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.936</v>
+        <v>-23.001</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.639</v>
+        <v>0.6194</v>
       </c>
       <c r="J22" t="n">
-        <v>19.17</v>
+        <v>18.582</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1108</v>
+        <v>0.1208</v>
       </c>
       <c r="J23" t="n">
-        <v>3.324</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0391</v>
+        <v>-0.0451</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.173</v>
+        <v>-1.353</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0533</v>
+        <v>-0.0607</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.599</v>
+        <v>-1.821</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1813</v>
+        <v>-0.1939</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.439</v>
+        <v>-5.817</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7785</v>
+        <v>0.7339</v>
       </c>
       <c r="J27" t="n">
-        <v>23.355</v>
+        <v>22.017</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5065</v>
+        <v>0.4923</v>
       </c>
       <c r="J28" t="n">
-        <v>15.195</v>
+        <v>14.769</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3229</v>
+        <v>0.3242</v>
       </c>
       <c r="J29" t="n">
-        <v>9.686999999999999</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2378</v>
+        <v>0.2445</v>
       </c>
       <c r="J30" t="n">
-        <v>7.134</v>
+        <v>7.335</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4066</v>
+        <v>-0.3885</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.198</v>
+        <v>-11.655</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5429</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>18.4586</v>
+        <v>20.3762</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3797</v>
+        <v>0.4026</v>
       </c>
       <c r="J33" t="n">
-        <v>12.9098</v>
+        <v>13.6884</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2291</v>
+        <v>-0.2447</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.7894</v>
+        <v>-8.319800000000001</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2881</v>
+        <v>-0.3027</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.795400000000001</v>
+        <v>-10.2918</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4569</v>
+        <v>-0.465</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.5346</v>
+        <v>-15.81</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8365</v>
+        <v>0.9245</v>
       </c>
       <c r="J37" t="n">
-        <v>28.441</v>
+        <v>31.433</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5199</v>
+        <v>0.5775</v>
       </c>
       <c r="J38" t="n">
-        <v>17.6766</v>
+        <v>19.635</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4365</v>
+        <v>0.4832</v>
       </c>
       <c r="J39" t="n">
-        <v>14.841</v>
+        <v>16.4288</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4218</v>
+        <v>0.4664</v>
       </c>
       <c r="J40" t="n">
-        <v>14.3412</v>
+        <v>15.8576</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1464</v>
+        <v>0.1654</v>
       </c>
       <c r="J41" t="n">
-        <v>4.9776</v>
+        <v>5.6236</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.6</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5544</v>
+        <v>0.6373</v>
       </c>
       <c r="J42" t="n">
-        <v>12.1968</v>
+        <v>14.0206</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.37</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4104</v>
+        <v>0.4674</v>
       </c>
       <c r="J43" t="n">
-        <v>9.0288</v>
+        <v>10.2828</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3658</v>
+        <v>0.4046</v>
       </c>
       <c r="J44" t="n">
-        <v>8.047599999999999</v>
+        <v>8.901199999999999</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3071</v>
+        <v>0.3266</v>
       </c>
       <c r="J45" t="n">
-        <v>6.7562</v>
+        <v>7.1852</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0944</v>
+        <v>0.1151</v>
       </c>
       <c r="J46" t="n">
-        <v>2.0768</v>
+        <v>2.5322</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5658</v>
       </c>
       <c r="J47" t="n">
-        <v>11.3872</v>
+        <v>12.4476</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2588</v>
+        <v>-0.278</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.6936</v>
+        <v>-6.116</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.62</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.381</v>
+        <v>-0.3961</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.382</v>
+        <v>-8.7142</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4184</v>
+        <v>-0.4317</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.204800000000001</v>
+        <v>-9.497400000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4649</v>
+        <v>-0.4757</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.2278</v>
+        <v>-10.4654</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.27</v>
       </c>
       <c r="I52" t="n">
-        <v>0.483</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>14.007</v>
+        <v>15.4512</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.7434</v>
+        <v>-3.1117</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1059</v>
+        <v>-0.1192</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.0711</v>
+        <v>-3.4568</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2122</v>
+        <v>-0.2272</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.1538</v>
+        <v>-6.5888</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.78</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2522</v>
+        <v>-0.2668</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.3138</v>
+        <v>-7.7372</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6672</v>
+        <v>0.7378</v>
       </c>
       <c r="J57" t="n">
-        <v>19.3488</v>
+        <v>21.3962</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5535</v>
       </c>
       <c r="J58" t="n">
-        <v>14.5145</v>
+        <v>16.0515</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5535</v>
       </c>
       <c r="J59" t="n">
-        <v>14.5145</v>
+        <v>16.0515</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2255</v>
+        <v>0.236</v>
       </c>
       <c r="J60" t="n">
-        <v>6.5395</v>
+        <v>6.844</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3026</v>
+        <v>-0.2892</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.775399999999999</v>
+        <v>-8.386799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.373</v>
+        <v>0.3943</v>
       </c>
       <c r="J62" t="n">
-        <v>11.19</v>
+        <v>11.829</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1968</v>
+        <v>0.2012</v>
       </c>
       <c r="J63" t="n">
-        <v>5.904</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0164</v>
+        <v>-0.0221</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.492</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2527</v>
+        <v>-0.2672</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.581</v>
+        <v>-8.016</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3015</v>
+        <v>-0.315</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.045</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0126</v>
+        <v>1.1062</v>
       </c>
       <c r="J67" t="n">
-        <v>30.378</v>
+        <v>33.186</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4951</v>
+        <v>0.5452</v>
       </c>
       <c r="J68" t="n">
-        <v>14.853</v>
+        <v>16.356</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2378</v>
+        <v>0.2445</v>
       </c>
       <c r="J69" t="n">
-        <v>7.134</v>
+        <v>7.335</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3187</v>
+        <v>-0.3075</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.561</v>
+        <v>-9.225</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8524</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>-25.572</v>
+        <v>-23.574</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.034</v>
+        <v>0.0246</v>
       </c>
       <c r="J72" t="n">
-        <v>0.952</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.034</v>
+        <v>-0.0459</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.952</v>
+        <v>-1.2852</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1419</v>
+        <v>-0.1584</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.9732</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2995</v>
+        <v>-0.3153</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.385999999999999</v>
+        <v>-8.8284</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2995</v>
+        <v>-0.3153</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.385999999999999</v>
+        <v>-8.8284</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5849</v>
+        <v>0.6474</v>
       </c>
       <c r="J77" t="n">
-        <v>16.3772</v>
+        <v>18.1272</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5289</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>14.8092</v>
+        <v>16.3856</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3995</v>
+        <v>0.4362</v>
       </c>
       <c r="J79" t="n">
-        <v>11.186</v>
+        <v>12.2136</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3121</v>
+        <v>0.3172</v>
       </c>
       <c r="J80" t="n">
-        <v>8.738799999999999</v>
+        <v>8.881600000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0175</v>
+        <v>0.034</v>
       </c>
       <c r="J81" t="n">
-        <v>0.49</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3452</v>
+        <v>0.3488</v>
       </c>
       <c r="J82" t="n">
-        <v>8.630000000000001</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3306</v>
+        <v>0.3299</v>
       </c>
       <c r="J83" t="n">
-        <v>8.265000000000001</v>
+        <v>8.2475</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1676</v>
+        <v>-0.1832</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.19</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2876</v>
+        <v>-0.3023</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.19</v>
+        <v>-7.5575</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.326</v>
+        <v>-0.3396</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.15</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0569</v>
+        <v>1.1543</v>
       </c>
       <c r="J87" t="n">
-        <v>26.4225</v>
+        <v>28.8575</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3572</v>
+        <v>0.3717</v>
       </c>
       <c r="J88" t="n">
-        <v>8.93</v>
+        <v>9.2925</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1618</v>
+        <v>-0.1574</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.045</v>
+        <v>-3.935</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2301</v>
+        <v>-0.2231</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.7525</v>
+        <v>-5.5775</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2624</v>
+        <v>-0.2536</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.56</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0104</v>
+        <v>-0.0413</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.208</v>
+        <v>-0.826</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3181</v>
+        <v>-0.3408</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.362</v>
+        <v>-6.816</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.52</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4458</v>
+        <v>-0.4622</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.916</v>
+        <v>-9.244</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.51</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4552</v>
+        <v>-0.471</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.103999999999999</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5884</v>
+        <v>-0.5945</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.768</v>
+        <v>-11.89</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2162</v>
+        <v>1.3402</v>
       </c>
       <c r="J97" t="n">
-        <v>24.324</v>
+        <v>26.804</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.6</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9325</v>
+        <v>1.0379</v>
       </c>
       <c r="J98" t="n">
-        <v>18.65</v>
+        <v>20.758</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7466</v>
+        <v>0.8357</v>
       </c>
       <c r="J99" t="n">
-        <v>14.932</v>
+        <v>16.714</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.4</v>
       </c>
       <c r="I100" t="n">
-        <v>0.697</v>
+        <v>0.7815</v>
       </c>
       <c r="J100" t="n">
-        <v>13.94</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6462</v>
+        <v>0.7258</v>
       </c>
       <c r="J101" t="n">
-        <v>12.924</v>
+        <v>14.516</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4418</v>
+        <v>0.5051</v>
       </c>
       <c r="J102" t="n">
-        <v>9.7196</v>
+        <v>11.1122</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4101</v>
+        <v>0.467</v>
       </c>
       <c r="J103" t="n">
-        <v>9.0222</v>
+        <v>10.274</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.34</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3909</v>
+        <v>0.4423</v>
       </c>
       <c r="J104" t="n">
-        <v>8.5998</v>
+        <v>9.730600000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3846</v>
+        <v>0.4333</v>
       </c>
       <c r="J105" t="n">
-        <v>8.4612</v>
+        <v>9.5326</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1932</v>
+        <v>0.2146</v>
       </c>
       <c r="J106" t="n">
-        <v>4.2504</v>
+        <v>4.7212</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0914</v>
+        <v>-0.1081</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.0108</v>
+        <v>-2.3782</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0914</v>
+        <v>-0.1081</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.0108</v>
+        <v>-2.3782</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1788</v>
+        <v>-0.1969</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.9336</v>
+        <v>-4.3318</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2462</v>
+        <v>-0.2643</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.4164</v>
+        <v>-5.8146</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3607</v>
+        <v>-0.3754</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.9354</v>
+        <v>-8.258800000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>0.86</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1044</v>
+        <v>-0.1341</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.1924</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2395</v>
+        <v>-0.2651</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.0295</v>
+        <v>-5.5671</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4014</v>
+        <v>-0.4201</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.429399999999999</v>
+        <v>-8.822100000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4106</v>
+        <v>-0.4287</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.6226</v>
+        <v>-9.002700000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.31</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6476</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.5996</v>
+        <v>-13.6227</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.87</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2382</v>
+        <v>1.3634</v>
       </c>
       <c r="J117" t="n">
-        <v>26.0022</v>
+        <v>28.6314</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9323</v>
+        <v>1.0377</v>
       </c>
       <c r="J118" t="n">
-        <v>19.5783</v>
+        <v>21.7917</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8638</v>
+        <v>0.9636</v>
       </c>
       <c r="J119" t="n">
-        <v>18.1398</v>
+        <v>20.2356</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>1.35</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6331</v>
+        <v>0.7114</v>
       </c>
       <c r="J120" t="n">
-        <v>13.2951</v>
+        <v>14.9394</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.5672</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>11.9112</v>
+        <v>13.4106</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2856</v>
+        <v>-0.3154</v>
       </c>
       <c r="J122" t="n">
-        <v>-5.4264</v>
+        <v>-5.9926</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3496</v>
+        <v>-0.3752</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.6424</v>
+        <v>-7.1288</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>0.46</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4814</v>
+        <v>-0.4987</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.146599999999999</v>
+        <v>-9.475300000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.43</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5098</v>
+        <v>-0.5249</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.686199999999999</v>
+        <v>-9.973100000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5979</v>
+        <v>-0.6057</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.3601</v>
+        <v>-11.5083</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.96</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3258</v>
+        <v>1.4576</v>
       </c>
       <c r="J127" t="n">
-        <v>25.1902</v>
+        <v>27.6944</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.227</v>
+        <v>1.3536</v>
       </c>
       <c r="J128" t="n">
-        <v>23.313</v>
+        <v>25.7184</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I129" t="n">
-        <v>1.0829</v>
+        <v>1.2007</v>
       </c>
       <c r="J129" t="n">
-        <v>20.5751</v>
+        <v>22.8133</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.38</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6643</v>
+        <v>0.7473</v>
       </c>
       <c r="J130" t="n">
-        <v>12.6217</v>
+        <v>14.1987</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0343</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.4858</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0009</v>
+        <v>0.9513</v>
       </c>
       <c r="J132" t="n">
-        <v>28.0252</v>
+        <v>26.6364</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3992</v>
+        <v>0.3975</v>
       </c>
       <c r="J133" t="n">
-        <v>11.1776</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.99</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0211</v>
+        <v>-0.0257</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.5908</v>
+        <v>-0.7196</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3466</v>
+        <v>-0.3575</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.704800000000001</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3933</v>
+        <v>-0.4026</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.0124</v>
+        <v>-11.2728</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8295</v>
+        <v>0.778</v>
       </c>
       <c r="J137" t="n">
-        <v>23.226</v>
+        <v>21.784</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6597</v>
+        <v>0.6287</v>
       </c>
       <c r="J138" t="n">
-        <v>18.4716</v>
+        <v>17.6036</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3238</v>
+        <v>0.3247</v>
       </c>
       <c r="J139" t="n">
-        <v>9.0664</v>
+        <v>9.0916</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2548</v>
+        <v>-0.2483</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.1344</v>
+        <v>-6.9524</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3756</v>
+        <v>-0.3606</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.5168</v>
+        <v>-10.0968</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1095</v>
+        <v>1.0761</v>
       </c>
       <c r="J142" t="n">
-        <v>27.7375</v>
+        <v>26.9025</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0043</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="J143" t="n">
-        <v>25.1075</v>
+        <v>23.8775</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.988</v>
+        <v>0.9377</v>
       </c>
       <c r="J144" t="n">
-        <v>24.7</v>
+        <v>23.4425</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.7632</v>
+        <v>0.7323</v>
       </c>
       <c r="J145" t="n">
-        <v>19.08</v>
+        <v>18.3075</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.18</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4783</v>
+        <v>0.4784</v>
       </c>
       <c r="J146" t="n">
-        <v>11.9575</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0376</v>
+        <v>-0.0564</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0376</v>
+        <v>-0.0564</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2387</v>
+        <v>-0.2585</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.9675</v>
+        <v>-6.4625</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4343</v>
+        <v>-0.4473</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.8575</v>
+        <v>-11.1825</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.51</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4809</v>
+        <v>-0.4911</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.0225</v>
+        <v>-12.2775</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3449</v>
+        <v>0.3337</v>
       </c>
       <c r="J152" t="n">
-        <v>7.9327</v>
+        <v>7.6751</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2804</v>
+        <v>0.2726</v>
       </c>
       <c r="J153" t="n">
-        <v>6.4492</v>
+        <v>6.2698</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2682</v>
+        <v>-0.2852</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.1686</v>
+        <v>-6.5596</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3541</v>
+        <v>-0.3685</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.144299999999999</v>
+        <v>-8.4755</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4289</v>
+        <v>-0.44</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.864699999999999</v>
+        <v>-10.12</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.6</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2359</v>
+        <v>1.2111</v>
       </c>
       <c r="J157" t="n">
-        <v>28.4257</v>
+        <v>27.8553</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.44</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0378</v>
+        <v>0.992</v>
       </c>
       <c r="J158" t="n">
-        <v>23.8694</v>
+        <v>22.816</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8963</v>
+        <v>0.8492</v>
       </c>
       <c r="J159" t="n">
-        <v>20.6149</v>
+        <v>19.5316</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6539</v>
+        <v>0.6343</v>
       </c>
       <c r="J160" t="n">
-        <v>15.0397</v>
+        <v>14.5889</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0521</v>
+        <v>0.0815</v>
       </c>
       <c r="J161" t="n">
-        <v>1.1983</v>
+        <v>1.8745</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3842</v>
+        <v>1.3597</v>
       </c>
       <c r="J162" t="n">
-        <v>37.3734</v>
+        <v>36.7119</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6424</v>
+        <v>0.6167</v>
       </c>
       <c r="J163" t="n">
-        <v>17.3448</v>
+        <v>16.6509</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4458</v>
+        <v>0.4395</v>
       </c>
       <c r="J164" t="n">
-        <v>12.0366</v>
+        <v>11.8665</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5306</v>
+        <v>-0.4984</v>
       </c>
       <c r="J165" t="n">
-        <v>-14.3262</v>
+        <v>-13.4568</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.84</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5575</v>
+        <v>-0.5226</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.0525</v>
+        <v>-14.1102</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7538</v>
+        <v>0.7154</v>
       </c>
       <c r="J167" t="n">
-        <v>20.3526</v>
+        <v>19.3158</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0133</v>
+        <v>0.0095</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3591</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2601</v>
+        <v>-0.275</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0227</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.77</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2601</v>
+        <v>-0.275</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.0227</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2893</v>
+        <v>-0.3036</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.8111</v>
+        <v>-8.1972</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1513</v>
+        <v>1.1154</v>
       </c>
       <c r="J172" t="n">
-        <v>29.9338</v>
+        <v>29.0004</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6516</v>
+        <v>0.6279</v>
       </c>
       <c r="J173" t="n">
-        <v>16.9416</v>
+        <v>16.3254</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5347</v>
+        <v>0.5226</v>
       </c>
       <c r="J174" t="n">
-        <v>13.9022</v>
+        <v>13.5876</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1812</v>
+        <v>0.1976</v>
       </c>
       <c r="J175" t="n">
-        <v>4.7112</v>
+        <v>5.1376</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1812</v>
+        <v>0.1976</v>
       </c>
       <c r="J176" t="n">
-        <v>4.7112</v>
+        <v>5.1376</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3628</v>
+        <v>0.3592</v>
       </c>
       <c r="J177" t="n">
-        <v>9.4328</v>
+        <v>9.3392</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3032</v>
+        <v>0.303</v>
       </c>
       <c r="J178" t="n">
-        <v>7.8832</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.198</v>
+        <v>0.202</v>
       </c>
       <c r="J179" t="n">
-        <v>5.148</v>
+        <v>5.252</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1814</v>
+        <v>-0.1964</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.7164</v>
+        <v>-5.1064</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.53</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.487</v>
+        <v>-0.4931</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.662</v>
+        <v>-12.8206</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2768</v>
+        <v>0.2699</v>
       </c>
       <c r="J182" t="n">
-        <v>6.6432</v>
+        <v>6.4776</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1513</v>
+        <v>-0.1682</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.6312</v>
+        <v>-4.0368</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1811</v>
+        <v>-0.1986</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.3464</v>
+        <v>-4.7664</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1909</v>
+        <v>-0.2085</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.5816</v>
+        <v>-5.004</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4021</v>
+        <v>-0.4143</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.650399999999999</v>
+        <v>-9.943199999999999</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2813</v>
+        <v>1.2578</v>
       </c>
       <c r="J187" t="n">
-        <v>30.7512</v>
+        <v>30.1872</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.4</v>
       </c>
       <c r="I188" t="n">
-        <v>0.983</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>23.592</v>
+        <v>22.3176</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5182</v>
+        <v>0.5112</v>
       </c>
       <c r="J189" t="n">
-        <v>12.4368</v>
+        <v>12.2688</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4932</v>
+        <v>0.4888</v>
       </c>
       <c r="J190" t="n">
-        <v>11.8368</v>
+        <v>11.7312</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1924</v>
+        <v>0.213</v>
       </c>
       <c r="J191" t="n">
-        <v>4.6176</v>
+        <v>5.112</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5292</v>
+        <v>0.5139</v>
       </c>
       <c r="J192" t="n">
-        <v>13.7592</v>
+        <v>13.3614</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2174</v>
+        <v>0.2215</v>
       </c>
       <c r="J193" t="n">
-        <v>5.6524</v>
+        <v>5.759</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0956</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.1736</v>
+        <v>-2.4856</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2333</v>
+        <v>-0.248</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.0658</v>
+        <v>-6.448</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3307</v>
+        <v>-0.3433</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.5982</v>
+        <v>-8.925800000000001</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0741</v>
+        <v>1.0241</v>
       </c>
       <c r="J197" t="n">
-        <v>27.9266</v>
+        <v>26.6266</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.26</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7281</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>18.9306</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4793</v>
+        <v>0.4681</v>
       </c>
       <c r="J199" t="n">
-        <v>12.4618</v>
+        <v>12.1706</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4365</v>
+        <v>-0.4155</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.349</v>
+        <v>-10.803</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6259</v>
+        <v>-0.5859</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.2734</v>
+        <v>-15.2334</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.45</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0856</v>
+        <v>1.0409</v>
       </c>
       <c r="J202" t="n">
-        <v>29.3112</v>
+        <v>28.1043</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.961</v>
+        <v>0.9008</v>
       </c>
       <c r="J203" t="n">
-        <v>25.947</v>
+        <v>24.3216</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5662</v>
+        <v>0.5493</v>
       </c>
       <c r="J204" t="n">
-        <v>15.2874</v>
+        <v>14.8311</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3943</v>
+        <v>-0.3737</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.6461</v>
+        <v>-10.0899</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3943</v>
+        <v>-0.3737</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.6461</v>
+        <v>-10.0899</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8076</v>
+        <v>0.7607</v>
       </c>
       <c r="J207" t="n">
-        <v>21.8052</v>
+        <v>20.5389</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.1195</v>
+        <v>-2.4759</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1132</v>
+        <v>-0.1279</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.0564</v>
+        <v>-3.4533</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.64</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.38</v>
+        <v>-0.3922</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.26</v>
+        <v>-10.5894</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4173</v>
+        <v>-0.4278</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.2671</v>
+        <v>-11.5506</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.77</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4046</v>
+        <v>1.3963</v>
       </c>
       <c r="J212" t="n">
-        <v>29.4966</v>
+        <v>29.3223</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1515</v>
+        <v>1.1254</v>
       </c>
       <c r="J213" t="n">
-        <v>24.1815</v>
+        <v>23.6334</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0333</v>
+        <v>0.9913</v>
       </c>
       <c r="J214" t="n">
-        <v>21.6993</v>
+        <v>20.8173</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.43</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0041</v>
+        <v>0.9587</v>
       </c>
       <c r="J215" t="n">
-        <v>21.0861</v>
+        <v>20.1327</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I216" t="n">
-        <v>0.7584</v>
+        <v>0.7332</v>
       </c>
       <c r="J216" t="n">
-        <v>15.9264</v>
+        <v>15.3972</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2546</v>
+        <v>-0.2769</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.3466</v>
+        <v>-5.8149</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2743</v>
+        <v>-0.296</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.7603</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3207</v>
+        <v>-0.3409</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.7347</v>
+        <v>-7.1589</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.62</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3654</v>
+        <v>-0.3841</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.6734</v>
+        <v>-8.0661</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3932</v>
+        <v>-0.4105</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.257199999999999</v>
+        <v>-8.6205</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6805</v>
+        <v>0.6586</v>
       </c>
       <c r="J222" t="n">
-        <v>20.415</v>
+        <v>19.758</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.07</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1729</v>
+        <v>0.1839</v>
       </c>
       <c r="J223" t="n">
-        <v>5.187</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1521</v>
+        <v>0.1633</v>
       </c>
       <c r="J224" t="n">
-        <v>4.563</v>
+        <v>4.899</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1296</v>
+        <v>-0.1405</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.888</v>
+        <v>-4.215</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1296</v>
+        <v>-0.1405</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.888</v>
+        <v>-4.215</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6563</v>
+        <v>0.6263</v>
       </c>
       <c r="J227" t="n">
-        <v>19.689</v>
+        <v>18.789</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.22</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6044</v>
       </c>
       <c r="J228" t="n">
-        <v>18.948</v>
+        <v>18.132</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2952</v>
+        <v>0.2983</v>
       </c>
       <c r="J229" t="n">
-        <v>8.856</v>
+        <v>8.949</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0716</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J230" t="n">
-        <v>2.148</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1919</v>
+        <v>-0.1878</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.757</v>
+        <v>-5.634</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1034</v>
+        <v>0.1083</v>
       </c>
       <c r="J232" t="n">
-        <v>2.6884</v>
+        <v>2.8158</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.046</v>
+        <v>-0.0552</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.196</v>
+        <v>-1.4352</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.1632</v>
+        <v>-2.4778</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1173</v>
+        <v>-0.131</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.0498</v>
+        <v>-3.406</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.15</v>
+        <v>-0.1646</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.9</v>
+        <v>-4.2796</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0914</v>
+        <v>1.0491</v>
       </c>
       <c r="J237" t="n">
-        <v>28.3764</v>
+        <v>27.2766</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.43</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0519</v>
+        <v>1.0023</v>
       </c>
       <c r="J238" t="n">
-        <v>27.3494</v>
+        <v>26.0598</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.41</v>
       </c>
       <c r="I239" t="n">
-        <v>1.0229</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J239" t="n">
-        <v>26.5954</v>
+        <v>25.1732</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.08</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2463</v>
+        <v>0.2577</v>
       </c>
       <c r="J240" t="n">
-        <v>6.4038</v>
+        <v>6.7002</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.59</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.1834</v>
+        <v>-1.0691</v>
       </c>
       <c r="J241" t="n">
-        <v>-30.7684</v>
+        <v>-27.7966</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.1932</v>
+        <v>-1.919</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.5</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.45</v>
+        <v>-0.4685</v>
       </c>
       <c r="J243" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.9015</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.47</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4777</v>
+        <v>-0.4943</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.0763</v>
+        <v>-9.3917</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.46</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4871</v>
+        <v>-0.5031</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.254899999999999</v>
+        <v>-9.5589</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.33</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.6192</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.6546</v>
+        <v>-11.7648</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.92</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5592</v>
+        <v>1.5619</v>
       </c>
       <c r="J247" t="n">
-        <v>29.6248</v>
+        <v>29.6761</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2468</v>
+        <v>1.2299</v>
       </c>
       <c r="J248" t="n">
-        <v>23.6892</v>
+        <v>23.3681</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.2355</v>
+        <v>1.2178</v>
       </c>
       <c r="J249" t="n">
-        <v>23.4745</v>
+        <v>23.1382</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.55</v>
       </c>
       <c r="I250" t="n">
-        <v>1.146</v>
+        <v>1.1208</v>
       </c>
       <c r="J250" t="n">
-        <v>21.774</v>
+        <v>21.2952</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.3568</v>
+        <v>0.3776</v>
       </c>
       <c r="J251" t="n">
-        <v>6.7792</v>
+        <v>7.1744</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.36</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7929</v>
+        <v>0.7444</v>
       </c>
       <c r="J252" t="n">
-        <v>19.0296</v>
+        <v>17.8656</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3972</v>
+        <v>0.3845</v>
       </c>
       <c r="J253" t="n">
-        <v>9.5328</v>
+        <v>9.228</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3284</v>
+        <v>-0.3433</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.8816</v>
+        <v>-8.2392</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4499</v>
+        <v>-0.4596</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.7976</v>
+        <v>-11.0304</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4683</v>
+        <v>-0.477</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.2392</v>
+        <v>-11.448</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.66</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3242</v>
+        <v>1.3023</v>
       </c>
       <c r="J257" t="n">
-        <v>31.7808</v>
+        <v>31.2552</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.4</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9886</v>
+        <v>0.9345</v>
       </c>
       <c r="J258" t="n">
-        <v>23.7264</v>
+        <v>22.428</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.27</v>
       </c>
       <c r="I259" t="n">
-        <v>0.7111</v>
+        <v>0.6829</v>
       </c>
       <c r="J259" t="n">
-        <v>17.0664</v>
+        <v>16.3896</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.04</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1027</v>
+        <v>0.1262</v>
       </c>
       <c r="J260" t="n">
-        <v>2.4648</v>
+        <v>3.0288</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1987</v>
+        <v>-0.1832</v>
       </c>
       <c r="J261" t="n">
-        <v>-4.7688</v>
+        <v>-4.3968</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4175</v>
+        <v>1.3955</v>
       </c>
       <c r="J262" t="n">
-        <v>41.1075</v>
+        <v>40.4695</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7108</v>
+        <v>0.678</v>
       </c>
       <c r="J263" t="n">
-        <v>20.6132</v>
+        <v>19.662</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6151</v>
+        <v>0.593</v>
       </c>
       <c r="J264" t="n">
-        <v>17.8379</v>
+        <v>17.197</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4788</v>
+        <v>-0.451</v>
       </c>
       <c r="J265" t="n">
-        <v>-13.8852</v>
+        <v>-13.079</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7929</v>
+        <v>-0.7311</v>
       </c>
       <c r="J266" t="n">
-        <v>-22.9941</v>
+        <v>-21.2019</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4742</v>
+        <v>0.4598</v>
       </c>
       <c r="J267" t="n">
-        <v>13.7518</v>
+        <v>13.3342</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1398</v>
+        <v>0.1418</v>
       </c>
       <c r="J268" t="n">
-        <v>4.0542</v>
+        <v>4.1122</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1352</v>
+        <v>-0.1505</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.9208</v>
+        <v>-4.3645</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.72</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3058</v>
+        <v>-0.3202</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.8682</v>
+        <v>-9.2858</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3439</v>
+        <v>-0.3572</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.973100000000001</v>
+        <v>-10.3588</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5829</v>
+        <v>0.5692</v>
       </c>
       <c r="J272" t="n">
-        <v>20.9844</v>
+        <v>20.4912</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.27</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5483</v>
+        <v>0.5376</v>
       </c>
       <c r="J273" t="n">
-        <v>19.7388</v>
+        <v>19.3536</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0315</v>
+        <v>0.039</v>
       </c>
       <c r="J274" t="n">
-        <v>1.134</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1169</v>
+        <v>-0.1276</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.2084</v>
+        <v>-4.5936</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.75</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2937</v>
+        <v>-0.3052</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.5732</v>
+        <v>-10.9872</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5135</v>
+        <v>0.4972</v>
       </c>
       <c r="J277" t="n">
-        <v>18.486</v>
+        <v>17.8992</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4876</v>
+        <v>0.4738</v>
       </c>
       <c r="J278" t="n">
-        <v>17.5536</v>
+        <v>17.0568</v>
       </c>
     </row>
     <row r="279">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0173</v>
+        <v>-0.0118</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.6228</v>
+        <v>-0.4248</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1849</v>
+        <v>-0.183</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.6564</v>
+        <v>-6.588</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0242</v>
+        <v>0.9795</v>
       </c>
       <c r="J282" t="n">
-        <v>36.8712</v>
+        <v>35.262</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3344</v>
+        <v>0.3385</v>
       </c>
       <c r="J283" t="n">
-        <v>12.0384</v>
+        <v>12.186</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.05</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1326</v>
+        <v>0.1431</v>
       </c>
       <c r="J284" t="n">
-        <v>4.7736</v>
+        <v>5.1516</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2635</v>
+        <v>-0.2756</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.486000000000001</v>
+        <v>-9.9216</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3874</v>
+        <v>-0.3963</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.9464</v>
+        <v>-14.2668</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.4</v>
       </c>
       <c r="I287" t="n">
-        <v>1.047</v>
+        <v>0.9881</v>
       </c>
       <c r="J287" t="n">
-        <v>37.692</v>
+        <v>35.5716</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8921</v>
+        <v>0.83</v>
       </c>
       <c r="J288" t="n">
-        <v>32.1156</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0127</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.4572</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2766</v>
+        <v>-0.271</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.957599999999999</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.65</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.0118</v>
+        <v>-0.926</v>
       </c>
       <c r="J291" t="n">
-        <v>-36.4248</v>
+        <v>-33.336</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3359</v>
+        <v>0.3396</v>
       </c>
       <c r="J292" t="n">
-        <v>11.4206</v>
+        <v>11.5464</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1768</v>
+        <v>0.1867</v>
       </c>
       <c r="J293" t="n">
-        <v>6.0112</v>
+        <v>6.3478</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0025</v>
+        <v>-0.0019</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0646</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0234</v>
+        <v>-0.0274</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.7956</v>
+        <v>-0.9316</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="J296" t="n">
-        <v>-2.2644</v>
+        <v>-2.5534</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.41</v>
       </c>
       <c r="I297" t="n">
-        <v>1.0665</v>
+        <v>1.0107</v>
       </c>
       <c r="J297" t="n">
-        <v>36.261</v>
+        <v>34.3638</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.1</v>
       </c>
       <c r="I298" t="n">
-        <v>0.335</v>
+        <v>0.3324</v>
       </c>
       <c r="J298" t="n">
-        <v>11.39</v>
+        <v>11.3016</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.07</v>
       </c>
       <c r="I299" t="n">
-        <v>0.248</v>
+        <v>0.2513</v>
       </c>
       <c r="J299" t="n">
-        <v>8.432</v>
+        <v>8.5442</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0633</v>
+        <v>-0.0654</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.1522</v>
+        <v>-2.2236</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0077</v>
+        <v>-0.9231</v>
       </c>
       <c r="J301" t="n">
-        <v>-34.2618</v>
+        <v>-31.3854</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.81</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5244</v>
+        <v>1.5103</v>
       </c>
       <c r="J302" t="n">
-        <v>38.11</v>
+        <v>37.7575</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7222</v>
+        <v>0.6904</v>
       </c>
       <c r="J303" t="n">
-        <v>18.055</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6757</v>
+        <v>0.6492</v>
       </c>
       <c r="J304" t="n">
-        <v>16.8925</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4342</v>
+        <v>-0.4079</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.855</v>
+        <v>-10.1975</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.625</v>
+        <v>-0.5803</v>
       </c>
       <c r="J306" t="n">
-        <v>-15.625</v>
+        <v>-14.5075</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0781</v>
+        <v>0.0726</v>
       </c>
       <c r="J307" t="n">
-        <v>1.9525</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0318</v>
+        <v>-0.0442</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.795</v>
+        <v>-1.105</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1907</v>
+        <v>-0.2084</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.7675</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2979</v>
+        <v>-0.314</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.4475</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.317</v>
+        <v>-0.3326</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.925</v>
+        <v>-8.315</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3309</v>
+        <v>0.3318</v>
       </c>
       <c r="J312" t="n">
-        <v>11.2506</v>
+        <v>11.2812</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2714</v>
+        <v>0.2754</v>
       </c>
       <c r="J313" t="n">
-        <v>9.227600000000001</v>
+        <v>9.3636</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1878</v>
+        <v>0.1946</v>
       </c>
       <c r="J314" t="n">
-        <v>6.3852</v>
+        <v>6.6164</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.99</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.0195</v>
+        <v>-0.0245</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.663</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4273</v>
+        <v>-0.4357</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.5282</v>
+        <v>-14.8138</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6495</v>
+        <v>0.6169</v>
       </c>
       <c r="J317" t="n">
-        <v>22.083</v>
+        <v>20.9746</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.21</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6243</v>
+        <v>0.5945</v>
       </c>
       <c r="J318" t="n">
-        <v>21.2262</v>
+        <v>20.213</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.154</v>
+        <v>0.1618</v>
       </c>
       <c r="J319" t="n">
-        <v>5.236</v>
+        <v>5.5012</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0112</v>
+        <v>-0.0076</v>
       </c>
       <c r="J320" t="n">
-        <v>-0.3808</v>
+        <v>-0.2584</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.637</v>
+        <v>-0.5986</v>
       </c>
       <c r="J321" t="n">
-        <v>-21.658</v>
+        <v>-20.3524</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0612</v>
+        <v>-0.0844</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.3464</v>
+        <v>-1.8568</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2298</v>
+        <v>-0.2517</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.0556</v>
+        <v>-5.5374</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>0.68</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3144</v>
+        <v>-0.3343</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.9168</v>
+        <v>-7.3546</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.64</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.351</v>
+        <v>-0.3696</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.722</v>
+        <v>-8.1312</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.46</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5192</v>
+        <v>-0.5282</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.4224</v>
+        <v>-11.6204</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.87</v>
       </c>
       <c r="I327" t="n">
-        <v>1.535</v>
+        <v>1.531</v>
       </c>
       <c r="J327" t="n">
-        <v>33.77</v>
+        <v>33.682</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.7</v>
       </c>
       <c r="I328" t="n">
-        <v>1.3386</v>
+        <v>1.3235</v>
       </c>
       <c r="J328" t="n">
-        <v>29.4492</v>
+        <v>29.117</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0531</v>
+        <v>1.0127</v>
       </c>
       <c r="J329" t="n">
-        <v>23.1682</v>
+        <v>22.2794</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.4146</v>
+        <v>0.4235</v>
       </c>
       <c r="J330" t="n">
-        <v>9.1212</v>
+        <v>9.317</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.91</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4232</v>
+        <v>-0.3877</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.3104</v>
+        <v>-8.529400000000001</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.61</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2752</v>
+        <v>1.248</v>
       </c>
       <c r="J332" t="n">
-        <v>33.1552</v>
+        <v>32.448</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.38</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9638</v>
+        <v>0.9069</v>
       </c>
       <c r="J333" t="n">
-        <v>25.0588</v>
+        <v>23.5794</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5088</v>
+        <v>0.4995</v>
       </c>
       <c r="J334" t="n">
-        <v>13.2288</v>
+        <v>12.987</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.97</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.187</v>
+        <v>-0.175</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.862</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.222</v>
+        <v>-0.2089</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.772</v>
+        <v>-5.4314</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3245</v>
+        <v>0.3187</v>
       </c>
       <c r="J337" t="n">
-        <v>8.436999999999999</v>
+        <v>8.286199999999999</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1464</v>
+        <v>0.1466</v>
       </c>
       <c r="J338" t="n">
-        <v>3.8064</v>
+        <v>3.8116</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2251</v>
+        <v>-0.2416</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.8526</v>
+        <v>-6.2816</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.74</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2839</v>
+        <v>-0.2994</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.3814</v>
+        <v>-7.7844</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2936</v>
+        <v>-0.3088</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.6336</v>
+        <v>-8.0288</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.66</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3786</v>
+        <v>1.3506</v>
       </c>
       <c r="J342" t="n">
-        <v>41.358</v>
+        <v>40.518</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.12</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3773</v>
+        <v>0.3744</v>
       </c>
       <c r="J343" t="n">
-        <v>11.319</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0328</v>
+        <v>0.0447</v>
       </c>
       <c r="J344" t="n">
-        <v>0.984</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1177</v>
+        <v>-0.116</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.531</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.8062</v>
       </c>
       <c r="J346" t="n">
-        <v>-26.265</v>
+        <v>-24.186</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.13</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3168</v>
+        <v>0.3173</v>
       </c>
       <c r="J347" t="n">
-        <v>9.504</v>
+        <v>9.519</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.09</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2353</v>
+        <v>0.2395</v>
       </c>
       <c r="J348" t="n">
-        <v>7.059</v>
+        <v>7.185</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0336</v>
+        <v>-0.0409</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.008</v>
+        <v>-1.227</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.83</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2044</v>
+        <v>-0.2189</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.132</v>
+        <v>-6.567</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.2447</v>
+        <v>-0.259</v>
       </c>
       <c r="J351" t="n">
-        <v>-7.341</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1518</v>
+        <v>0.136</v>
       </c>
       <c r="J352" t="n">
-        <v>3.795</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>0.96</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.025</v>
+        <v>-0.0429</v>
       </c>
       <c r="J353" t="n">
-        <v>-0.625</v>
+        <v>-1.0725</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.66</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.3413</v>
+        <v>-0.3585</v>
       </c>
       <c r="J354" t="n">
-        <v>-8.532500000000001</v>
+        <v>-8.9625</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.62</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3788</v>
+        <v>-0.3945</v>
       </c>
       <c r="J355" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.862500000000001</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.5</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4907</v>
+        <v>-0.5003</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.2675</v>
+        <v>-12.5075</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.78</v>
       </c>
       <c r="I357" t="n">
-        <v>1.4533</v>
+        <v>1.4413</v>
       </c>
       <c r="J357" t="n">
-        <v>36.3325</v>
+        <v>36.0325</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.77</v>
       </c>
       <c r="I358" t="n">
-        <v>1.4415</v>
+        <v>1.4288</v>
       </c>
       <c r="J358" t="n">
-        <v>36.0375</v>
+        <v>35.72</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.11</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3012</v>
+        <v>0.3157</v>
       </c>
       <c r="J359" t="n">
-        <v>7.53</v>
+        <v>7.8925</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.0788</v>
+        <v>-0.0547</v>
       </c>
       <c r="J360" t="n">
-        <v>-1.97</v>
+        <v>-1.3675</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2121</v>
+        <v>-0.1926</v>
       </c>
       <c r="J361" t="n">
-        <v>-5.3025</v>
+        <v>-4.815</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>0.88</v>
       </c>
       <c r="I362" t="n">
-        <v>-0.1144</v>
+        <v>-0.137</v>
       </c>
       <c r="J362" t="n">
-        <v>-2.1736</v>
+        <v>-2.603</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.87</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.1259</v>
+        <v>-0.1486</v>
       </c>
       <c r="J363" t="n">
-        <v>-2.3921</v>
+        <v>-2.8234</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.77</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2328</v>
+        <v>-0.254</v>
       </c>
       <c r="J364" t="n">
-        <v>-4.4232</v>
+        <v>-4.826</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.54</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.447</v>
+        <v>-0.4602</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.493</v>
+        <v>-8.7438</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.49</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4937</v>
+        <v>-0.504</v>
       </c>
       <c r="J366" t="n">
-        <v>-9.3803</v>
+        <v>-9.576000000000001</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.86</v>
       </c>
       <c r="I367" t="n">
-        <v>1.5083</v>
+        <v>1.5056</v>
       </c>
       <c r="J367" t="n">
-        <v>28.6577</v>
+        <v>28.6064</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.64</v>
       </c>
       <c r="I368" t="n">
-        <v>1.257</v>
+        <v>1.2388</v>
       </c>
       <c r="J368" t="n">
-        <v>23.883</v>
+        <v>23.5372</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.36</v>
       </c>
       <c r="I369" t="n">
-        <v>0.8712</v>
+        <v>0.832</v>
       </c>
       <c r="J369" t="n">
-        <v>16.5528</v>
+        <v>15.808</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.33</v>
       </c>
       <c r="I370" t="n">
-        <v>0.8052</v>
+        <v>0.774</v>
       </c>
       <c r="J370" t="n">
-        <v>15.2988</v>
+        <v>14.706</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>1.27</v>
       </c>
       <c r="I371" t="n">
-        <v>0.6687</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J371" t="n">
-        <v>12.7053</v>
+        <v>12.4203</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>2.03</v>
       </c>
       <c r="I372" t="n">
-        <v>1.6753</v>
+        <v>1.6844</v>
       </c>
       <c r="J372" t="n">
-        <v>28.4801</v>
+        <v>28.6348</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.99</v>
       </c>
       <c r="I373" t="n">
-        <v>1.6319</v>
+        <v>1.6389</v>
       </c>
       <c r="J373" t="n">
-        <v>27.7423</v>
+        <v>27.8613</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.44</v>
       </c>
       <c r="I374" t="n">
-        <v>1.0067</v>
+        <v>0.9644</v>
       </c>
       <c r="J374" t="n">
-        <v>17.1139</v>
+        <v>16.3948</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.27</v>
       </c>
       <c r="I375" t="n">
-        <v>0.6476</v>
+        <v>0.6389</v>
       </c>
       <c r="J375" t="n">
-        <v>11.0092</v>
+        <v>10.8613</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.27</v>
       </c>
       <c r="I376" t="n">
-        <v>0.6476</v>
+        <v>0.6389</v>
       </c>
       <c r="J376" t="n">
-        <v>11.0092</v>
+        <v>10.8613</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I377" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J377" t="n">
-        <v>1.3804</v>
+        <v>0.1496</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.55</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.4071</v>
+        <v>-0.4278</v>
       </c>
       <c r="J378" t="n">
-        <v>-6.9207</v>
+        <v>-7.2726</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.53</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.4247</v>
+        <v>-0.4444</v>
       </c>
       <c r="J379" t="n">
-        <v>-7.2199</v>
+        <v>-7.5548</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.45</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4974</v>
+        <v>-0.5125</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.4558</v>
+        <v>-8.7125</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.17</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7741</v>
+        <v>-0.7648</v>
       </c>
       <c r="J381" t="n">
-        <v>-13.1597</v>
+        <v>-13.0016</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.76</v>
       </c>
       <c r="I382" t="n">
-        <v>1.3887</v>
+        <v>1.3803</v>
       </c>
       <c r="J382" t="n">
-        <v>27.774</v>
+        <v>27.606</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.71</v>
       </c>
       <c r="I383" t="n">
-        <v>1.332</v>
+        <v>1.3199</v>
       </c>
       <c r="J383" t="n">
-        <v>26.64</v>
+        <v>26.398</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.47</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0563</v>
+        <v>1.019</v>
       </c>
       <c r="J384" t="n">
-        <v>21.126</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.47</v>
       </c>
       <c r="I385" t="n">
-        <v>1.0563</v>
+        <v>1.019</v>
       </c>
       <c r="J385" t="n">
-        <v>21.126</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.24</v>
       </c>
       <c r="I386" t="n">
-        <v>0.5904</v>
+        <v>0.5856</v>
       </c>
       <c r="J386" t="n">
-        <v>11.808</v>
+        <v>11.712</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>0.7</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.2502</v>
+        <v>-0.2807</v>
       </c>
       <c r="J387" t="n">
-        <v>-5.004</v>
+        <v>-5.614</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.59</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3662</v>
+        <v>-0.3898</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.324</v>
+        <v>-7.796</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.55</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.405</v>
+        <v>-0.4261</v>
       </c>
       <c r="J389" t="n">
-        <v>-8.1</v>
+        <v>-8.522</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.42</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.5239</v>
+        <v>-0.5374</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.478</v>
+        <v>-10.748</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.33</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.6121</v>
+        <v>-0.6182</v>
       </c>
       <c r="J391" t="n">
-        <v>-12.242</v>
+        <v>-12.364</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.47</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1455</v>
+        <v>1.1005</v>
       </c>
       <c r="J392" t="n">
-        <v>34.365</v>
+        <v>33.015</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>0.5481</v>
+        <v>0.5264</v>
       </c>
       <c r="J393" t="n">
-        <v>16.443</v>
+        <v>15.792</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.06</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2164</v>
+        <v>0.2218</v>
       </c>
       <c r="J394" t="n">
-        <v>6.492</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.84</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.5308</v>
+        <v>-0.5039</v>
       </c>
       <c r="J395" t="n">
-        <v>-15.924</v>
+        <v>-15.117</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.71</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.8638</v>
+        <v>-0.798</v>
       </c>
       <c r="J396" t="n">
-        <v>-25.914</v>
+        <v>-23.94</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.724</v>
       </c>
       <c r="J397" t="n">
-        <v>22.635</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.05</v>
       </c>
       <c r="I398" t="n">
-        <v>0.1326</v>
+        <v>0.1431</v>
       </c>
       <c r="J398" t="n">
-        <v>3.978</v>
+        <v>4.293</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.08</v>
+        <v>-0.0892</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.4</v>
+        <v>-2.676</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.91</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1274</v>
+        <v>-0.1388</v>
       </c>
       <c r="J400" t="n">
-        <v>-3.822</v>
+        <v>-4.164</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1387</v>
+        <v>-0.1504</v>
       </c>
       <c r="J401" t="n">
-        <v>-4.161</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.34</v>
       </c>
       <c r="I402" t="n">
-        <v>0.6972</v>
+        <v>0.668</v>
       </c>
       <c r="J402" t="n">
-        <v>19.5216</v>
+        <v>18.704</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3334</v>
+        <v>0.3336</v>
       </c>
       <c r="J403" t="n">
-        <v>9.3352</v>
+        <v>9.3408</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.96</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.0609</v>
+        <v>-0.0708</v>
       </c>
       <c r="J404" t="n">
-        <v>-1.7052</v>
+        <v>-1.9824</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.82</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2158</v>
+        <v>-0.23</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.0424</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.61</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4173</v>
+        <v>-0.4263</v>
       </c>
       <c r="J406" t="n">
-        <v>-11.6844</v>
+        <v>-11.9364</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.5</v>
       </c>
       <c r="I407" t="n">
-        <v>1.1747</v>
+        <v>1.1337</v>
       </c>
       <c r="J407" t="n">
-        <v>32.8916</v>
+        <v>31.7436</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.2</v>
       </c>
       <c r="I408" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5645</v>
       </c>
       <c r="J408" t="n">
-        <v>16.4696</v>
+        <v>15.806</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.93</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.2833</v>
+        <v>-0.2757</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.9324</v>
+        <v>-7.7196</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.9</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3728</v>
+        <v>-0.3586</v>
       </c>
       <c r="J410" t="n">
-        <v>-10.4384</v>
+        <v>-10.0408</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.89</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4016</v>
+        <v>-0.385</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.2448</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.79</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4904</v>
+        <v>1.4761</v>
       </c>
       <c r="J412" t="n">
-        <v>53.6544</v>
+        <v>53.1396</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.26</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J413" t="n">
-        <v>24.948</v>
+        <v>23.9688</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.3216</v>
+        <v>0.3299</v>
       </c>
       <c r="J414" t="n">
-        <v>11.5776</v>
+        <v>11.8764</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2936</v>
+        <v>0.304</v>
       </c>
       <c r="J415" t="n">
-        <v>10.5696</v>
+        <v>10.944</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.93</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3233</v>
+        <v>-0.3037</v>
       </c>
       <c r="J416" t="n">
-        <v>-11.6388</v>
+        <v>-10.9332</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3838</v>
+        <v>0.3746</v>
       </c>
       <c r="J417" t="n">
-        <v>13.8168</v>
+        <v>13.4856</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.01</v>
       </c>
       <c r="I418" t="n">
-        <v>0.0631</v>
+        <v>0.0616</v>
       </c>
       <c r="J418" t="n">
-        <v>2.2716</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.9</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1237</v>
+        <v>-0.1389</v>
       </c>
       <c r="J419" t="n">
-        <v>-4.4532</v>
+        <v>-5.0004</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.8</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.121600000000001</v>
+        <v>-8.712</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.59</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.426</v>
+        <v>-0.4362</v>
       </c>
       <c r="J421" t="n">
-        <v>-15.336</v>
+        <v>-15.7032</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>0.82</v>
       </c>
       <c r="I422" t="n">
-        <v>-0.1816</v>
+        <v>-0.2037</v>
       </c>
       <c r="J422" t="n">
-        <v>-3.9952</v>
+        <v>-4.4814</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>0.78</v>
       </c>
       <c r="I423" t="n">
-        <v>-0.2231</v>
+        <v>-0.2445</v>
       </c>
       <c r="J423" t="n">
-        <v>-4.9082</v>
+        <v>-5.379</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.2897</v>
+        <v>-0.3096</v>
       </c>
       <c r="J424" t="n">
-        <v>-6.3734</v>
+        <v>-6.8112</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.65</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.3445</v>
+        <v>-0.3628</v>
       </c>
       <c r="J425" t="n">
-        <v>-7.579</v>
+        <v>-7.9816</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.6</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.3912</v>
+        <v>-0.4073</v>
       </c>
       <c r="J426" t="n">
-        <v>-8.606400000000001</v>
+        <v>-8.960599999999999</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.76</v>
       </c>
       <c r="I427" t="n">
-        <v>1.406</v>
+        <v>1.3954</v>
       </c>
       <c r="J427" t="n">
-        <v>30.932</v>
+        <v>30.6988</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.59</v>
       </c>
       <c r="I428" t="n">
-        <v>1.2072</v>
+        <v>1.1836</v>
       </c>
       <c r="J428" t="n">
-        <v>26.5584</v>
+        <v>26.0392</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>1.47</v>
       </c>
       <c r="I429" t="n">
-        <v>1.0642</v>
+        <v>1.0263</v>
       </c>
       <c r="J429" t="n">
-        <v>23.4124</v>
+        <v>22.5786</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>1.29</v>
       </c>
       <c r="I430" t="n">
-        <v>0.7269</v>
+        <v>0.7029</v>
       </c>
       <c r="J430" t="n">
-        <v>15.9918</v>
+        <v>15.4638</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>1.05</v>
       </c>
       <c r="I431" t="n">
-        <v>0.0992</v>
+        <v>0.1323</v>
       </c>
       <c r="J431" t="n">
-        <v>2.1824</v>
+        <v>2.9106</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2261/event_2261_evp_summary.xlsx
+++ b/database/event/2261/event_2261_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8397</v>
+        <v>6.5633</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0749</v>
+        <v>2.9506</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4894</v>
+        <v>2.3841</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8397</v>
+        <v>6.5633</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6443</v>
+        <v>2.5866</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1954</v>
+        <v>3.9767</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0626</v>
+        <v>2.9776</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0626</v>
+        <v>2.9776</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1954</v>
+        <v>3.9767</v>
       </c>
       <c r="K2" t="n">
         <v>133</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.258000000000001</v>
+        <v>6.9543</v>
       </c>
       <c r="N2" t="n">
         <v>333</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.953</v>
+        <v>5.9171</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6763</v>
+        <v>2.6601</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0857</v>
+        <v>2.0897</v>
       </c>
       <c r="E3" t="n">
-        <v>5.953</v>
+        <v>5.9171</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3762</v>
+        <v>2.3775</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5768</v>
+        <v>3.5395</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4759</v>
+        <v>2.4984</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4759</v>
+        <v>2.4984</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5768</v>
+        <v>3.5395</v>
       </c>
       <c r="K3" t="n">
         <v>133</v>
@@ -575,7 +575,7 @@
         <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0527</v>
+        <v>6.0379</v>
       </c>
       <c r="N3" t="n">
         <v>333</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7852</v>
+        <v>5.5804</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6008</v>
+        <v>2.5088</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0093</v>
+        <v>1.9364</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7852</v>
+        <v>5.5804</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0158</v>
+        <v>3.9037</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7694</v>
+        <v>1.6767</v>
       </c>
       <c r="H4" t="n">
-        <v>8.355499999999999</v>
+        <v>8.2135</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5119</v>
+        <v>4.6116</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7694</v>
+        <v>1.6767</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>85</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2813</v>
+        <v>6.2883</v>
       </c>
       <c r="N4" t="n">
         <v>211</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2452</v>
+        <v>5.2116</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3581</v>
+        <v>2.343</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7635</v>
+        <v>1.7683</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2452</v>
+        <v>5.2116</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4186</v>
+        <v>1.3668</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8266</v>
+        <v>3.8448</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4186</v>
+        <v>1.3668</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4186</v>
+        <v>1.3668</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8266</v>
+        <v>3.8448</v>
       </c>
       <c r="K5" t="n">
         <v>124</v>
@@ -667,7 +667,7 @@
         <v>210</v>
       </c>
       <c r="M5" t="n">
-        <v>5.245200000000001</v>
+        <v>5.211600000000001</v>
       </c>
       <c r="N5" t="n">
         <v>334</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8565</v>
+        <v>3.8252</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7338</v>
+        <v>1.7197</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1314</v>
+        <v>1.1368</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8565</v>
+        <v>3.8252</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7872</v>
+        <v>1.7805</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0693</v>
+        <v>2.0447</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7872</v>
+        <v>1.7805</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7872</v>
+        <v>1.7805</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0693</v>
+        <v>2.0447</v>
       </c>
       <c r="K6" t="n">
         <v>124</v>
@@ -713,7 +713,7 @@
         <v>210</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8565</v>
+        <v>3.8252</v>
       </c>
       <c r="N6" t="n">
         <v>334</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8549</v>
+        <v>3.7418</v>
       </c>
       <c r="C7" t="n">
-        <v>1.733</v>
+        <v>1.6822</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1306</v>
+        <v>1.0988</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8549</v>
+        <v>3.7418</v>
       </c>
       <c r="F7" t="n">
-        <v>3.155</v>
+        <v>3.1398</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6999</v>
+        <v>0.602</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5155</v>
+        <v>5.3454</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9783</v>
+        <v>3.0013</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6999</v>
+        <v>0.602</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6782</v>
+        <v>3.6033</v>
       </c>
       <c r="N7" t="n">
         <v>211</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4983</v>
+        <v>3.3746</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5727</v>
+        <v>1.5171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9683</v>
+        <v>0.9315</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4983</v>
+        <v>3.3746</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1286</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6303</v>
+        <v>2.7189</v>
       </c>
       <c r="H8" t="n">
-        <v>8.7277</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7129</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6303</v>
+        <v>2.7189</v>
       </c>
       <c r="K8" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0826</v>
+        <v>3.3746</v>
       </c>
       <c r="N8" t="n">
-        <v>187</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4959</v>
+        <v>3.3327</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5716</v>
+        <v>1.4983</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9124</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4959</v>
+        <v>3.3327</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6641</v>
+        <v>3.9285</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8318</v>
+        <v>-0.5958</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6641</v>
+        <v>8.306800000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6641</v>
+        <v>4.664</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8318</v>
+        <v>-0.5958</v>
       </c>
       <c r="K9" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L9" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4959</v>
+        <v>4.0682</v>
       </c>
       <c r="N9" t="n">
-        <v>333</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2442</v>
+        <v>3.1644</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4585</v>
+        <v>1.4226</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8526</v>
+        <v>0.8357</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2442</v>
+        <v>3.1644</v>
       </c>
       <c r="F10" t="n">
-        <v>3.361</v>
+        <v>3.3143</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1168</v>
+        <v>-0.1499</v>
       </c>
       <c r="H10" t="n">
-        <v>6.1949</v>
+        <v>6.0009</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3452</v>
+        <v>3.3693</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1168</v>
+        <v>-0.1499</v>
       </c>
       <c r="K10" t="n">
         <v>126</v>
@@ -897,7 +897,7 @@
         <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2284</v>
+        <v>3.2194</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1575</v>
+        <v>3.0321</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4195</v>
+        <v>1.3631</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8132</v>
+        <v>0.7755</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1575</v>
+        <v>3.0321</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3608</v>
+        <v>3.2498</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2033</v>
+        <v>-0.2177</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1944</v>
+        <v>5.7586</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3449</v>
+        <v>3.2333</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2033</v>
+        <v>-0.2177</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1416</v>
+        <v>3.0156</v>
       </c>
       <c r="N11" t="n">
         <v>211</v>
@@ -952,231 +952,231 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8255</v>
+        <v>2.8373</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2703</v>
+        <v>1.2756</v>
       </c>
       <c r="D12" t="n">
-        <v>0.662</v>
+        <v>0.6867</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8255</v>
+        <v>2.8373</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7114</v>
+        <v>0.0985</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1141</v>
+        <v>2.7388</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7114</v>
+        <v>0.0985</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7114</v>
+        <v>0.0985</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1141</v>
+        <v>2.7388</v>
       </c>
       <c r="K12" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="L12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8255</v>
+        <v>2.8373</v>
       </c>
       <c r="N12" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8196</v>
+        <v>2.7863</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2676</v>
+        <v>1.2526</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6593</v>
+        <v>0.6635</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8196</v>
+        <v>2.7863</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1087</v>
+        <v>2.7837</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7109</v>
+        <v>0.0026</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1087</v>
+        <v>4.0088</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1087</v>
+        <v>2.2508</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7109</v>
+        <v>0.0026</v>
       </c>
       <c r="K13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8196</v>
+        <v>2.2534</v>
       </c>
       <c r="N13" t="n">
-        <v>334</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7559</v>
+        <v>2.6737</v>
       </c>
       <c r="C14" t="n">
-        <v>1.239</v>
+        <v>1.202</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6303</v>
+        <v>0.6122</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7559</v>
+        <v>2.6737</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7534</v>
+        <v>0.6051</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0025</v>
+        <v>2.0686</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1902</v>
+        <v>0.6051</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2627</v>
+        <v>0.6051</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0025</v>
+        <v>2.0686</v>
       </c>
       <c r="K14" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L14" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2652</v>
+        <v>2.6737</v>
       </c>
       <c r="N14" t="n">
-        <v>187</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6814</v>
+        <v>2.6696</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2055</v>
+        <v>1.2002</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5964</v>
+        <v>0.6103</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6814</v>
+        <v>2.6696</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3928</v>
+        <v>2.472</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2886</v>
+        <v>0.1976</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5121</v>
+        <v>2.8383</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5768</v>
+        <v>1.5936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2886</v>
+        <v>0.1976</v>
       </c>
       <c r="K15" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8654</v>
+        <v>1.7912</v>
       </c>
       <c r="N15" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6577</v>
+        <v>2.6667</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1948</v>
+        <v>1.1989</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5856</v>
+        <v>0.609</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6577</v>
+        <v>2.6667</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0541</v>
+        <v>2.407</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3964</v>
+        <v>0.2597</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1825</v>
+        <v>2.5661</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7985</v>
+        <v>2.6346</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3964</v>
+        <v>0.2597</v>
       </c>
       <c r="K16" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="L16" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4021</v>
+        <v>2.8943</v>
       </c>
       <c r="N16" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6559</v>
+        <v>2.6514</v>
       </c>
       <c r="C17" t="n">
-        <v>1.194</v>
+        <v>1.192</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5848</v>
+        <v>0.6021</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6559</v>
+        <v>2.6514</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6559</v>
+        <v>2.6514</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0881</v>
+        <v>3.126</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0881</v>
+        <v>3.126</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0881</v>
+        <v>3.126</v>
       </c>
       <c r="N17" t="n">
         <v>127</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6001</v>
+        <v>2.6464</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1689</v>
+        <v>1.1897</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5594</v>
+        <v>0.5998</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6001</v>
+        <v>2.6464</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3642</v>
+        <v>3.0316</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2359</v>
+        <v>-0.3852</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9062</v>
+        <v>4.9392</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5693</v>
+        <v>2.7732</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2359</v>
+        <v>-0.3852</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L18" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8052</v>
+        <v>2.388</v>
       </c>
       <c r="N18" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4855</v>
+        <v>2.4784</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1174</v>
+        <v>1.1142</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5072</v>
+        <v>0.5232</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4855</v>
+        <v>2.4784</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4855</v>
+        <v>2.4784</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7151</v>
+        <v>2.7297</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7151</v>
+        <v>2.7297</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7151</v>
+        <v>2.7297</v>
       </c>
       <c r="N19" t="n">
         <v>127</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4021</v>
+        <v>2.3442</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0799</v>
+        <v>1.0539</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4693</v>
+        <v>0.4621</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4021</v>
+        <v>2.3442</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2996</v>
+        <v>0.341</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1025</v>
+        <v>2.0032</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2996</v>
+        <v>0.341</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2996</v>
+        <v>0.341</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1025</v>
+        <v>2.0032</v>
       </c>
       <c r="K20" t="n">
         <v>133</v>
@@ -1357,7 +1357,7 @@
         <v>200</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4021</v>
+        <v>2.3442</v>
       </c>
       <c r="N20" t="n">
         <v>333</v>
@@ -1366,415 +1366,415 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2098</v>
+        <v>2.2377</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9935</v>
+        <v>1.006</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3817</v>
+        <v>0.4136</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2098</v>
+        <v>2.2377</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9743</v>
+        <v>2.3763</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7645</v>
+        <v>-0.1386</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7848</v>
+        <v>2.4792</v>
       </c>
       <c r="I21" t="n">
-        <v>3.8823</v>
+        <v>1.392</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7645</v>
+        <v>-0.1386</v>
       </c>
       <c r="K21" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1178</v>
+        <v>1.2534</v>
       </c>
       <c r="N21" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1517</v>
+        <v>2.1868</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9673</v>
+        <v>0.9831</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3553</v>
+        <v>0.3904</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1517</v>
+        <v>2.1868</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2658</v>
+        <v>2.9284</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1141</v>
+        <v>-0.7416</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5815</v>
+        <v>3.7608</v>
       </c>
       <c r="I22" t="n">
-        <v>1.394</v>
+        <v>3.8613</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1141</v>
+        <v>-0.7416</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2799</v>
+        <v>3.1197</v>
       </c>
       <c r="N22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1368</v>
+        <v>2.1605</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9606</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3485</v>
+        <v>0.3784</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1368</v>
+        <v>2.1605</v>
       </c>
       <c r="F23" t="n">
-        <v>2.259</v>
+        <v>2.4449</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1222</v>
+        <v>-0.2844</v>
       </c>
       <c r="H23" t="n">
-        <v>2.259</v>
+        <v>2.7366</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3172</v>
+        <v>1.5365</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1222</v>
+        <v>-0.2844</v>
       </c>
       <c r="K23" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M23" t="n">
-        <v>2.195</v>
+        <v>1.2521</v>
       </c>
       <c r="N23" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1362</v>
+        <v>2.0438</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9604</v>
+        <v>0.9188</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3482</v>
+        <v>0.3253</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1362</v>
+        <v>2.0438</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5947</v>
+        <v>2.0438</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5415</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5947</v>
+        <v>2.0438</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5947</v>
+        <v>2.0438</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5415</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L24" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.1362</v>
+        <v>2.0438</v>
       </c>
       <c r="N24" t="n">
-        <v>334</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0547</v>
+        <v>2.0117</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9237</v>
+        <v>0.9044</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3111</v>
+        <v>0.3106</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0547</v>
+        <v>2.0117</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0547</v>
+        <v>2.1826</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.1709</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0547</v>
+        <v>2.1826</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0547</v>
+        <v>2.2409</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.1709</v>
       </c>
       <c r="K25" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0547</v>
+        <v>2.07</v>
       </c>
       <c r="N25" t="n">
-        <v>127</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.0186</v>
+        <v>1.9342</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9075</v>
+        <v>0.8696</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2947</v>
+        <v>0.2753</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0186</v>
+        <v>1.9342</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0186</v>
+        <v>0.5294</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.4048</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0186</v>
+        <v>0.5294</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0186</v>
+        <v>0.5294</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.4048</v>
       </c>
       <c r="K26" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M26" t="n">
-        <v>2.0186</v>
+        <v>1.9342</v>
       </c>
       <c r="N26" t="n">
-        <v>146</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9944</v>
+        <v>1.8655</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8966</v>
+        <v>0.8387</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2837</v>
+        <v>0.244</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9944</v>
+        <v>1.8655</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3075</v>
+        <v>1.8707</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3131</v>
+        <v>-0.0052</v>
       </c>
       <c r="H27" t="n">
-        <v>2.7191</v>
+        <v>1.8707</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4683</v>
+        <v>1.8707</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3131</v>
+        <v>-0.0052</v>
       </c>
       <c r="K27" t="n">
         <v>129</v>
       </c>
       <c r="L27" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1552</v>
+        <v>1.8655</v>
       </c>
       <c r="N27" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.8871</v>
+        <v>1.8488</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8484</v>
+        <v>0.8312</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2348</v>
+        <v>0.2364</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8871</v>
+        <v>1.8488</v>
       </c>
       <c r="F28" t="n">
-        <v>1.8696</v>
+        <v>1.8488</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8696</v>
+        <v>1.8488</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8696</v>
+        <v>1.8488</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L28" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.8871</v>
+        <v>1.8488</v>
       </c>
       <c r="N28" t="n">
-        <v>191</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8232</v>
+        <v>0.8277</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2094</v>
+        <v>0.2329</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8311</v>
+        <v>1.8411</v>
       </c>
       <c r="N29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6792</v>
+        <v>0.6625</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0635</v>
+        <v>0.0655</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5107</v>
+        <v>1.4736</v>
       </c>
       <c r="N30" t="n">
         <v>127</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.397</v>
+        <v>1.4184</v>
       </c>
       <c r="C31" t="n">
-        <v>0.628</v>
+        <v>0.6377</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0117</v>
+        <v>0.0404</v>
       </c>
       <c r="E31" t="n">
-        <v>1.397</v>
+        <v>1.4184</v>
       </c>
       <c r="F31" t="n">
-        <v>1.397</v>
+        <v>0.8166</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.6018</v>
       </c>
       <c r="H31" t="n">
-        <v>1.397</v>
+        <v>0.8166</v>
       </c>
       <c r="I31" t="n">
-        <v>1.397</v>
+        <v>0.8166</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.6018</v>
       </c>
       <c r="K31" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M31" t="n">
-        <v>1.397</v>
+        <v>1.4184</v>
       </c>
       <c r="N31" t="n">
-        <v>146</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5916</v>
+        <v>0.5628</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0252</v>
+        <v>-0.0355</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3159</v>
+        <v>1.2518</v>
       </c>
       <c r="N32" t="n">
         <v>127</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3109</v>
+        <v>1.2328</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5893</v>
+        <v>0.5542</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0275</v>
+        <v>-0.0442</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3109</v>
+        <v>1.2328</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7618</v>
+        <v>1.2328</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5491</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7618</v>
+        <v>1.2328</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7618</v>
+        <v>1.2328</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5491</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="L33" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3109</v>
+        <v>1.2328</v>
       </c>
       <c r="N33" t="n">
-        <v>334</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4743</v>
+        <v>0.4152</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1439</v>
+        <v>-0.1851</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0551</v>
+        <v>0.9235</v>
       </c>
       <c r="N34" t="n">
         <v>126</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3635</v>
+        <v>0.3755</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2561</v>
+        <v>-0.2253</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8086</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>146</v>
@@ -2056,231 +2056,231 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7272</v>
+        <v>0.6877</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3269</v>
+        <v>0.3092</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2932</v>
+        <v>-0.2925</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7272</v>
+        <v>0.6877</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7272</v>
+        <v>1.2932</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.6055</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7272</v>
+        <v>1.2932</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7272</v>
+        <v>1.2932</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.6055</v>
       </c>
       <c r="K36" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7272</v>
+        <v>0.6876999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="C37" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3326</v>
+        <v>-0.3109</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6473</v>
       </c>
       <c r="N37" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2858</v>
+        <v>0.2743</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3348</v>
+        <v>-0.3279</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6357</v>
+        <v>0.6101</v>
       </c>
       <c r="N38" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6351</v>
+        <v>0.6035</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2855</v>
+        <v>0.2713</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3351</v>
+        <v>-0.3309</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6351</v>
+        <v>0.6035</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2105</v>
+        <v>0.6035</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5754</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2105</v>
+        <v>0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2105</v>
+        <v>0.6035</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5754</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L39" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6350999999999999</v>
+        <v>0.6035</v>
       </c>
       <c r="N39" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2751</v>
+        <v>0.2095</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3457</v>
+        <v>-0.3935</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6119</v>
+        <v>0.4659</v>
       </c>
       <c r="N40" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1971</v>
+        <v>0.1786</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4246</v>
+        <v>-0.4248</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4385</v>
+        <v>0.3972</v>
       </c>
       <c r="N41" t="n">
         <v>126</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="C42" t="n">
-        <v>0.195</v>
+        <v>0.1646</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4267</v>
+        <v>-0.439</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4338</v>
+        <v>0.3661</v>
       </c>
       <c r="N42" t="n">
         <v>146</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1494</v>
+        <v>0.1459</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4729</v>
+        <v>-0.458</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3323</v>
+        <v>0.3245</v>
       </c>
       <c r="N43" t="n">
         <v>137</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1012</v>
+        <v>0.0633</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5218</v>
+        <v>-0.5417</v>
       </c>
       <c r="E44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="F44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="I44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.225</v>
+        <v>0.1407</v>
       </c>
       <c r="N44" t="n">
         <v>132</v>
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1208</v>
+        <v>0.0425</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0543</v>
+        <v>0.0191</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5692</v>
+        <v>-0.5864</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1208</v>
+        <v>0.0425</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9419</v>
+        <v>0.9539</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.9114</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9419</v>
+        <v>0.9539</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9419</v>
+        <v>0.9539</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.9114</v>
       </c>
       <c r="K45" t="n">
         <v>129</v>
@@ -2507,7 +2507,7 @@
         <v>62</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1207999999999999</v>
+        <v>0.04249999999999998</v>
       </c>
       <c r="N45" t="n">
         <v>191</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0271</v>
+        <v>-0.0412</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6516</v>
+        <v>-0.6476</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0602</v>
+        <v>-0.0917</v>
       </c>
       <c r="N46" t="n">
         <v>127</v>
@@ -2566,31 +2566,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.2216</v>
+        <v>-0.2551</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1147</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7251</v>
+        <v>-0.722</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.2216</v>
+        <v>-0.2551</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3024</v>
+        <v>0.2399</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.524</v>
+        <v>-0.495</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3024</v>
+        <v>0.2399</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3102</v>
+        <v>0.2463</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.524</v>
+        <v>-0.495</v>
       </c>
       <c r="K47" t="n">
         <v>154</v>
@@ -2599,7 +2599,7 @@
         <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.2138</v>
+        <v>-0.2487</v>
       </c>
       <c r="N47" t="n">
         <v>199</v>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4424</v>
+        <v>-0.4606</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1989</v>
+        <v>-0.2071</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.8256</v>
+        <v>-0.8156</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.4424</v>
+        <v>-0.4606</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4917</v>
+        <v>0.468</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.9341</v>
+        <v>-0.9286</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4917</v>
+        <v>0.468</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5044</v>
+        <v>0.4805</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9341</v>
+        <v>-0.9286</v>
       </c>
       <c r="K48" t="n">
         <v>154</v>
@@ -2645,7 +2645,7 @@
         <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.4297000000000001</v>
+        <v>-0.4481</v>
       </c>
       <c r="N48" t="n">
         <v>199</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.472</v>
+        <v>-0.49</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2122</v>
+        <v>-0.2203</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8391</v>
+        <v>-0.829</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.472</v>
+        <v>-0.49</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.119</v>
+        <v>-0.49</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.353</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.119</v>
+        <v>-0.49</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.119</v>
+        <v>-0.49</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.353</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L49" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.472</v>
+        <v>-0.49</v>
       </c>
       <c r="N49" t="n">
-        <v>191</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.5412</v>
+        <v>-0.5232</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2433</v>
+        <v>-0.2352</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8706</v>
+        <v>-0.8441</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5412</v>
+        <v>-0.5232</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.5412</v>
+        <v>-0.1248</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.3984</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.5412</v>
+        <v>-0.1248</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5412</v>
+        <v>-0.1248</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.3984</v>
       </c>
       <c r="K50" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.5412</v>
+        <v>-0.5232</v>
       </c>
       <c r="N50" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2546</v>
+        <v>-0.2377</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.882</v>
+        <v>-0.8467</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.5664</v>
+        <v>-0.5288</v>
       </c>
       <c r="N51" t="n">
         <v>127</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6666</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2997</v>
+        <v>-0.308</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9277</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.6666</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2443</v>
+        <v>-0.2257</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4223</v>
+        <v>-0.4593</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2443</v>
+        <v>-0.2257</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2443</v>
+        <v>-0.2257</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4223</v>
+        <v>-0.4593</v>
       </c>
       <c r="K52" t="n">
         <v>129</v>
@@ -2829,7 +2829,7 @@
         <v>62</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.6666</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="N52" t="n">
         <v>191</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3956</v>
+        <v>-0.3832</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.0248</v>
+        <v>-0.9941</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.88</v>
+        <v>-0.8524</v>
       </c>
       <c r="N53" t="n">
         <v>137</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4181</v>
+        <v>-0.399</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.0475</v>
+        <v>-1.0101</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8875</v>
       </c>
       <c r="N54" t="n">
         <v>132</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4198</v>
+        <v>-0.4465</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.0492</v>
+        <v>-1.0582</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.9337</v>
+        <v>-0.9931</v>
       </c>
       <c r="N55" t="n">
         <v>127</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4874</v>
+        <v>-0.4801</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1177</v>
+        <v>-1.0923</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.0841</v>
+        <v>-1.0679</v>
       </c>
       <c r="N56" t="n">
         <v>132</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5999</v>
+        <v>-0.5667</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.2316</v>
+        <v>-1.1801</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.3344</v>
+        <v>-1.2606</v>
       </c>
       <c r="N57" t="n">
         <v>126</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6561</v>
+        <v>-0.6143</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2886</v>
+        <v>-1.2282</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.4595</v>
+        <v>-1.3664</v>
       </c>
       <c r="N58" t="n">
         <v>137</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6566</v>
+        <v>-0.6318</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2891</v>
+        <v>-1.246</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.4606</v>
+        <v>-1.4054</v>
       </c>
       <c r="N59" t="n">
         <v>132</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.8293</v>
+        <v>-0.7775</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4639</v>
+        <v>-1.3936</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.8447</v>
+        <v>-1.7294</v>
       </c>
       <c r="N60" t="n">
         <v>127</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.8272</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4801</v>
+        <v>-1.444</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.8802</v>
+        <v>-1.8399</v>
       </c>
       <c r="N61" t="n">
         <v>126</v>
@@ -3349,10 +3349,10 @@
         <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6201</v>
+        <v>0.5508</v>
       </c>
       <c r="J2" t="n">
-        <v>12.402</v>
+        <v>11.016</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5414</v>
       </c>
       <c r="J3" t="n">
-        <v>12.208</v>
+        <v>10.828</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.483</v>
+        <v>0.4203</v>
       </c>
       <c r="J4" t="n">
-        <v>9.66</v>
+        <v>8.406000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4312</v>
+        <v>0.3718</v>
       </c>
       <c r="J5" t="n">
-        <v>8.624000000000001</v>
+        <v>7.436</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3656</v>
+        <v>0.3109</v>
       </c>
       <c r="J6" t="n">
-        <v>7.312</v>
+        <v>6.218</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3514</v>
+        <v>0.3569</v>
       </c>
       <c r="J7" t="n">
-        <v>7.028</v>
+        <v>7.138</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>0.78</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2496</v>
+        <v>-0.2337</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.992</v>
+        <v>-4.674</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>0.74</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2861</v>
+        <v>-0.2701</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.722</v>
+        <v>-5.402</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>0.62</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3947</v>
+        <v>-0.3829</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.894</v>
+        <v>-7.658</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5266</v>
+        <v>-0.5288</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.532</v>
+        <v>-10.576</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5578</v>
+        <v>0.4981</v>
       </c>
       <c r="J12" t="n">
-        <v>16.734</v>
+        <v>14.943</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3756</v>
+        <v>0.3205</v>
       </c>
       <c r="J13" t="n">
-        <v>11.268</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.166</v>
+        <v>0.1303</v>
       </c>
       <c r="J14" t="n">
-        <v>4.98</v>
+        <v>3.909</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2146</v>
+        <v>-0.194</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.438</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.653</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1098</v>
+        <v>1.1147</v>
       </c>
       <c r="J17" t="n">
-        <v>33.294</v>
+        <v>33.441</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7927</v>
+        <v>0.7657</v>
       </c>
       <c r="J18" t="n">
-        <v>23.781</v>
+        <v>22.971</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2137</v>
+        <v>0.1833</v>
       </c>
       <c r="J19" t="n">
-        <v>6.411</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0412</v>
+        <v>0.0304</v>
       </c>
       <c r="J20" t="n">
-        <v>1.236</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7667</v>
+        <v>-0.7411</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.001</v>
+        <v>-22.233</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6194</v>
+        <v>0.5601</v>
       </c>
       <c r="J22" t="n">
-        <v>18.582</v>
+        <v>16.803</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1208</v>
+        <v>0.0921</v>
       </c>
       <c r="J23" t="n">
-        <v>3.624</v>
+        <v>2.763</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0451</v>
+        <v>-0.034</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.353</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0607</v>
+        <v>-0.0474</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.821</v>
+        <v>-1.422</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1939</v>
+        <v>-0.1733</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.817</v>
+        <v>-5.199</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7339</v>
+        <v>0.7028</v>
       </c>
       <c r="J27" t="n">
-        <v>22.017</v>
+        <v>21.084</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4923</v>
+        <v>0.4527</v>
       </c>
       <c r="J28" t="n">
-        <v>14.769</v>
+        <v>13.581</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3242</v>
+        <v>0.2872</v>
       </c>
       <c r="J29" t="n">
-        <v>9.726000000000001</v>
+        <v>8.616</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2445</v>
+        <v>0.2115</v>
       </c>
       <c r="J30" t="n">
-        <v>7.335</v>
+        <v>6.345</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3885</v>
+        <v>-0.3457</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.655</v>
+        <v>-10.371</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5744</v>
       </c>
       <c r="J32" t="n">
-        <v>20.3762</v>
+        <v>19.5296</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4026</v>
+        <v>0.3475</v>
       </c>
       <c r="J33" t="n">
-        <v>13.6884</v>
+        <v>11.815</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2447</v>
+        <v>-0.2249</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.319800000000001</v>
+        <v>-7.6466</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3027</v>
+        <v>-0.2847</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.2918</v>
+        <v>-9.6798</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.465</v>
+        <v>-0.4611</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.81</v>
+        <v>-15.6774</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9245</v>
+        <v>0.91</v>
       </c>
       <c r="J37" t="n">
-        <v>31.433</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5775</v>
+        <v>0.5698</v>
       </c>
       <c r="J38" t="n">
-        <v>19.635</v>
+        <v>19.3732</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4832</v>
+        <v>0.4654</v>
       </c>
       <c r="J39" t="n">
-        <v>16.4288</v>
+        <v>15.8236</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4664</v>
+        <v>0.4428</v>
       </c>
       <c r="J40" t="n">
-        <v>15.8576</v>
+        <v>15.0552</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>1.05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1654</v>
+        <v>0.1394</v>
       </c>
       <c r="J41" t="n">
-        <v>5.6236</v>
+        <v>4.7396</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.6</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6373</v>
+        <v>0.5968</v>
       </c>
       <c r="J42" t="n">
-        <v>14.0206</v>
+        <v>13.1296</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>1.37</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4674</v>
+        <v>0.4131</v>
       </c>
       <c r="J43" t="n">
-        <v>10.2828</v>
+        <v>9.088200000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4046</v>
+        <v>0.3454</v>
       </c>
       <c r="J44" t="n">
-        <v>8.901199999999999</v>
+        <v>7.5988</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3266</v>
+        <v>0.2739</v>
       </c>
       <c r="J45" t="n">
-        <v>7.1852</v>
+        <v>6.0258</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1151</v>
+        <v>0.0871</v>
       </c>
       <c r="J46" t="n">
-        <v>2.5322</v>
+        <v>1.9162</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5658</v>
+        <v>0.615</v>
       </c>
       <c r="J47" t="n">
-        <v>12.4476</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.278</v>
+        <v>-0.2616</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.116</v>
+        <v>-5.7552</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>0.62</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3961</v>
+        <v>-0.3844</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.7142</v>
+        <v>-8.456799999999999</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4317</v>
+        <v>-0.423</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.497400000000001</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.53</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4757</v>
+        <v>-0.4716</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4654</v>
+        <v>-10.3752</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.27</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>15.4512</v>
+        <v>14.6595</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.1117</v>
+        <v>-2.6361</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1192</v>
+        <v>-0.1019</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.4568</v>
+        <v>-2.9551</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2272</v>
+        <v>-0.2069</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.5888</v>
+        <v>-6.0001</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.78</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2668</v>
+        <v>-0.2474</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.7372</v>
+        <v>-7.1746</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7378</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>21.3962</v>
+        <v>20.9467</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5535</v>
+        <v>0.5446</v>
       </c>
       <c r="J58" t="n">
-        <v>16.0515</v>
+        <v>15.7934</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5535</v>
+        <v>0.5446</v>
       </c>
       <c r="J59" t="n">
-        <v>16.0515</v>
+        <v>15.7934</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.236</v>
+        <v>0.2053</v>
       </c>
       <c r="J60" t="n">
-        <v>6.844</v>
+        <v>5.9537</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2892</v>
+        <v>-0.2492</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.386799999999999</v>
+        <v>-7.2268</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3943</v>
+        <v>0.3387</v>
       </c>
       <c r="J62" t="n">
-        <v>11.829</v>
+        <v>10.161</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>1.07</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2012</v>
+        <v>0.1595</v>
       </c>
       <c r="J63" t="n">
-        <v>6.036</v>
+        <v>4.785</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0221</v>
+        <v>-0.0164</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.663</v>
+        <v>-0.492</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2672</v>
+        <v>-0.2478</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.016</v>
+        <v>-7.434</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.315</v>
+        <v>-0.2977</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.449999999999999</v>
+        <v>-8.930999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>1.59</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1062</v>
+        <v>1.1012</v>
       </c>
       <c r="J67" t="n">
-        <v>33.186</v>
+        <v>33.036</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5452</v>
+        <v>0.5346</v>
       </c>
       <c r="J68" t="n">
-        <v>16.356</v>
+        <v>16.038</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2445</v>
+        <v>0.2115</v>
       </c>
       <c r="J69" t="n">
-        <v>7.335</v>
+        <v>6.345</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3075</v>
+        <v>-0.2662</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.225</v>
+        <v>-7.986</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.7615</v>
       </c>
       <c r="J71" t="n">
-        <v>-23.574</v>
+        <v>-22.845</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0246</v>
+        <v>0.019</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6888</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0459</v>
+        <v>-0.0366</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.2852</v>
+        <v>-1.0248</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1584</v>
+        <v>-0.1411</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.4352</v>
+        <v>-3.9508</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3153</v>
+        <v>-0.2981</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.8284</v>
+        <v>-8.3468</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3153</v>
+        <v>-0.2981</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.8284</v>
+        <v>-8.3468</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6474</v>
+        <v>0.6341</v>
       </c>
       <c r="J77" t="n">
-        <v>18.1272</v>
+        <v>17.7548</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5747</v>
       </c>
       <c r="J78" t="n">
-        <v>16.3856</v>
+        <v>16.0916</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4362</v>
+        <v>0.4022</v>
       </c>
       <c r="J79" t="n">
-        <v>12.2136</v>
+        <v>11.2616</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3172</v>
+        <v>0.2829</v>
       </c>
       <c r="J80" t="n">
-        <v>8.881600000000001</v>
+        <v>7.9212</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I81" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J81" t="n">
-        <v>0.952</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3488</v>
+        <v>0.2958</v>
       </c>
       <c r="J82" t="n">
-        <v>8.720000000000001</v>
+        <v>7.395</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3299</v>
+        <v>0.2779</v>
       </c>
       <c r="J83" t="n">
-        <v>8.2475</v>
+        <v>6.9475</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1832</v>
+        <v>-0.1636</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.58</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3023</v>
+        <v>-0.2843</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.5575</v>
+        <v>-7.1075</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3396</v>
+        <v>-0.3237</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.49</v>
+        <v>-8.092499999999999</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>1.63</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1543</v>
+        <v>1.1518</v>
       </c>
       <c r="J87" t="n">
-        <v>28.8575</v>
+        <v>28.795</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3717</v>
+        <v>0.3342</v>
       </c>
       <c r="J88" t="n">
-        <v>9.2925</v>
+        <v>8.355</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1574</v>
+        <v>-0.126</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.935</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2231</v>
+        <v>-0.186</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.5775</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2536</v>
+        <v>-0.2147</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.34</v>
+        <v>-5.3675</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>0.93</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0413</v>
+        <v>-0.0164</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.826</v>
+        <v>-0.328</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3408</v>
+        <v>-0.3314</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.816</v>
+        <v>-6.628</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>0.52</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4622</v>
+        <v>-0.4573</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.244</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>0.51</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.471</v>
+        <v>-0.4667</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.42</v>
+        <v>-9.334</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5945</v>
+        <v>-0.6049</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.89</v>
+        <v>-12.098</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3402</v>
+        <v>1.3458</v>
       </c>
       <c r="J97" t="n">
-        <v>26.804</v>
+        <v>26.916</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.6</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0379</v>
+        <v>1.0319</v>
       </c>
       <c r="J98" t="n">
-        <v>20.758</v>
+        <v>20.638</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8357</v>
+        <v>0.8293</v>
       </c>
       <c r="J99" t="n">
-        <v>16.714</v>
+        <v>16.586</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>1.4</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7815</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>15.63</v>
+        <v>15.514</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7258</v>
+        <v>0.7206</v>
       </c>
       <c r="J101" t="n">
-        <v>14.516</v>
+        <v>14.412</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5051</v>
+        <v>0.4612</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1122</v>
+        <v>10.1464</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.467</v>
+        <v>0.4128</v>
       </c>
       <c r="J103" t="n">
-        <v>10.274</v>
+        <v>9.0816</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>1.34</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4423</v>
+        <v>0.3838</v>
       </c>
       <c r="J104" t="n">
-        <v>9.730600000000001</v>
+        <v>8.4436</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4333</v>
+        <v>0.3742</v>
       </c>
       <c r="J105" t="n">
-        <v>9.5326</v>
+        <v>8.2324</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2146</v>
+        <v>0.1734</v>
       </c>
       <c r="J106" t="n">
-        <v>4.7212</v>
+        <v>3.8148</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1081</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.3782</v>
+        <v>-2.0636</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1081</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.3782</v>
+        <v>-2.0636</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1969</v>
+        <v>-0.1795</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.3318</v>
+        <v>-3.949</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2643</v>
+        <v>-0.2462</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.8146</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3754</v>
+        <v>-0.3619</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.258800000000001</v>
+        <v>-7.9618</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>0.86</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1341</v>
+        <v>-0.1137</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.8161</v>
+        <v>-2.3877</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2651</v>
+        <v>-0.252</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.5671</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4201</v>
+        <v>-0.4125</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.822100000000001</v>
+        <v>-8.6625</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4287</v>
+        <v>-0.4216</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.002700000000001</v>
+        <v>-8.8536</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.31</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6687</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.6227</v>
+        <v>-14.0427</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.87</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3634</v>
+        <v>1.3706</v>
       </c>
       <c r="J117" t="n">
-        <v>28.6314</v>
+        <v>28.7826</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0377</v>
+        <v>1.0318</v>
       </c>
       <c r="J118" t="n">
-        <v>21.7917</v>
+        <v>21.6678</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9636</v>
+        <v>0.957</v>
       </c>
       <c r="J119" t="n">
-        <v>20.2356</v>
+        <v>20.097</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>1.35</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7114</v>
+        <v>0.7064</v>
       </c>
       <c r="J120" t="n">
-        <v>14.9394</v>
+        <v>14.8344</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6351</v>
       </c>
       <c r="J121" t="n">
-        <v>13.4106</v>
+        <v>13.3371</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3154</v>
+        <v>-0.3043</v>
       </c>
       <c r="J122" t="n">
-        <v>-5.9926</v>
+        <v>-5.7817</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3752</v>
+        <v>-0.3697</v>
       </c>
       <c r="J123" t="n">
-        <v>-7.1288</v>
+        <v>-7.0243</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>0.46</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4987</v>
+        <v>-0.4989</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.475300000000001</v>
+        <v>-9.479100000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.43</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5249</v>
+        <v>-0.5269</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.973100000000001</v>
+        <v>-10.0111</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.34</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6057</v>
+        <v>-0.6169</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.5083</v>
+        <v>-11.7211</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.96</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4576</v>
+        <v>1.472</v>
       </c>
       <c r="J127" t="n">
-        <v>27.6944</v>
+        <v>27.968</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3536</v>
+        <v>1.3611</v>
       </c>
       <c r="J128" t="n">
-        <v>25.7184</v>
+        <v>25.8609</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I129" t="n">
-        <v>1.2007</v>
+        <v>1.2009</v>
       </c>
       <c r="J129" t="n">
-        <v>22.8133</v>
+        <v>22.8171</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.38</v>
       </c>
       <c r="I130" t="n">
-        <v>0.7473</v>
+        <v>0.7428</v>
       </c>
       <c r="J130" t="n">
-        <v>14.1987</v>
+        <v>14.1132</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0477</v>
       </c>
       <c r="J131" t="n">
-        <v>1.4858</v>
+        <v>0.9063</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9513</v>
+        <v>0.9124</v>
       </c>
       <c r="J132" t="n">
-        <v>26.6364</v>
+        <v>25.5472</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3975</v>
+        <v>0.3413</v>
       </c>
       <c r="J133" t="n">
-        <v>11.13</v>
+        <v>9.5564</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>0.99</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0257</v>
+        <v>-0.0184</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.7196</v>
+        <v>-0.5152</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3575</v>
+        <v>-0.3436</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.01</v>
+        <v>-9.620799999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4026</v>
+        <v>-0.3927</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.2728</v>
+        <v>-10.9956</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.778</v>
+        <v>0.7498</v>
       </c>
       <c r="J137" t="n">
-        <v>21.784</v>
+        <v>20.9944</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6287</v>
+        <v>0.592</v>
       </c>
       <c r="J138" t="n">
-        <v>17.6036</v>
+        <v>16.576</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3247</v>
+        <v>0.2874</v>
       </c>
       <c r="J139" t="n">
-        <v>9.0916</v>
+        <v>8.0472</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2483</v>
+        <v>-0.2095</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.9524</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3606</v>
+        <v>-0.318</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.0968</v>
+        <v>-8.904</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0761</v>
+        <v>1.0877</v>
       </c>
       <c r="J142" t="n">
-        <v>26.9025</v>
+        <v>27.1925</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.42</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9505</v>
       </c>
       <c r="J143" t="n">
-        <v>23.8775</v>
+        <v>23.7625</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9377</v>
+        <v>0.931</v>
       </c>
       <c r="J144" t="n">
-        <v>23.4425</v>
+        <v>23.275</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.7323</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>18.3075</v>
+        <v>17.805</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.18</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4784</v>
+        <v>0.4482</v>
       </c>
       <c r="J146" t="n">
-        <v>11.96</v>
+        <v>11.205</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0564</v>
+        <v>-0.0437</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.41</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0564</v>
+        <v>-0.0437</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.41</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.77</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2585</v>
+        <v>-0.2427</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.4625</v>
+        <v>-6.0675</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4473</v>
+        <v>-0.4399</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.1825</v>
+        <v>-10.9975</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.51</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4911</v>
+        <v>-0.4887</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.2775</v>
+        <v>-12.2175</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3337</v>
+        <v>0.2846</v>
       </c>
       <c r="J152" t="n">
-        <v>7.6751</v>
+        <v>6.5458</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2726</v>
+        <v>0.227</v>
       </c>
       <c r="J153" t="n">
-        <v>6.2698</v>
+        <v>5.221</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.75</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2852</v>
+        <v>-0.2671</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.5596</v>
+        <v>-6.1433</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3685</v>
+        <v>-0.3545</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.4755</v>
+        <v>-8.153499999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.58</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.44</v>
+        <v>-0.4324</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.12</v>
+        <v>-9.9452</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.6</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2111</v>
+        <v>1.2267</v>
       </c>
       <c r="J157" t="n">
-        <v>27.8553</v>
+        <v>28.2141</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.44</v>
       </c>
       <c r="I158" t="n">
-        <v>0.992</v>
+        <v>0.9915</v>
       </c>
       <c r="J158" t="n">
-        <v>22.816</v>
+        <v>22.8045</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.36</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8492</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>19.5316</v>
+        <v>19.1866</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6343</v>
+        <v>0.6087</v>
       </c>
       <c r="J160" t="n">
-        <v>14.5889</v>
+        <v>14.0001</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0815</v>
+        <v>0.0601</v>
       </c>
       <c r="J161" t="n">
-        <v>1.8745</v>
+        <v>1.3823</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3597</v>
+        <v>1.3859</v>
       </c>
       <c r="J162" t="n">
-        <v>36.7119</v>
+        <v>37.4193</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6167</v>
+        <v>0.5815</v>
       </c>
       <c r="J163" t="n">
-        <v>16.6509</v>
+        <v>15.7005</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4395</v>
+        <v>0.4024</v>
       </c>
       <c r="J164" t="n">
-        <v>11.8665</v>
+        <v>10.8648</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4984</v>
+        <v>-0.4577</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.4568</v>
+        <v>-12.3579</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.84</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5226</v>
+        <v>-0.4828</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.1102</v>
+        <v>-13.0356</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.36</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7154</v>
+        <v>0.6637</v>
       </c>
       <c r="J167" t="n">
-        <v>19.3158</v>
+        <v>17.9199</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0095</v>
+        <v>0.006</v>
       </c>
       <c r="J168" t="n">
-        <v>0.2565</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.77</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.275</v>
+        <v>-0.2559</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.425</v>
+        <v>-6.9093</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.77</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.275</v>
+        <v>-0.2559</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.425</v>
+        <v>-6.9093</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3036</v>
+        <v>-0.2857</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.1972</v>
+        <v>-7.7139</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1154</v>
+        <v>1.1273</v>
       </c>
       <c r="J172" t="n">
-        <v>29.0004</v>
+        <v>29.3098</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6279</v>
+        <v>0.5962</v>
       </c>
       <c r="J173" t="n">
-        <v>16.3254</v>
+        <v>15.5012</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5226</v>
+        <v>0.4888</v>
       </c>
       <c r="J174" t="n">
-        <v>13.5876</v>
+        <v>12.7088</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1976</v>
+        <v>0.1697</v>
       </c>
       <c r="J175" t="n">
-        <v>5.1376</v>
+        <v>4.4122</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1976</v>
+        <v>0.1697</v>
       </c>
       <c r="J176" t="n">
-        <v>5.1376</v>
+        <v>4.4122</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3592</v>
+        <v>0.3051</v>
       </c>
       <c r="J177" t="n">
-        <v>9.3392</v>
+        <v>7.9326</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.303</v>
+        <v>0.2522</v>
       </c>
       <c r="J178" t="n">
-        <v>7.878</v>
+        <v>6.5572</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.202</v>
+        <v>0.1602</v>
       </c>
       <c r="J179" t="n">
-        <v>5.252</v>
+        <v>4.1652</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1964</v>
+        <v>-0.1761</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.1064</v>
+        <v>-4.5786</v>
       </c>
     </row>
     <row r="181">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2699</v>
+        <v>0.2242</v>
       </c>
       <c r="J182" t="n">
-        <v>6.4776</v>
+        <v>5.3808</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1682</v>
+        <v>-0.1509</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.0368</v>
+        <v>-3.6216</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1986</v>
+        <v>-0.1803</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.7664</v>
+        <v>-4.3272</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>0.83</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2085</v>
+        <v>-0.19</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.004</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.61</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4143</v>
+        <v>-0.4041</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.943199999999999</v>
+        <v>-9.698399999999999</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2578</v>
+        <v>1.2751</v>
       </c>
       <c r="J187" t="n">
-        <v>30.1872</v>
+        <v>30.6024</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.4</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9191</v>
       </c>
       <c r="J188" t="n">
-        <v>22.3176</v>
+        <v>22.0584</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.19</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5112</v>
+        <v>0.4805</v>
       </c>
       <c r="J189" t="n">
-        <v>12.2688</v>
+        <v>11.532</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4888</v>
+        <v>0.4576</v>
       </c>
       <c r="J190" t="n">
-        <v>11.7312</v>
+        <v>10.9824</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I191" t="n">
-        <v>0.213</v>
+        <v>0.1838</v>
       </c>
       <c r="J191" t="n">
-        <v>5.112</v>
+        <v>4.4112</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5139</v>
+        <v>0.4559</v>
       </c>
       <c r="J192" t="n">
-        <v>13.3614</v>
+        <v>11.8534</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2215</v>
+        <v>0.1776</v>
       </c>
       <c r="J193" t="n">
-        <v>5.759</v>
+        <v>4.6176</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0956</v>
+        <v>-0.0799</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.4856</v>
+        <v>-2.0774</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.248</v>
+        <v>-0.228</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.448</v>
+        <v>-5.928</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3433</v>
+        <v>-0.3278</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.925800000000001</v>
+        <v>-8.5228</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0241</v>
+        <v>1.0257</v>
       </c>
       <c r="J197" t="n">
-        <v>26.6266</v>
+        <v>26.6682</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.26</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6565</v>
       </c>
       <c r="J198" t="n">
-        <v>17.94</v>
+        <v>17.069</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.16</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4681</v>
+        <v>0.4286</v>
       </c>
       <c r="J199" t="n">
-        <v>12.1706</v>
+        <v>11.1436</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4155</v>
+        <v>-0.3728</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.803</v>
+        <v>-9.6928</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5859</v>
+        <v>-0.5478</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.2334</v>
+        <v>-14.2428</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>1.45</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0409</v>
+        <v>1.0449</v>
       </c>
       <c r="J202" t="n">
-        <v>28.1043</v>
+        <v>28.2123</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9008</v>
+        <v>0.8831</v>
       </c>
       <c r="J203" t="n">
-        <v>24.3216</v>
+        <v>23.8437</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5493</v>
+        <v>0.5133</v>
       </c>
       <c r="J204" t="n">
-        <v>14.8311</v>
+        <v>13.8591</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.9</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3737</v>
+        <v>-0.332</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.0899</v>
+        <v>-8.964</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.9</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3737</v>
+        <v>-0.332</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.0899</v>
+        <v>-8.964</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.38</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7607</v>
+        <v>0.7145</v>
       </c>
       <c r="J207" t="n">
-        <v>20.5389</v>
+        <v>19.2915</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.4759</v>
+        <v>-2.0979</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>0.91</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1279</v>
+        <v>-0.1112</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.4533</v>
+        <v>-3.0024</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>0.64</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3922</v>
+        <v>-0.3803</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.5894</v>
+        <v>-10.2681</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>0.6</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4278</v>
+        <v>-0.4193</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.5506</v>
+        <v>-11.3211</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.77</v>
       </c>
       <c r="I212" t="n">
-        <v>1.3963</v>
+        <v>1.422</v>
       </c>
       <c r="J212" t="n">
-        <v>29.3223</v>
+        <v>29.862</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1254</v>
+        <v>1.1435</v>
       </c>
       <c r="J213" t="n">
-        <v>23.6334</v>
+        <v>24.0135</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9913</v>
+        <v>0.9982</v>
       </c>
       <c r="J214" t="n">
-        <v>20.8173</v>
+        <v>20.9622</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>1.43</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9587</v>
+        <v>0.9613</v>
       </c>
       <c r="J215" t="n">
-        <v>20.1327</v>
+        <v>20.1873</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I216" t="n">
-        <v>0.7332</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>15.3972</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2769</v>
+        <v>-0.2636</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.8149</v>
+        <v>-5.5356</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.296</v>
+        <v>-0.2831</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.216</v>
+        <v>-5.9451</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3409</v>
+        <v>-0.3288</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.1589</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.62</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3841</v>
+        <v>-0.3731</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.0661</v>
+        <v>-7.8351</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4105</v>
+        <v>-0.4008</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.6205</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6586</v>
+        <v>0.5996</v>
       </c>
       <c r="J222" t="n">
-        <v>19.758</v>
+        <v>17.988</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.07</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1839</v>
+        <v>0.1468</v>
       </c>
       <c r="J223" t="n">
-        <v>5.517</v>
+        <v>4.404</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1633</v>
+        <v>0.1289</v>
       </c>
       <c r="J224" t="n">
-        <v>4.899</v>
+        <v>3.867</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1405</v>
+        <v>-0.1209</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.215</v>
+        <v>-3.627</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1405</v>
+        <v>-0.1209</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.215</v>
+        <v>-3.627</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6263</v>
+        <v>0.5898</v>
       </c>
       <c r="J227" t="n">
-        <v>18.789</v>
+        <v>17.694</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>1.22</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6044</v>
+        <v>0.5671</v>
       </c>
       <c r="J228" t="n">
-        <v>18.132</v>
+        <v>17.013</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2983</v>
+        <v>0.2626</v>
       </c>
       <c r="J229" t="n">
-        <v>8.949</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0668</v>
       </c>
       <c r="J230" t="n">
-        <v>2.535</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1878</v>
+        <v>-0.1533</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.634</v>
+        <v>-4.599</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1083</v>
+        <v>0.0798</v>
       </c>
       <c r="J232" t="n">
-        <v>2.8158</v>
+        <v>2.0748</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0552</v>
+        <v>-0.0441</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.4352</v>
+        <v>-1.1466</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.4778</v>
+        <v>-2.0748</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.131</v>
+        <v>-0.1129</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.406</v>
+        <v>-2.9354</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1646</v>
+        <v>-0.145</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.2796</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0491</v>
+        <v>1.0543</v>
       </c>
       <c r="J237" t="n">
-        <v>27.2766</v>
+        <v>27.4118</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.43</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0023</v>
+        <v>0.9997</v>
       </c>
       <c r="J238" t="n">
-        <v>26.0598</v>
+        <v>25.9922</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>1.41</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9597</v>
       </c>
       <c r="J239" t="n">
-        <v>25.1732</v>
+        <v>24.9522</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>1.08</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2577</v>
+        <v>0.2266</v>
       </c>
       <c r="J240" t="n">
-        <v>6.7002</v>
+        <v>5.8916</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.59</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.0691</v>
+        <v>-1.0802</v>
       </c>
       <c r="J241" t="n">
-        <v>-27.7966</v>
+        <v>-28.0852</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.101</v>
+        <v>-0.0688</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.919</v>
+        <v>-1.3072</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>0.5</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.4685</v>
+        <v>-0.4663</v>
       </c>
       <c r="J243" t="n">
-        <v>-8.9015</v>
+        <v>-8.8597</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.47</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4943</v>
+        <v>-0.4934</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.3917</v>
+        <v>-9.374599999999999</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.46</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5031</v>
+        <v>-0.5027</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.5589</v>
+        <v>-9.551299999999999</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.33</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6192</v>
+        <v>-0.6327</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.7648</v>
+        <v>-12.0213</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.92</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5619</v>
+        <v>1.5985</v>
       </c>
       <c r="J247" t="n">
-        <v>29.6761</v>
+        <v>30.3715</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2299</v>
+        <v>1.2518</v>
       </c>
       <c r="J248" t="n">
-        <v>23.3681</v>
+        <v>23.7842</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.2178</v>
+        <v>1.2395</v>
       </c>
       <c r="J249" t="n">
-        <v>23.1382</v>
+        <v>23.5505</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.55</v>
       </c>
       <c r="I250" t="n">
-        <v>1.1208</v>
+        <v>1.1413</v>
       </c>
       <c r="J250" t="n">
-        <v>21.2952</v>
+        <v>21.6847</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>1.15</v>
       </c>
       <c r="I251" t="n">
-        <v>0.3776</v>
+        <v>0.3436</v>
       </c>
       <c r="J251" t="n">
-        <v>7.1744</v>
+        <v>6.5284</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.36</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7444</v>
+        <v>0.7007</v>
       </c>
       <c r="J252" t="n">
-        <v>17.8656</v>
+        <v>16.8168</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3845</v>
+        <v>0.3324</v>
       </c>
       <c r="J253" t="n">
-        <v>9.228</v>
+        <v>7.9776</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3433</v>
+        <v>-0.3276</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.2392</v>
+        <v>-7.8624</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4596</v>
+        <v>-0.4543</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.0304</v>
+        <v>-10.9032</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.477</v>
+        <v>-0.4738</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.448</v>
+        <v>-11.3712</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.66</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3023</v>
+        <v>1.3218</v>
       </c>
       <c r="J257" t="n">
-        <v>31.2552</v>
+        <v>31.7232</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.4</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9345</v>
+        <v>0.9232</v>
       </c>
       <c r="J258" t="n">
-        <v>22.428</v>
+        <v>22.1568</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.27</v>
       </c>
       <c r="I259" t="n">
-        <v>0.6829</v>
+        <v>0.656</v>
       </c>
       <c r="J259" t="n">
-        <v>16.3896</v>
+        <v>15.744</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>1.04</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1262</v>
+        <v>0.1026</v>
       </c>
       <c r="J260" t="n">
-        <v>3.0288</v>
+        <v>2.4624</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1832</v>
+        <v>-0.1528</v>
       </c>
       <c r="J261" t="n">
-        <v>-4.3968</v>
+        <v>-3.6672</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3955</v>
+        <v>1.4241</v>
       </c>
       <c r="J262" t="n">
-        <v>40.4695</v>
+        <v>41.2989</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.26</v>
       </c>
       <c r="I263" t="n">
-        <v>0.678</v>
+        <v>0.6456</v>
       </c>
       <c r="J263" t="n">
-        <v>19.662</v>
+        <v>18.7224</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.593</v>
+        <v>0.5577</v>
       </c>
       <c r="J264" t="n">
-        <v>17.197</v>
+        <v>16.1733</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.451</v>
+        <v>-0.4095</v>
       </c>
       <c r="J265" t="n">
-        <v>-13.079</v>
+        <v>-11.8755</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7311</v>
+        <v>-0.7037</v>
       </c>
       <c r="J266" t="n">
-        <v>-21.2019</v>
+        <v>-20.4073</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.2</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4598</v>
+        <v>0.4038</v>
       </c>
       <c r="J267" t="n">
-        <v>13.3342</v>
+        <v>11.7102</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1418</v>
+        <v>0.108</v>
       </c>
       <c r="J268" t="n">
-        <v>4.1122</v>
+        <v>3.132</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1505</v>
+        <v>-0.1323</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.3645</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.72</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3202</v>
+        <v>-0.3032</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.2858</v>
+        <v>-8.7928</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3572</v>
+        <v>-0.3425</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.3588</v>
+        <v>-9.932499999999999</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5692</v>
+        <v>0.5094</v>
       </c>
       <c r="J272" t="n">
-        <v>20.4912</v>
+        <v>18.3384</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.27</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5376</v>
+        <v>0.4779</v>
       </c>
       <c r="J273" t="n">
-        <v>19.3536</v>
+        <v>17.2044</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.039</v>
+        <v>0.0272</v>
       </c>
       <c r="J274" t="n">
-        <v>1.404</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1276</v>
+        <v>-0.1086</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.5936</v>
+        <v>-3.9096</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.75</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3052</v>
+        <v>-0.2879</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.9872</v>
+        <v>-10.3644</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.17</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4972</v>
+        <v>0.4566</v>
       </c>
       <c r="J277" t="n">
-        <v>17.8992</v>
+        <v>16.4376</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4738</v>
+        <v>0.433</v>
       </c>
       <c r="J278" t="n">
-        <v>17.0568</v>
+        <v>15.588</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3267</v>
+        <v>0.2884</v>
       </c>
       <c r="J279" t="n">
-        <v>11.7612</v>
+        <v>10.3824</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0118</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.4248</v>
+        <v>-0.2844</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.96</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.183</v>
+        <v>-0.1488</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.588</v>
+        <v>-5.3568</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9795</v>
+        <v>0.9433</v>
       </c>
       <c r="J282" t="n">
-        <v>35.262</v>
+        <v>33.9588</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3385</v>
+        <v>0.2858</v>
       </c>
       <c r="J283" t="n">
-        <v>12.186</v>
+        <v>10.2888</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.05</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1431</v>
+        <v>0.111</v>
       </c>
       <c r="J284" t="n">
-        <v>5.1516</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2756</v>
+        <v>-0.2568</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.9216</v>
+        <v>-9.2448</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3963</v>
+        <v>-0.3862</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.2668</v>
+        <v>-13.9032</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.4</v>
       </c>
       <c r="I287" t="n">
-        <v>0.9881</v>
+        <v>0.984</v>
       </c>
       <c r="J287" t="n">
-        <v>35.5716</v>
+        <v>35.424</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.83</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J288" t="n">
-        <v>29.88</v>
+        <v>29.0124</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0054</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.3132</v>
+        <v>-0.1944</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.271</v>
+        <v>-0.231</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.756</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.65</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.926</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>-33.336</v>
+        <v>-32.9328</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.15</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3396</v>
+        <v>0.2867</v>
       </c>
       <c r="J292" t="n">
-        <v>11.5464</v>
+        <v>9.7478</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1867</v>
+        <v>0.1483</v>
       </c>
       <c r="J293" t="n">
-        <v>6.3478</v>
+        <v>5.0422</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0019</v>
+        <v>-0.001</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.0646</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0274</v>
+        <v>-0.0194</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.9316</v>
+        <v>-0.6596</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0751</v>
+        <v>-0.0602</v>
       </c>
       <c r="J296" t="n">
-        <v>-2.5534</v>
+        <v>-2.0468</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.41</v>
       </c>
       <c r="I297" t="n">
-        <v>1.0107</v>
+        <v>1.0115</v>
       </c>
       <c r="J297" t="n">
-        <v>34.3638</v>
+        <v>34.391</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.1</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3324</v>
+        <v>0.2922</v>
       </c>
       <c r="J298" t="n">
-        <v>11.3016</v>
+        <v>9.934799999999999</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>1.07</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2513</v>
+        <v>0.215</v>
       </c>
       <c r="J299" t="n">
-        <v>8.5442</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0654</v>
+        <v>-0.047</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.2236</v>
+        <v>-1.598</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.9231</v>
+        <v>-0.9111</v>
       </c>
       <c r="J301" t="n">
-        <v>-31.3854</v>
+        <v>-30.9774</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>1.81</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5103</v>
+        <v>1.547</v>
       </c>
       <c r="J302" t="n">
-        <v>37.7575</v>
+        <v>38.675</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>1.27</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6904</v>
+        <v>0.6606</v>
       </c>
       <c r="J303" t="n">
-        <v>17.26</v>
+        <v>16.515</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I304" t="n">
-        <v>0.6492</v>
+        <v>0.6179</v>
       </c>
       <c r="J304" t="n">
-        <v>16.23</v>
+        <v>15.4475</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4079</v>
+        <v>-0.367</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.1975</v>
+        <v>-9.175000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5803</v>
+        <v>-0.5442</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.5075</v>
+        <v>-13.605</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="I307" t="n">
-        <v>0.0726</v>
+        <v>0.0532</v>
       </c>
       <c r="J307" t="n">
-        <v>1.815</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0442</v>
+        <v>-0.035</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.105</v>
+        <v>-0.875</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2084</v>
+        <v>-0.1899</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.21</v>
+        <v>-4.7475</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.314</v>
+        <v>-0.2969</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.85</v>
+        <v>-7.4225</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>0.7</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3326</v>
+        <v>-0.3163</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.315</v>
+        <v>-7.9075</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3318</v>
+        <v>0.279</v>
       </c>
       <c r="J312" t="n">
-        <v>11.2812</v>
+        <v>9.486000000000001</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2754</v>
+        <v>0.2266</v>
       </c>
       <c r="J313" t="n">
-        <v>9.3636</v>
+        <v>7.7044</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1946</v>
+        <v>0.154</v>
       </c>
       <c r="J314" t="n">
-        <v>6.6164</v>
+        <v>5.236</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>0.99</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.0245</v>
+        <v>-0.0178</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.833</v>
+        <v>-0.6052</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4357</v>
+        <v>-0.4291</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.8138</v>
+        <v>-14.5894</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.22</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6169</v>
+        <v>0.5789</v>
       </c>
       <c r="J317" t="n">
-        <v>20.9746</v>
+        <v>19.6826</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>1.21</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5945</v>
+        <v>0.5556</v>
       </c>
       <c r="J318" t="n">
-        <v>20.213</v>
+        <v>18.8904</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1618</v>
+        <v>0.1335</v>
       </c>
       <c r="J319" t="n">
-        <v>5.5012</v>
+        <v>4.539</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0076</v>
+        <v>-0.0046</v>
       </c>
       <c r="J320" t="n">
-        <v>-0.2584</v>
+        <v>-0.1564</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5986</v>
+        <v>-0.5602</v>
       </c>
       <c r="J321" t="n">
-        <v>-20.3524</v>
+        <v>-19.0468</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0844</v>
+        <v>-0.0683</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.8568</v>
+        <v>-1.5026</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2517</v>
+        <v>-0.2373</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.5374</v>
+        <v>-5.2206</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>0.68</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3343</v>
+        <v>-0.321</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.3546</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.64</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3696</v>
+        <v>-0.3573</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.1312</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.46</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5282</v>
+        <v>-0.53</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.6204</v>
+        <v>-11.66</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.87</v>
       </c>
       <c r="I327" t="n">
-        <v>1.531</v>
+        <v>1.5648</v>
       </c>
       <c r="J327" t="n">
-        <v>33.682</v>
+        <v>34.4256</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>1.7</v>
       </c>
       <c r="I328" t="n">
-        <v>1.3235</v>
+        <v>1.3446</v>
       </c>
       <c r="J328" t="n">
-        <v>29.117</v>
+        <v>29.5812</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>1.46</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0127</v>
+        <v>1.0189</v>
       </c>
       <c r="J329" t="n">
-        <v>22.2794</v>
+        <v>22.4158</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.4235</v>
+        <v>0.3923</v>
       </c>
       <c r="J330" t="n">
-        <v>9.317</v>
+        <v>8.630599999999999</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.91</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3877</v>
+        <v>-0.3532</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.529400000000001</v>
+        <v>-7.7704</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>1.61</v>
       </c>
       <c r="I332" t="n">
-        <v>1.248</v>
+        <v>1.2652</v>
       </c>
       <c r="J332" t="n">
-        <v>32.448</v>
+        <v>32.8952</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>1.38</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9069</v>
+        <v>0.891</v>
       </c>
       <c r="J333" t="n">
-        <v>23.5794</v>
+        <v>23.166</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.4995</v>
+        <v>0.4659</v>
       </c>
       <c r="J334" t="n">
-        <v>12.987</v>
+        <v>12.1134</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>0.97</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.175</v>
+        <v>-0.1439</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.55</v>
+        <v>-3.7414</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2089</v>
+        <v>-0.1748</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.4314</v>
+        <v>-4.5448</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3187</v>
+        <v>0.2681</v>
       </c>
       <c r="J337" t="n">
-        <v>8.286199999999999</v>
+        <v>6.9706</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1466</v>
+        <v>0.1125</v>
       </c>
       <c r="J338" t="n">
-        <v>3.8116</v>
+        <v>2.925</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2416</v>
+        <v>-0.2221</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.2816</v>
+        <v>-5.7746</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.74</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2994</v>
+        <v>-0.2814</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.7844</v>
+        <v>-7.3164</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3088</v>
+        <v>-0.2912</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.0288</v>
+        <v>-7.5712</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.66</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3506</v>
+        <v>1.3787</v>
       </c>
       <c r="J342" t="n">
-        <v>40.518</v>
+        <v>41.361</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.12</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3744</v>
+        <v>0.3355</v>
       </c>
       <c r="J343" t="n">
-        <v>11.232</v>
+        <v>10.065</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0447</v>
+        <v>0.0334</v>
       </c>
       <c r="J344" t="n">
-        <v>1.341</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>0.98</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.116</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.48</v>
+        <v>-2.682</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8062</v>
+        <v>-0.7836</v>
       </c>
       <c r="J346" t="n">
-        <v>-24.186</v>
+        <v>-23.508</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.13</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3173</v>
+        <v>0.2654</v>
       </c>
       <c r="J347" t="n">
-        <v>9.519</v>
+        <v>7.962</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>1.09</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2395</v>
+        <v>0.1939</v>
       </c>
       <c r="J348" t="n">
-        <v>7.185</v>
+        <v>5.817</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.98</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0409</v>
+        <v>-0.0316</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.227</v>
+        <v>-0.948</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.83</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2189</v>
+        <v>-0.1985</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.567</v>
+        <v>-5.955</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.259</v>
+        <v>-0.2392</v>
       </c>
       <c r="J351" t="n">
-        <v>-7.77</v>
+        <v>-7.176</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.02</v>
       </c>
       <c r="I352" t="n">
-        <v>0.136</v>
+        <v>0.1128</v>
       </c>
       <c r="J352" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>0.96</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0429</v>
+        <v>-0.0312</v>
       </c>
       <c r="J353" t="n">
-        <v>-1.0725</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>0.66</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.3585</v>
+        <v>-0.3446</v>
       </c>
       <c r="J354" t="n">
-        <v>-8.9625</v>
+        <v>-8.615</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>0.62</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3945</v>
+        <v>-0.3827</v>
       </c>
       <c r="J355" t="n">
-        <v>-9.862500000000001</v>
+        <v>-9.567500000000001</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.5</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5003</v>
+        <v>-0.499</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.5075</v>
+        <v>-12.475</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.78</v>
       </c>
       <c r="I357" t="n">
-        <v>1.4413</v>
+        <v>1.4691</v>
       </c>
       <c r="J357" t="n">
-        <v>36.0325</v>
+        <v>36.7275</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.77</v>
       </c>
       <c r="I358" t="n">
-        <v>1.4288</v>
+        <v>1.4558</v>
       </c>
       <c r="J358" t="n">
-        <v>35.72</v>
+        <v>36.395</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>1.11</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3157</v>
+        <v>0.2839</v>
       </c>
       <c r="J359" t="n">
-        <v>7.8925</v>
+        <v>7.0975</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>1</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.0547</v>
+        <v>-0.0506</v>
       </c>
       <c r="J360" t="n">
-        <v>-1.3675</v>
+        <v>-1.265</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.97</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.1926</v>
+        <v>-0.1634</v>
       </c>
       <c r="J361" t="n">
-        <v>-4.815</v>
+        <v>-4.085</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>0.88</v>
       </c>
       <c r="I362" t="n">
-        <v>-0.137</v>
+        <v>-0.1212</v>
       </c>
       <c r="J362" t="n">
-        <v>-2.603</v>
+        <v>-2.3028</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.87</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.1486</v>
+        <v>-0.1328</v>
       </c>
       <c r="J363" t="n">
-        <v>-2.8234</v>
+        <v>-2.5232</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.77</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.254</v>
+        <v>-0.2394</v>
       </c>
       <c r="J364" t="n">
-        <v>-4.826</v>
+        <v>-4.5486</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.54</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4602</v>
+        <v>-0.4541</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.7438</v>
+        <v>-8.6279</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.49</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.504</v>
+        <v>-0.5028</v>
       </c>
       <c r="J366" t="n">
-        <v>-9.576000000000001</v>
+        <v>-9.5532</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.86</v>
       </c>
       <c r="I367" t="n">
-        <v>1.5056</v>
+        <v>1.5376</v>
       </c>
       <c r="J367" t="n">
-        <v>28.6064</v>
+        <v>29.2144</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.64</v>
       </c>
       <c r="I368" t="n">
-        <v>1.2388</v>
+        <v>1.2583</v>
       </c>
       <c r="J368" t="n">
-        <v>23.5372</v>
+        <v>23.9077</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.36</v>
       </c>
       <c r="I369" t="n">
-        <v>0.832</v>
+        <v>0.8226</v>
       </c>
       <c r="J369" t="n">
-        <v>15.808</v>
+        <v>15.6294</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.33</v>
       </c>
       <c r="I370" t="n">
-        <v>0.774</v>
+        <v>0.7605</v>
       </c>
       <c r="J370" t="n">
-        <v>14.706</v>
+        <v>14.4495</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>1.27</v>
       </c>
       <c r="I371" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6324</v>
       </c>
       <c r="J371" t="n">
-        <v>12.4203</v>
+        <v>12.0156</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>2.03</v>
       </c>
       <c r="I372" t="n">
-        <v>1.6844</v>
+        <v>1.7307</v>
       </c>
       <c r="J372" t="n">
-        <v>28.6348</v>
+        <v>29.4219</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1.99</v>
       </c>
       <c r="I373" t="n">
-        <v>1.6389</v>
+        <v>1.6814</v>
       </c>
       <c r="J373" t="n">
-        <v>27.8613</v>
+        <v>28.5838</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>1.44</v>
       </c>
       <c r="I374" t="n">
-        <v>0.9644</v>
+        <v>0.9709</v>
       </c>
       <c r="J374" t="n">
-        <v>16.3948</v>
+        <v>16.5053</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>1.27</v>
       </c>
       <c r="I375" t="n">
-        <v>0.6389</v>
+        <v>0.6173</v>
       </c>
       <c r="J375" t="n">
-        <v>10.8613</v>
+        <v>10.4941</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>1.27</v>
       </c>
       <c r="I376" t="n">
-        <v>0.6389</v>
+        <v>0.6173</v>
       </c>
       <c r="J376" t="n">
-        <v>10.8613</v>
+        <v>10.4941</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I377" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0726</v>
       </c>
       <c r="J377" t="n">
-        <v>0.1496</v>
+        <v>1.2342</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>0.55</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.4278</v>
+        <v>-0.4242</v>
       </c>
       <c r="J378" t="n">
-        <v>-7.2726</v>
+        <v>-7.2114</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>0.53</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.4444</v>
+        <v>-0.4413</v>
       </c>
       <c r="J379" t="n">
-        <v>-7.5548</v>
+        <v>-7.5021</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>0.45</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.5125</v>
+        <v>-0.5128</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.7125</v>
+        <v>-8.717599999999999</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>0.17</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7648</v>
+        <v>-0.8087</v>
       </c>
       <c r="J381" t="n">
-        <v>-13.0016</v>
+        <v>-13.7479</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.76</v>
       </c>
       <c r="I382" t="n">
-        <v>1.3803</v>
+        <v>1.4057</v>
       </c>
       <c r="J382" t="n">
-        <v>27.606</v>
+        <v>28.114</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.71</v>
       </c>
       <c r="I383" t="n">
-        <v>1.3199</v>
+        <v>1.3429</v>
       </c>
       <c r="J383" t="n">
-        <v>26.398</v>
+        <v>26.858</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.47</v>
       </c>
       <c r="I384" t="n">
-        <v>1.019</v>
+        <v>1.0307</v>
       </c>
       <c r="J384" t="n">
-        <v>20.38</v>
+        <v>20.614</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.47</v>
       </c>
       <c r="I385" t="n">
-        <v>1.019</v>
+        <v>1.0307</v>
       </c>
       <c r="J385" t="n">
-        <v>20.38</v>
+        <v>20.614</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.24</v>
       </c>
       <c r="I386" t="n">
-        <v>0.5856</v>
+        <v>0.5607</v>
       </c>
       <c r="J386" t="n">
-        <v>11.712</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>0.7</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.2807</v>
+        <v>-0.2668</v>
       </c>
       <c r="J387" t="n">
-        <v>-5.614</v>
+        <v>-5.336</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>0.59</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3898</v>
+        <v>-0.3849</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.796</v>
+        <v>-7.698</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.55</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.4261</v>
+        <v>-0.423</v>
       </c>
       <c r="J389" t="n">
-        <v>-8.522</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.42</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.5374</v>
+        <v>-0.54</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.748</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.33</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.6182</v>
+        <v>-0.6315</v>
       </c>
       <c r="J391" t="n">
-        <v>-12.364</v>
+        <v>-12.63</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.47</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1005</v>
+        <v>1.1144</v>
       </c>
       <c r="J392" t="n">
-        <v>33.015</v>
+        <v>33.432</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>0.5264</v>
+        <v>0.4856</v>
       </c>
       <c r="J393" t="n">
-        <v>15.792</v>
+        <v>14.568</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>1.06</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2218</v>
+        <v>0.1881</v>
       </c>
       <c r="J394" t="n">
-        <v>6.654</v>
+        <v>5.643</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.84</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.5039</v>
+        <v>-0.4619</v>
       </c>
       <c r="J395" t="n">
-        <v>-15.117</v>
+        <v>-13.857</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.71</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.798</v>
+        <v>-0.7736</v>
       </c>
       <c r="J396" t="n">
-        <v>-23.94</v>
+        <v>-23.208</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>0.724</v>
+        <v>0.6673</v>
       </c>
       <c r="J397" t="n">
-        <v>21.72</v>
+        <v>20.019</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.05</v>
       </c>
       <c r="I398" t="n">
-        <v>0.1431</v>
+        <v>0.111</v>
       </c>
       <c r="J398" t="n">
-        <v>4.293</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>0.95</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0892</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.676</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>0.91</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1388</v>
+        <v>-0.1193</v>
       </c>
       <c r="J400" t="n">
-        <v>-4.164</v>
+        <v>-3.579</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>0.9</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.1504</v>
+        <v>-0.1304</v>
       </c>
       <c r="J401" t="n">
-        <v>-4.512</v>
+        <v>-3.912</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.34</v>
       </c>
       <c r="I402" t="n">
-        <v>0.668</v>
+        <v>0.6116</v>
       </c>
       <c r="J402" t="n">
-        <v>18.704</v>
+        <v>17.1248</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.14</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3336</v>
+        <v>0.2807</v>
       </c>
       <c r="J403" t="n">
-        <v>9.3408</v>
+        <v>7.8596</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.96</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.0708</v>
+        <v>-0.0572</v>
       </c>
       <c r="J404" t="n">
-        <v>-1.9824</v>
+        <v>-1.6016</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.82</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.23</v>
+        <v>-0.2096</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.44</v>
+        <v>-5.8688</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.61</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4263</v>
+        <v>-0.4185</v>
       </c>
       <c r="J406" t="n">
-        <v>-11.9364</v>
+        <v>-11.718</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.5</v>
       </c>
       <c r="I407" t="n">
-        <v>1.1337</v>
+        <v>1.1483</v>
       </c>
       <c r="J407" t="n">
-        <v>31.7436</v>
+        <v>32.1524</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.2</v>
       </c>
       <c r="I408" t="n">
-        <v>0.5645</v>
+        <v>0.5254</v>
       </c>
       <c r="J408" t="n">
-        <v>15.806</v>
+        <v>14.7112</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>0.93</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.2757</v>
+        <v>-0.2354</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.7196</v>
+        <v>-6.5912</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.9</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3586</v>
+        <v>-0.316</v>
       </c>
       <c r="J410" t="n">
-        <v>-10.0408</v>
+        <v>-8.848000000000001</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.89</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.385</v>
+        <v>-0.3421</v>
       </c>
       <c r="J411" t="n">
-        <v>-10.78</v>
+        <v>-9.578799999999999</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.79</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4761</v>
+        <v>1.5086</v>
       </c>
       <c r="J412" t="n">
-        <v>53.1396</v>
+        <v>54.3096</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.26</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J413" t="n">
-        <v>23.9688</v>
+        <v>22.9176</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.3299</v>
+        <v>0.2974</v>
       </c>
       <c r="J414" t="n">
-        <v>11.8764</v>
+        <v>10.7064</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.1</v>
       </c>
       <c r="I415" t="n">
-        <v>0.304</v>
+        <v>0.272</v>
       </c>
       <c r="J415" t="n">
-        <v>10.944</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>0.93</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3037</v>
+        <v>-0.265</v>
       </c>
       <c r="J416" t="n">
-        <v>-10.9332</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3746</v>
+        <v>0.3213</v>
       </c>
       <c r="J417" t="n">
-        <v>13.4856</v>
+        <v>11.5668</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.01</v>
       </c>
       <c r="I418" t="n">
-        <v>0.0616</v>
+        <v>0.043</v>
       </c>
       <c r="J418" t="n">
-        <v>2.2176</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="419">
@@ -20029,10 +20029,10 @@
         <v>0.9</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1389</v>
+        <v>-0.1217</v>
       </c>
       <c r="J419" t="n">
-        <v>-5.0004</v>
+        <v>-4.3812</v>
       </c>
     </row>
     <row r="420">
@@ -20069,10 +20069,10 @@
         <v>0.8</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.712</v>
+        <v>-8.006399999999999</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.59</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4362</v>
+        <v>-0.4286</v>
       </c>
       <c r="J421" t="n">
-        <v>-15.7032</v>
+        <v>-15.4296</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>0.82</v>
       </c>
       <c r="I422" t="n">
-        <v>-0.2037</v>
+        <v>-0.1884</v>
       </c>
       <c r="J422" t="n">
-        <v>-4.4814</v>
+        <v>-4.1448</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>0.78</v>
       </c>
       <c r="I423" t="n">
-        <v>-0.2445</v>
+        <v>-0.2297</v>
       </c>
       <c r="J423" t="n">
-        <v>-5.379</v>
+        <v>-5.0534</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.3096</v>
+        <v>-0.2954</v>
       </c>
       <c r="J424" t="n">
-        <v>-6.8112</v>
+        <v>-6.4988</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>0.65</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.3628</v>
+        <v>-0.3498</v>
       </c>
       <c r="J425" t="n">
-        <v>-7.9816</v>
+        <v>-7.6956</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>0.6</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.4073</v>
+        <v>-0.3968</v>
       </c>
       <c r="J426" t="n">
-        <v>-8.960599999999999</v>
+        <v>-8.7296</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.76</v>
       </c>
       <c r="I427" t="n">
-        <v>1.3954</v>
+        <v>1.4202</v>
       </c>
       <c r="J427" t="n">
-        <v>30.6988</v>
+        <v>31.2444</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>1.59</v>
       </c>
       <c r="I428" t="n">
-        <v>1.1836</v>
+        <v>1.2003</v>
       </c>
       <c r="J428" t="n">
-        <v>26.0392</v>
+        <v>26.4066</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>1.47</v>
       </c>
       <c r="I429" t="n">
-        <v>1.0263</v>
+        <v>1.0348</v>
       </c>
       <c r="J429" t="n">
-        <v>22.5786</v>
+        <v>22.7656</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>1.29</v>
       </c>
       <c r="I430" t="n">
-        <v>0.7029</v>
+        <v>0.6835</v>
       </c>
       <c r="J430" t="n">
-        <v>15.4638</v>
+        <v>15.037</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>1.05</v>
       </c>
       <c r="I431" t="n">
-        <v>0.1323</v>
+        <v>0.1041</v>
       </c>
       <c r="J431" t="n">
-        <v>2.9106</v>
+        <v>2.2902</v>
       </c>
     </row>
   </sheetData>
